--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F4DFFB-1EAC-4B33-B3F4-4DD90D2D9141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4214C8CC-9118-40D4-ABAB-A5E3B8C8698E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>Freq:</t>
   </si>
@@ -171,6 +171,51 @@
   </si>
   <si>
     <t>Contents 2:</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>viclink receive freq</t>
+  </si>
+  <si>
+    <t>msllink receive freq</t>
+  </si>
+  <si>
+    <t>my user 1</t>
+  </si>
+  <si>
+    <t>my user 2</t>
+  </si>
+  <si>
+    <t>Long Range File Verify Radar Elevation Slew</t>
+  </si>
+  <si>
+    <t>Long Range File Verify Radar Azimuth Slew Speed</t>
+  </si>
+  <si>
+    <t>Slew Y</t>
+  </si>
+  <si>
+    <t>Slew X</t>
+  </si>
+  <si>
+    <t>FOVY</t>
+  </si>
+  <si>
+    <t>FOVX</t>
+  </si>
+  <si>
+    <t>Gimbal FOV</t>
+  </si>
+  <si>
+    <t>Gimbal Pitch</t>
+  </si>
+  <si>
+    <t>Gimbal Pivot</t>
   </si>
 </sst>
 </file>
@@ -193,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,8 +251,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -230,11 +281,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -243,9 +368,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -565,366 +717,611 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="D3" s="8"/>
+      <c r="E3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="D4" s="8"/>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="C6" s="5"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="D7" s="8"/>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="C9" s="5"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="2">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="D10" s="8"/>
+      <c r="E10" s="2">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="2">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="2">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="D13" s="8"/>
+      <c r="E13" s="2">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="C14" s="5"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="2">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="D15" s="8"/>
+      <c r="E15" s="2">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="C16" s="5"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="2">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="C17" s="5"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="2">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="D18" s="8"/>
+      <c r="E18" s="2">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="C19" s="5"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="C20" s="5"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="2">
+        <v>17</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="D21" s="8"/>
+      <c r="E21" s="2">
+        <v>18</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="C22" s="5"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="2">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="C23" s="5"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="2">
+        <v>20</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="D24" s="8"/>
+      <c r="E24" s="2">
+        <v>21</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="C25" s="5"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="2">
+        <v>22</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="C26" s="5"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="2">
+        <v>23</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="D27" s="8"/>
+      <c r="E27" s="2">
+        <v>24</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="C28" s="5"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="2">
+        <v>25</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="C29" s="5"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="2">
+        <v>26</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="D30" s="8"/>
+      <c r="E30" s="2">
+        <v>27</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="C31" s="5"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="2">
+        <v>28</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="C32" s="5"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="2">
+        <v>29</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="D33" s="8"/>
+      <c r="E33" s="2">
+        <v>30</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>31</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="4"/>
+      <c r="C34" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="2">
+        <v>31</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="2">
+        <v>32</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C6:C8"/>
+  <mergeCells count="15">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4214C8CC-9118-40D4-ABAB-A5E3B8C8698E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91741AD0-1F12-44D5-8B55-4409226E9284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>Freq:</t>
   </si>
@@ -164,9 +164,6 @@
     <t>new check current azim</t>
   </si>
   <si>
-    <t>free :3</t>
-  </si>
-  <si>
     <t>TWS</t>
   </si>
   <si>
@@ -216,6 +213,15 @@
   </si>
   <si>
     <t>Gimbal Pivot</t>
+  </si>
+  <si>
+    <t>time since detected scan radars</t>
+  </si>
+  <si>
+    <t>time since detected new check</t>
+  </si>
+  <si>
+    <t>time since detected</t>
   </si>
 </sst>
 </file>
@@ -359,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -367,17 +373,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -399,9 +399,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,7 +718,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
@@ -731,48 +728,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>44</v>
+      <c r="G3" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -782,15 +779,15 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -801,13 +798,13 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -818,13 +815,13 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -835,15 +832,15 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -854,13 +851,13 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="8"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -871,13 +868,13 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -888,15 +885,15 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -907,13 +904,13 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -924,13 +921,13 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="8"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -941,15 +938,15 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -960,13 +957,13 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -977,15 +974,15 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -996,13 +993,13 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="6"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -1013,8 +1010,8 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1028,10 +1025,10 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1045,8 +1042,8 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1060,8 +1057,8 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1075,10 +1072,10 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1092,8 +1089,8 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -1107,8 +1104,8 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="6"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -1122,10 +1119,10 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -1139,8 +1136,8 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="8"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="6"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -1154,8 +1151,8 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="6"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -1169,10 +1166,10 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="6"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -1186,8 +1183,8 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="8"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="6"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -1201,8 +1198,8 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="8"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="6"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -1216,10 +1213,10 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="6"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -1233,8 +1230,8 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="8"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="6"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -1248,8 +1245,8 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="8"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="6"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
@@ -1266,44 +1263,44 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="6"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="6"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="9"/>
+        <v>60</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="3"/>
+      <c r="G35" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1324,5 +1321,6 @@
     <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91741AD0-1F12-44D5-8B55-4409226E9284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C246C11E-91B4-4B10-BE5E-24555B8DAC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -379,6 +379,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -395,9 +398,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -728,28 +728,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -761,7 +761,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="7"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -782,7 +782,7 @@
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="7"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="7"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
@@ -816,7 +816,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="6"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -835,7 +835,7 @@
       <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -852,7 +852,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -869,7 +869,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -888,7 +888,7 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
@@ -922,7 +922,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="6"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
@@ -941,7 +941,7 @@
       <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
@@ -958,7 +958,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="6"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -977,7 +977,7 @@
       <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -994,7 +994,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="6"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="6"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1028,7 +1028,7 @@
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="6"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="6"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1075,7 +1075,7 @@
       <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="6"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="6"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -1122,7 +1122,7 @@
       <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="6"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="6"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -1169,7 +1169,7 @@
       <c r="C27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="6"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="6"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -1216,7 +1216,7 @@
       <c r="C30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="6"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="6"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="C34" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>60</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="7"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C246C11E-91B4-4B10-BE5E-24555B8DAC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4D3422-064A-4D7B-BFE3-DD58FD6AB085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>Freq:</t>
   </si>
@@ -188,18 +188,6 @@
     <t>my user 2</t>
   </si>
   <si>
-    <t>Long Range File Verify Radar Elevation Slew</t>
-  </si>
-  <si>
-    <t>Long Range File Verify Radar Azimuth Slew Speed</t>
-  </si>
-  <si>
-    <t>Slew Y</t>
-  </si>
-  <si>
-    <t>Slew X</t>
-  </si>
-  <si>
     <t>FOVY</t>
   </si>
   <si>
@@ -222,6 +210,108 @@
   </si>
   <si>
     <t>time since detected</t>
+  </si>
+  <si>
+    <t>enemy trans1 x</t>
+  </si>
+  <si>
+    <t>enemy trans1 y</t>
+  </si>
+  <si>
+    <t>enemy trans1 z</t>
+  </si>
+  <si>
+    <t>enemy trans2 x</t>
+  </si>
+  <si>
+    <t>enemy trans2 y</t>
+  </si>
+  <si>
+    <t>enemy trans2 z</t>
+  </si>
+  <si>
+    <t>friendly trans x</t>
+  </si>
+  <si>
+    <t>friendly trans y</t>
+  </si>
+  <si>
+    <t>friendly trans z</t>
+  </si>
+  <si>
+    <t>missile trans1 x</t>
+  </si>
+  <si>
+    <t>missile trans1 y</t>
+  </si>
+  <si>
+    <t>missile trans1 z</t>
+  </si>
+  <si>
+    <t>my username</t>
+  </si>
+  <si>
+    <t>EVA</t>
+  </si>
+  <si>
+    <t>enemy trans1 index</t>
+  </si>
+  <si>
+    <t>enemy trans2 index</t>
+  </si>
+  <si>
+    <t>friendly trans1 index</t>
+  </si>
+  <si>
+    <t>new check elevation slew</t>
+  </si>
+  <si>
+    <t>new check azim slew speed</t>
+  </si>
+  <si>
+    <t>old check slew Y</t>
+  </si>
+  <si>
+    <t>old check slew X</t>
+  </si>
+  <si>
+    <t>transmit indexes</t>
+  </si>
+  <si>
+    <t>new check radar slews</t>
+  </si>
+  <si>
+    <t>old check radar slews</t>
+  </si>
+  <si>
+    <t>old check radar FOVs</t>
+  </si>
+  <si>
+    <t>gimbal Controls</t>
+  </si>
+  <si>
+    <t>enemy transmit 1</t>
+  </si>
+  <si>
+    <t>enemy transmit 2</t>
+  </si>
+  <si>
+    <t>friendly transmit 1</t>
+  </si>
+  <si>
+    <t>missile transmit 1</t>
+  </si>
+  <si>
+    <t>selected target y</t>
+  </si>
+  <si>
+    <t>selected target z</t>
+  </si>
+  <si>
+    <t>selected target x</t>
+  </si>
+  <si>
+    <t>selected target</t>
   </si>
 </sst>
 </file>
@@ -264,7 +354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -276,43 +366,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -365,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -382,22 +435,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -714,20 +758,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="26.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
@@ -737,21 +787,41 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="9" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -761,7 +831,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -771,8 +841,27 @@
       <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -782,16 +871,33 @@
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -799,16 +905,29 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="4"/>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="2">
+        <v>2</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -816,16 +935,31 @@
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="2">
+        <v>3</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -835,16 +969,33 @@
       <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="2">
+        <v>4</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -852,16 +1003,31 @@
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -869,16 +1035,29 @@
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="I9" s="2">
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="2">
+        <v>6</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -888,16 +1067,33 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="2">
+        <v>7</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -905,16 +1101,29 @@
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="2">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -922,16 +1131,31 @@
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="2">
+        <v>9</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -941,16 +1165,31 @@
       <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="I13" s="2">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="2">
+        <v>10</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -958,16 +1197,31 @@
         <v>12</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="2">
+        <v>11</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="2">
+        <v>11</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -977,16 +1231,29 @@
       <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="7"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="I15" s="2">
+        <v>12</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="2">
+        <v>12</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -994,16 +1261,31 @@
         <v>14</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="I16" s="2">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="2">
+        <v>13</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1011,14 +1293,31 @@
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="2">
+        <v>14</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="2">
+        <v>14</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1028,14 +1327,29 @@
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="7"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="I18" s="2">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="2">
+        <v>15</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1043,14 +1357,31 @@
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="I19" s="2">
+        <v>16</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="2">
+        <v>16</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1058,14 +1389,31 @@
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="2">
+        <v>17</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="2">
+        <v>17</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1075,14 +1423,29 @@
       <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="7"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="I21" s="2">
+        <v>18</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="2">
+        <v>18</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1090,14 +1453,31 @@
         <v>28</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="I22" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="2">
+        <v>19</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1105,14 +1485,31 @@
         <v>29</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="7"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="2">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="2">
+        <v>20</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1122,14 +1519,29 @@
       <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="7"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="I24" s="2">
+        <v>21</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="2">
+        <v>21</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1137,14 +1549,31 @@
         <v>34</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="I25" s="2">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="2">
+        <v>22</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1152,14 +1581,31 @@
         <v>35</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="2">
+        <v>23</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="2">
+        <v>23</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -1169,14 +1615,29 @@
       <c r="C27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="7"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="I27" s="2">
+        <v>24</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="2">
+        <v>24</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -1184,14 +1645,27 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="I28" s="2">
+        <v>25</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="2">
+        <v>25</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -1199,14 +1673,29 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I29" s="2">
+        <v>26</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="2">
+        <v>26</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -1216,14 +1705,27 @@
       <c r="C30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="7"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="I30" s="2">
+        <v>27</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="2">
+        <v>27</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -1231,14 +1733,27 @@
         <v>38</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="7"/>
+      <c r="D31" s="5"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="I31" s="2">
+        <v>28</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="2">
+        <v>28</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -1246,14 +1761,29 @@
         <v>39</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="7"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="2">
+        <v>29</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="2">
+        <v>29</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -1263,47 +1793,106 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="7"/>
+      <c r="D33" s="5"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="8"/>
+      <c r="I33" s="2">
+        <v>30</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="2">
+        <v>30</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="D34" s="5"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="I34" s="2">
+        <v>31</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="2">
+        <v>31</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="5"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
+      <c r="I35" s="2">
+        <v>32</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="2">
+        <v>32</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="38">
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -1319,6 +1908,7 @@
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4D3422-064A-4D7B-BFE3-DD58FD6AB085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF99A9E7-2065-4EEE-B872-FD815C4142AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
   <si>
     <t>Freq:</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>selected target</t>
+  </si>
+  <si>
+    <t>missile trans1 index</t>
   </si>
 </sst>
 </file>
@@ -432,16 +435,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,48 +781,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="I1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="I1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="I2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -831,7 +834,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -850,7 +853,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -871,7 +874,7 @@
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -890,7 +893,7 @@
       <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -905,7 +908,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
@@ -920,7 +923,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="4"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -935,7 +938,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -952,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="8"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -969,7 +972,7 @@
       <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -988,7 +991,7 @@
       <c r="K7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="8"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1003,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="8"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -1050,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="8"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1067,7 +1070,7 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
@@ -1086,7 +1089,7 @@
       <c r="K10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="8"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1101,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>59</v>
       </c>
       <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="8"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>60</v>
       </c>
       <c r="K12" s="4"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="8"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1165,7 +1168,7 @@
       <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
@@ -1182,7 +1185,7 @@
       <c r="K13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="5"/>
+      <c r="L13" s="8"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>62</v>
       </c>
       <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="8"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1231,7 +1234,7 @@
       <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="4"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1261,7 +1264,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1278,7 +1281,7 @@
       <c r="K16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="5"/>
+      <c r="L16" s="8"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>65</v>
       </c>
       <c r="K17" s="4"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1327,7 +1330,7 @@
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1342,7 +1345,7 @@
         <v>66</v>
       </c>
       <c r="K18" s="4"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="8"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1357,7 +1360,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1374,7 +1377,7 @@
       <c r="K19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L19" s="5"/>
+      <c r="L19" s="8"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1389,7 +1392,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1406,7 +1409,7 @@
         <v>68</v>
       </c>
       <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="8"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1423,7 +1426,7 @@
       <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1438,7 +1441,7 @@
         <v>69</v>
       </c>
       <c r="K21" s="4"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="8"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -1467,10 +1470,10 @@
       <c r="J22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="5"/>
+      <c r="L22" s="8"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -1501,8 +1504,8 @@
       <c r="J23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="5"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -1519,7 +1522,7 @@
       <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -1533,8 +1536,8 @@
       <c r="J24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="5"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="8"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -1561,12 +1564,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="L25" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="8"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -1581,7 +1582,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -1595,10 +1596,12 @@
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="8"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -1615,7 +1618,7 @@
       <c r="C27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -1627,10 +1630,10 @@
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="8"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -1645,7 +1648,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="D28" s="8"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -1656,9 +1659,11 @@
       <c r="I28" s="2">
         <v>25</v>
       </c>
-      <c r="J28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="8"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -1673,14 +1678,14 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>79</v>
       </c>
       <c r="I29" s="2">
@@ -1688,7 +1693,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="8"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -1705,20 +1710,20 @@
       <c r="C30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="8"/>
+      <c r="G30" s="4"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="8"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -1733,20 +1738,20 @@
         <v>38</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="7"/>
+      <c r="G31" s="4"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="8"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -1761,22 +1766,20 @@
         <v>39</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
+      <c r="D32" s="8"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G32" s="4"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="8"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -1793,20 +1796,22 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="8"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -1823,20 +1828,20 @@
       <c r="C34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="G34" s="4"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="8"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -1851,18 +1856,20 @@
         <v>56</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="4"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="8"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -1870,29 +1877,7 @@
       <c r="O35" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
+  <mergeCells count="37">
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -1909,6 +1894,27 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF99A9E7-2065-4EEE-B872-FD815C4142AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD502741-2CD7-4354-B1C8-66805297CF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -435,6 +435,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -442,9 +445,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -781,48 +781,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="I2" s="8" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -834,7 +834,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -853,7 +853,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="8"/>
+      <c r="L3" s="5"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -874,7 +874,7 @@
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -893,7 +893,7 @@
       <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="8"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -908,7 +908,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
@@ -923,7 +923,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="4"/>
-      <c r="L5" s="8"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -938,7 +938,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="4"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
       <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -991,7 +991,7 @@
       <c r="K7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="8"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="8"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="5"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1070,7 +1070,7 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
@@ -1089,7 +1089,7 @@
       <c r="K10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="8"/>
+      <c r="L10" s="5"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>59</v>
       </c>
       <c r="K11" s="4"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="5"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="8"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>60</v>
       </c>
       <c r="K12" s="4"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="5"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1168,7 +1168,7 @@
       <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
@@ -1185,7 +1185,7 @@
       <c r="K13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="8"/>
+      <c r="L13" s="5"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>62</v>
       </c>
       <c r="K14" s="4"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="5"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1234,7 +1234,7 @@
       <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="4"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="5"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1281,7 +1281,7 @@
       <c r="K16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="8"/>
+      <c r="L16" s="5"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>65</v>
       </c>
       <c r="K17" s="4"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="5"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1330,7 +1330,7 @@
       <c r="C18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>66</v>
       </c>
       <c r="K18" s="4"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="5"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1377,7 +1377,7 @@
       <c r="K19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L19" s="8"/>
+      <c r="L19" s="5"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>68</v>
       </c>
       <c r="K20" s="4"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="5"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>69</v>
       </c>
       <c r="K21" s="4"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="5"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -1470,10 +1470,10 @@
       <c r="J22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="8"/>
+      <c r="L22" s="5"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -1504,8 +1504,8 @@
       <c r="J23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="8"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="5"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -1536,8 +1536,8 @@
       <c r="J24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="8"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="5"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -1566,8 +1566,8 @@
       <c r="J25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="5"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="8"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="K26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L26" s="8"/>
+      <c r="L26" s="5"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="C27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="K27" s="2"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="5"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="8"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>89</v>
       </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="5"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="5"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -1710,7 +1710,7 @@
       <c r="C30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
+      <c r="L30" s="5"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="5"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="5"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="8"/>
+      <c r="L32" s="5"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="5"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="5"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -1828,7 +1828,7 @@
       <c r="C34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="8"/>
+      <c r="D34" s="5"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="5"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="5"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="5"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -1878,6 +1878,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -1894,27 +1915,6 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD502741-2CD7-4354-B1C8-66805297CF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967B0FAC-D069-4780-9FDE-F192585107C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -1878,11 +1878,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
@@ -1899,22 +1910,11 @@
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K7:K9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967B0FAC-D069-4780-9FDE-F192585107C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9505D36E-7FF2-4519-A2DF-28DAED0E0D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="94">
   <si>
     <t>Freq:</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>missile trans1 index</t>
+  </si>
+  <si>
+    <t>TWS Dev Version</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -431,6 +434,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -761,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
@@ -781,48 +787,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="I1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -834,7 +840,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -853,7 +859,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -871,17 +877,17 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="2">
@@ -890,10 +896,10 @@
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="6"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -907,23 +913,23 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="5"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -937,8 +943,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -954,8 +960,8 @@
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -969,10 +975,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -988,10 +994,10 @@
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1005,15 +1011,15 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="2">
@@ -1022,8 +1028,8 @@
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1037,23 +1043,23 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="5"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1067,17 +1073,17 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="2">
@@ -1086,10 +1092,10 @@
       <c r="J10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1103,23 +1109,23 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="5"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1133,15 +1139,15 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="2">
@@ -1150,8 +1156,8 @@
       <c r="J12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1165,27 +1171,27 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="5"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="5"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1199,15 +1205,15 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I14" s="2">
@@ -1216,8 +1222,8 @@
       <c r="J14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1231,25 +1237,25 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="5"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1263,25 +1269,25 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="5"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="5"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1295,15 +1301,15 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I17" s="2">
@@ -1312,8 +1318,8 @@
       <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1327,25 +1333,25 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="5"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1359,25 +1365,25 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="4"/>
+      <c r="G19" s="5"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="L19" s="5"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1391,15 +1397,15 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>85</v>
       </c>
       <c r="I20" s="2">
@@ -1408,8 +1414,8 @@
       <c r="J20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1423,25 +1429,25 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="4"/>
+      <c r="G21" s="5"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1455,25 +1461,25 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="5"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="5"/>
+      <c r="L22" s="6"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -1487,15 +1493,15 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="I23" s="2">
@@ -1504,8 +1510,8 @@
       <c r="J23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="5"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="6"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -1519,25 +1525,25 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="4"/>
+      <c r="G24" s="5"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="5"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="6"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -1551,23 +1557,23 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="6"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="4"/>
+      <c r="G25" s="5"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="5"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="6"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -1581,15 +1587,15 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>87</v>
       </c>
       <c r="I26" s="2">
@@ -1601,7 +1607,7 @@
       <c r="K26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L26" s="5"/>
+      <c r="L26" s="6"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -1615,17 +1621,17 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="6"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="5"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -1633,7 +1639,7 @@
         <v>88</v>
       </c>
       <c r="K27" s="2"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="6"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -1647,15 +1653,15 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="4"/>
+      <c r="G28" s="5"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -1663,7 +1669,7 @@
         <v>89</v>
       </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="6"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -1677,15 +1683,15 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I29" s="2">
@@ -1693,7 +1699,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="6"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -1707,23 +1713,23 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="6"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="4"/>
+      <c r="G30" s="5"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="6"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -1737,21 +1743,21 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="4"/>
+      <c r="G31" s="5"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="6"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -1765,21 +1771,21 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G32" s="4"/>
+      <c r="G32" s="5"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="6"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -1796,14 +1802,14 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="6"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="5" t="s">
         <v>91</v>
       </c>
       <c r="I33" s="2">
@@ -1811,7 +1817,7 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="6"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -1825,23 +1831,23 @@
       <c r="B34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="6"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G34" s="4"/>
+      <c r="G34" s="5"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="6"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -1855,29 +1861,589 @@
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G35" s="4"/>
+      <c r="G35" s="5"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="6"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>2</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>3</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="2">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>4</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="2">
+        <v>4</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="2">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="2">
+        <v>6</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="2">
+        <v>7</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="2">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="2">
+        <v>9</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>10</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="2">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G49" s="5"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>11</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="2">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="2">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>13</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="2">
+        <v>13</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>14</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="2">
+        <v>14</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>15</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="E54" s="2">
+        <v>15</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54" s="5"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>16</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="2">
+        <v>16</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="5"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>17</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="2">
+        <v>17</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>18</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="2">
+        <v>18</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G57" s="5"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>19</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="2">
+        <v>19</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>20</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="2">
+        <v>20</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>21</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="2">
+        <v>21</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>22</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="2">
+        <v>22</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>23</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="2">
+        <v>23</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>24</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="2">
+        <v>24</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>25</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="2">
+        <v>25</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>26</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="2">
+        <v>26</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>27</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="2">
+        <v>27</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>28</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="2">
+        <v>28</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>29</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="2">
+        <v>29</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>30</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="2">
+        <v>30</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>31</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="6"/>
+      <c r="E70" s="2">
+        <v>31</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>32</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="2">
+        <v>32</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="49">
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -1894,27 +2460,6 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9505D36E-7FF2-4519-A2DF-28DAED0E0D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287EE06B-3E1C-4B06-B7D1-AADBDECBE7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="96">
   <si>
     <t>Freq:</t>
   </si>
@@ -287,9 +287,6 @@
     <t>old check radar FOVs</t>
   </si>
   <si>
-    <t>gimbal Controls</t>
-  </si>
-  <si>
     <t>enemy transmit 1</t>
   </si>
   <si>
@@ -317,7 +314,16 @@
     <t>missile trans1 index</t>
   </si>
   <si>
-    <t>TWS Dev Version</t>
+    <t>TSD</t>
+  </si>
+  <si>
+    <t>Zoom</t>
+  </si>
+  <si>
+    <t>forward radar ang</t>
+  </si>
+  <si>
+    <t>gimbal controls (might be removed)</t>
   </si>
 </sst>
 </file>
@@ -424,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -435,13 +441,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -451,6 +457,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,70 +776,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="6.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="19.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
     <col min="12" max="13" width="9.140625" style="1"/>
     <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5703125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="1"/>
+    <col min="21" max="21" width="7.28515625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+    </row>
+    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="I2" s="6" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="Q2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -840,7 +877,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -859,7 +896,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="6"/>
+      <c r="L3" s="5"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -869,25 +906,44 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" s="5"/>
+      <c r="U3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="2">
@@ -896,55 +952,83 @@
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="6"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q4" s="2">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="5"/>
+      <c r="U4" s="2">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="6"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="2">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -960,25 +1044,38 @@
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="2">
+        <v>3</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S6" s="6"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="2">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -994,32 +1091,47 @@
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="6"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q7" s="2">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T7" s="5"/>
+      <c r="U7" s="2">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="2">
@@ -1028,62 +1140,88 @@
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q8" s="2">
+        <v>5</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="6"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="2">
+        <v>5</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="5"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="2">
+        <v>6</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="6"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="2">
+        <v>6</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="2">
@@ -1092,62 +1230,90 @@
       <c r="J10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="L10" s="6"/>
+      <c r="K10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="5"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2">
+        <v>7</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="T10" s="5"/>
+      <c r="U10" s="2">
+        <v>7</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="5"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="2">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="S11" s="6"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="2">
+        <v>8</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="2">
@@ -1156,65 +1322,93 @@
       <c r="J12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="5"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2">
+        <v>9</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="S12" s="6"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="2">
+        <v>9</v>
+      </c>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="5"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q13" s="2">
+        <v>10</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="T13" s="5"/>
+      <c r="U13" s="2">
+        <v>10</v>
+      </c>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>83</v>
+      <c r="G14" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="I14" s="2">
         <v>11</v>
@@ -1222,95 +1416,136 @@
       <c r="J14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="5"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2">
+        <v>11</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S14" s="6"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="2">
+        <v>11</v>
+      </c>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="5"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2">
+        <v>12</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S15" s="6"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="2">
+        <v>12</v>
+      </c>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L16" s="6"/>
+      <c r="K16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2">
+        <v>13</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="T16" s="5"/>
+      <c r="U16" s="2">
+        <v>13</v>
+      </c>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>84</v>
+      <c r="G17" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="I17" s="2">
         <v>14</v>
@@ -1318,95 +1553,136 @@
       <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="5"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2">
+        <v>14</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S17" s="6"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="2">
+        <v>14</v>
+      </c>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="5"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2">
+        <v>15</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S18" s="6"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="2">
+        <v>15</v>
+      </c>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="6"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="5"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q19" s="2">
+        <v>16</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="T19" s="5"/>
+      <c r="U19" s="2">
+        <v>16</v>
+      </c>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>85</v>
+      <c r="G20" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="I20" s="2">
         <v>17</v>
@@ -1414,62 +1690,88 @@
       <c r="J20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="5"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2">
+        <v>17</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="S20" s="6"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="2">
+        <v>17</v>
+      </c>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="6"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="5"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="2">
+        <v>18</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S21" s="6"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="2">
+        <v>18</v>
+      </c>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="6"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -1479,30 +1781,45 @@
       <c r="K22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="6"/>
+      <c r="L22" s="5"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q22" s="2">
+        <v>19</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="T22" s="5"/>
+      <c r="U22" s="2">
+        <v>19</v>
+      </c>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>86</v>
+      <c r="G23" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="I23" s="2">
         <v>20</v>
@@ -1511,31 +1828,44 @@
         <v>73</v>
       </c>
       <c r="K23" s="8"/>
-      <c r="L23" s="6"/>
+      <c r="L23" s="5"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q23" s="2">
+        <v>20</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S23" s="8"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="2">
+        <v>20</v>
+      </c>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="6"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -1543,155 +1873,222 @@
         <v>74</v>
       </c>
       <c r="K24" s="8"/>
-      <c r="L24" s="6"/>
+      <c r="L24" s="5"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q24" s="2">
+        <v>21</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S24" s="8"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="2">
+        <v>21</v>
+      </c>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25" s="6"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="6"/>
+      <c r="L25" s="5"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q25" s="2">
+        <v>22</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S25" s="9"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="2">
+        <v>22</v>
+      </c>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>87</v>
+      <c r="G26" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L26" s="6"/>
+      <c r="L26" s="5"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q26" s="2">
+        <v>23</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T26" s="5"/>
+      <c r="U26" s="2">
+        <v>23</v>
+      </c>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27" s="6"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K27" s="2"/>
-      <c r="L27" s="6"/>
+      <c r="L27" s="5"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q27" s="2">
+        <v>24</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S27" s="8"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="2">
+        <v>24</v>
+      </c>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+    </row>
+    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="6"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="6"/>
+      <c r="L28" s="5"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2">
+        <v>25</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S28" s="9"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="2">
+        <v>25</v>
+      </c>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>79</v>
       </c>
       <c r="I29" s="2">
@@ -1699,100 +2096,148 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="6"/>
+      <c r="L29" s="5"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q29" s="2">
+        <v>26</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S29" s="2"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="2">
+        <v>26</v>
+      </c>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="6"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="6"/>
+      <c r="L30" s="5"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q30" s="2">
+        <v>27</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="S30" s="2"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="2">
+        <v>27</v>
+      </c>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+    </row>
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="5"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="5"/>
+      <c r="G31" s="6"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="6"/>
+      <c r="L31" s="5"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q31" s="2">
+        <v>28</v>
+      </c>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="2">
+        <v>28</v>
+      </c>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="G32" s="6"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="6"/>
+      <c r="L32" s="5"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q32" s="2">
+        <v>29</v>
+      </c>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="2">
+        <v>29</v>
+      </c>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+    </row>
+    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -1802,632 +2247,315 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="5"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="6"/>
+      <c r="L33" s="5"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q33" s="2">
+        <v>30</v>
+      </c>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="2">
+        <v>30</v>
+      </c>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+    </row>
+    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="5"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="G34" s="6"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="6"/>
+      <c r="L34" s="5"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q34" s="2">
+        <v>31</v>
+      </c>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="2">
+        <v>31</v>
+      </c>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+    </row>
+    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="5"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="G35" s="6"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="6"/>
+      <c r="L35" s="5"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>1</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="2">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2"/>
+      <c r="Q35" s="2">
+        <v>32</v>
+      </c>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="2">
+        <v>32</v>
+      </c>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>2</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="2">
-        <v>2</v>
-      </c>
-      <c r="F41" s="2"/>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>3</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="2">
-        <v>3</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>4</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="2">
-        <v>4</v>
-      </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>5</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="2">
-        <v>5</v>
-      </c>
-      <c r="F44" s="2"/>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="2">
-        <v>6</v>
-      </c>
-      <c r="F45" s="2"/>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2"/>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C46" s="4"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="2">
-        <v>7</v>
-      </c>
-      <c r="F46" s="2"/>
+      <c r="D46" s="10"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>8</v>
-      </c>
-      <c r="B47" s="2"/>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C47" s="4"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="2">
-        <v>8</v>
-      </c>
-      <c r="F47" s="2"/>
+      <c r="D47" s="10"/>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>9</v>
-      </c>
-      <c r="B48" s="2"/>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="2">
-        <v>9</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>10</v>
-      </c>
-      <c r="B49" s="2"/>
+      <c r="D48" s="10"/>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="2">
-        <v>10</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>11</v>
-      </c>
-      <c r="B50" s="2"/>
+      <c r="D49" s="10"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C50" s="4"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="2">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2"/>
+      <c r="D50" s="10"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>12</v>
-      </c>
-      <c r="B51" s="2"/>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C51" s="4"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="2">
-        <v>12</v>
-      </c>
-      <c r="F51" s="2"/>
+      <c r="D51" s="10"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>13</v>
-      </c>
-      <c r="B52" s="2"/>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C52" s="4"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="2">
-        <v>13</v>
-      </c>
-      <c r="F52" s="2"/>
+      <c r="D52" s="10"/>
       <c r="G52" s="4"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>14</v>
-      </c>
-      <c r="B53" s="2"/>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C53" s="4"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="2">
-        <v>14</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>15</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="2">
-        <v>15</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>16</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="2">
-        <v>16</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>17</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="2">
-        <v>17</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>18</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="2">
-        <v>18</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>19</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="2">
-        <v>19</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>20</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="2">
-        <v>20</v>
-      </c>
-      <c r="F59" s="2"/>
+      <c r="D53" s="10"/>
+      <c r="G53" s="10"/>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="G54" s="10"/>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="G55" s="10"/>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="G56" s="10"/>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="G57" s="10"/>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="G58" s="10"/>
+    </row>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
       <c r="G59" s="4"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>21</v>
-      </c>
-      <c r="B60" s="2"/>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C60" s="4"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="2">
-        <v>21</v>
-      </c>
-      <c r="F60" s="2"/>
+      <c r="D60" s="10"/>
       <c r="G60" s="4"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>22</v>
-      </c>
-      <c r="B61" s="2"/>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C61" s="4"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="2">
-        <v>22</v>
-      </c>
-      <c r="F61" s="2"/>
+      <c r="D61" s="10"/>
       <c r="G61" s="4"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>23</v>
-      </c>
-      <c r="B62" s="2"/>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C62" s="4"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="2">
-        <v>23</v>
-      </c>
-      <c r="F62" s="2"/>
+      <c r="D62" s="10"/>
       <c r="G62" s="4"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>24</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="2">
-        <v>24</v>
-      </c>
-      <c r="F63" s="2"/>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
       <c r="G63" s="4"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>25</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="2">
-        <v>25</v>
-      </c>
-      <c r="F64" s="2"/>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
       <c r="G64" s="4"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>26</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="2">
-        <v>26</v>
-      </c>
-      <c r="F65" s="2"/>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
       <c r="G65" s="4"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>27</v>
-      </c>
-      <c r="B66" s="2"/>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C66" s="4"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="2">
-        <v>27</v>
-      </c>
-      <c r="F66" s="2"/>
+      <c r="D66" s="10"/>
       <c r="G66" s="4"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>28</v>
-      </c>
-      <c r="B67" s="2"/>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C67" s="4"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="2">
-        <v>28</v>
-      </c>
-      <c r="F67" s="2"/>
+      <c r="D67" s="10"/>
       <c r="G67" s="4"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>29</v>
-      </c>
-      <c r="B68" s="2"/>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C68" s="4"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="2">
-        <v>29</v>
-      </c>
-      <c r="F68" s="2"/>
+      <c r="D68" s="10"/>
       <c r="G68" s="4"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>30</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="2">
-        <v>30</v>
-      </c>
-      <c r="F69" s="2"/>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D69" s="10"/>
       <c r="G69" s="4"/>
     </row>
-    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>31</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="2">
-        <v>31</v>
-      </c>
-      <c r="F70" s="2"/>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="4"/>
+      <c r="D70" s="10"/>
       <c r="G70" s="4"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>32</v>
-      </c>
-      <c r="B71" s="2"/>
+    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C71" s="4"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="2">
-        <v>32</v>
-      </c>
-      <c r="F71" s="2"/>
+      <c r="D71" s="10"/>
       <c r="G71" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
+  <mergeCells count="61">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
@@ -2444,22 +2572,35 @@
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K7:K9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:T35"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="S13:S15"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="S19:S21"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="S26:S28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287EE06B-3E1C-4B06-B7D1-AADBDECBE7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAB2246-75B7-47DA-91FE-5F92C124CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38400" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -444,10 +444,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,68 +804,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="I1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="Q1" s="5" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="Q1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="Q2" s="5" t="s">
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="Q2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5" t="s">
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -877,7 +877,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="S3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="5"/>
+      <c r="T3" s="6"/>
       <c r="U3" s="3" t="s">
         <v>0</v>
       </c>
@@ -933,17 +933,17 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="2">
@@ -952,10 +952,10 @@
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="6"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -967,10 +967,10 @@
       <c r="R4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="5"/>
+      <c r="T4" s="6"/>
       <c r="U4" s="2">
         <v>1</v>
       </c>
@@ -984,23 +984,23 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -1012,8 +1012,8 @@
       <c r="R5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="S5" s="6"/>
-      <c r="T5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="6"/>
       <c r="U5" s="2">
         <v>2</v>
       </c>
@@ -1027,8 +1027,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1044,8 +1044,8 @@
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -1057,8 +1057,8 @@
       <c r="R6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="S6" s="6"/>
-      <c r="T6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="6"/>
       <c r="U6" s="2">
         <v>3</v>
       </c>
@@ -1072,10 +1072,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1091,10 +1091,10 @@
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1106,10 +1106,10 @@
       <c r="R7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="S7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T7" s="5"/>
+      <c r="T7" s="6"/>
       <c r="U7" s="2">
         <v>4</v>
       </c>
@@ -1123,15 +1123,15 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="2">
@@ -1140,8 +1140,8 @@
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1153,8 +1153,8 @@
       <c r="R8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="6"/>
-      <c r="T8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="6"/>
       <c r="U8" s="2">
         <v>5</v>
       </c>
@@ -1168,23 +1168,23 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="5"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1196,8 +1196,8 @@
       <c r="R9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="S9" s="6"/>
-      <c r="T9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="6"/>
       <c r="U9" s="2">
         <v>6</v>
       </c>
@@ -1211,17 +1211,17 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="2">
@@ -1230,10 +1230,10 @@
       <c r="J10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1245,10 +1245,10 @@
       <c r="R10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="S10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="6"/>
       <c r="U10" s="2">
         <v>7</v>
       </c>
@@ -1262,23 +1262,23 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="5"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1290,8 +1290,8 @@
       <c r="R11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S11" s="6"/>
-      <c r="T11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="6"/>
       <c r="U11" s="2">
         <v>8</v>
       </c>
@@ -1305,15 +1305,15 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="2">
@@ -1322,8 +1322,8 @@
       <c r="J12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1335,8 +1335,8 @@
       <c r="R12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S12" s="6"/>
-      <c r="T12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="6"/>
       <c r="U12" s="2">
         <v>9</v>
       </c>
@@ -1350,27 +1350,27 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="5"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="5"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1382,10 +1382,10 @@
       <c r="R13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="S13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="6"/>
       <c r="U13" s="2">
         <v>10</v>
       </c>
@@ -1399,15 +1399,15 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="2">
@@ -1416,8 +1416,8 @@
       <c r="J14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1429,8 +1429,8 @@
       <c r="R14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S14" s="6"/>
-      <c r="T14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="6"/>
       <c r="U14" s="2">
         <v>11</v>
       </c>
@@ -1444,25 +1444,25 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="5"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1474,8 +1474,8 @@
       <c r="R15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S15" s="6"/>
-      <c r="T15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="6"/>
       <c r="U15" s="2">
         <v>12</v>
       </c>
@@ -1489,25 +1489,25 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L16" s="5"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1519,10 +1519,10 @@
       <c r="R16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S16" s="6" t="s">
+      <c r="S16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="T16" s="5"/>
+      <c r="T16" s="6"/>
       <c r="U16" s="2">
         <v>13</v>
       </c>
@@ -1536,15 +1536,15 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>83</v>
       </c>
       <c r="I17" s="2">
@@ -1553,8 +1553,8 @@
       <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1566,8 +1566,8 @@
       <c r="R17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S17" s="6"/>
-      <c r="T17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="6"/>
       <c r="U17" s="2">
         <v>14</v>
       </c>
@@ -1581,25 +1581,25 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="6"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="5"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1611,8 +1611,8 @@
       <c r="R18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S18" s="6"/>
-      <c r="T18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="6"/>
       <c r="U18" s="2">
         <v>15</v>
       </c>
@@ -1626,25 +1626,25 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="5"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="L19" s="5"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1656,10 +1656,10 @@
       <c r="R19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="S19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="T19" s="6"/>
       <c r="U19" s="2">
         <v>16</v>
       </c>
@@ -1673,15 +1673,15 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>84</v>
       </c>
       <c r="I20" s="2">
@@ -1690,8 +1690,8 @@
       <c r="J20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1703,8 +1703,8 @@
       <c r="R20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="S20" s="6"/>
-      <c r="T20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="6"/>
       <c r="U20" s="2">
         <v>17</v>
       </c>
@@ -1718,25 +1718,25 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="6"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="5"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1748,8 +1748,8 @@
       <c r="R21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="S21" s="6"/>
-      <c r="T21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="6"/>
       <c r="U21" s="2">
         <v>18</v>
       </c>
@@ -1763,15 +1763,15 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="5"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -1781,7 +1781,7 @@
       <c r="K22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="5"/>
+      <c r="L22" s="6"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="S22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="T22" s="5"/>
+      <c r="T22" s="6"/>
       <c r="U22" s="2">
         <v>19</v>
       </c>
@@ -1810,15 +1810,15 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>85</v>
       </c>
       <c r="I23" s="2">
@@ -1828,7 +1828,7 @@
         <v>73</v>
       </c>
       <c r="K23" s="8"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="6"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>73</v>
       </c>
       <c r="S23" s="8"/>
-      <c r="T23" s="5"/>
+      <c r="T23" s="6"/>
       <c r="U23" s="2">
         <v>20</v>
       </c>
@@ -1855,17 +1855,17 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="5"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>74</v>
       </c>
       <c r="K24" s="8"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="6"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>74</v>
       </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="5"/>
+      <c r="T24" s="6"/>
       <c r="U24" s="2">
         <v>21</v>
       </c>
@@ -1900,15 +1900,15 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="6"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="5"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>91</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="6"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>91</v>
       </c>
       <c r="S25" s="9"/>
-      <c r="T25" s="5"/>
+      <c r="T25" s="6"/>
       <c r="U25" s="2">
         <v>22</v>
       </c>
@@ -1943,15 +1943,15 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>86</v>
       </c>
       <c r="I26" s="2">
@@ -1963,7 +1963,7 @@
       <c r="K26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L26" s="5"/>
+      <c r="L26" s="6"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -1978,7 +1978,7 @@
       <c r="S26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="T26" s="5"/>
+      <c r="T26" s="6"/>
       <c r="U26" s="2">
         <v>23</v>
       </c>
@@ -1992,17 +1992,17 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="6"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="5"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>87</v>
       </c>
       <c r="K27" s="2"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="6"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>87</v>
       </c>
       <c r="S27" s="8"/>
-      <c r="T27" s="5"/>
+      <c r="T27" s="6"/>
       <c r="U27" s="2">
         <v>24</v>
       </c>
@@ -2037,15 +2037,15 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="5"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>88</v>
       </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="6"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>88</v>
       </c>
       <c r="S28" s="9"/>
-      <c r="T28" s="5"/>
+      <c r="T28" s="6"/>
       <c r="U28" s="2">
         <v>25</v>
       </c>
@@ -2080,15 +2080,15 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I29" s="2">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="6"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>93</v>
       </c>
       <c r="S29" s="2"/>
-      <c r="T29" s="5"/>
+      <c r="T29" s="6"/>
       <c r="U29" s="2">
         <v>26</v>
       </c>
@@ -2123,23 +2123,23 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="6"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="5"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="6"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>94</v>
       </c>
       <c r="S30" s="2"/>
-      <c r="T30" s="5"/>
+      <c r="T30" s="6"/>
       <c r="U30" s="2">
         <v>27</v>
       </c>
@@ -2166,21 +2166,21 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="5"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="6"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
-      <c r="T31" s="5"/>
+      <c r="T31" s="6"/>
       <c r="U31" s="2">
         <v>28</v>
       </c>
@@ -2205,21 +2205,21 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="5"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="6"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
-      <c r="T32" s="5"/>
+      <c r="T32" s="6"/>
       <c r="U32" s="2">
         <v>29</v>
       </c>
@@ -2247,14 +2247,14 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="6"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>90</v>
       </c>
       <c r="I33" s="2">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="6"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
-      <c r="T33" s="5"/>
+      <c r="T33" s="6"/>
       <c r="U33" s="2">
         <v>30</v>
       </c>
@@ -2287,23 +2287,23 @@
       <c r="B34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="6"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34" s="5"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="6"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
-      <c r="T34" s="5"/>
+      <c r="T34" s="6"/>
       <c r="U34" s="2">
         <v>31</v>
       </c>
@@ -2328,21 +2328,21 @@
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G35" s="5"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="6"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
-      <c r="T35" s="5"/>
+      <c r="T35" s="6"/>
       <c r="U35" s="2">
         <v>32</v>
       </c>
@@ -2540,6 +2540,51 @@
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:T35"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="S13:S15"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="S19:S21"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -2556,51 +2601,6 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:T35"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="S4:S6"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="S13:S15"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="S19:S21"/>
-    <mergeCell ref="S22:S25"/>
-    <mergeCell ref="S26:S28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAB2246-75B7-47DA-91FE-5F92C124CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66A770B-AE2F-4F93-A763-DD2557FD89C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -444,10 +444,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,68 +804,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="Q1" s="6" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="I2" s="6" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="Q2" s="6" t="s">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="Q2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6" t="s">
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -877,7 +877,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="6"/>
+      <c r="L3" s="5"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="S3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="5"/>
       <c r="U3" s="3" t="s">
         <v>0</v>
       </c>
@@ -933,17 +933,17 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="2">
@@ -952,10 +952,10 @@
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="6"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -967,10 +967,10 @@
       <c r="R4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="5"/>
       <c r="U4" s="2">
         <v>1</v>
       </c>
@@ -984,23 +984,23 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -1012,8 +1012,8 @@
       <c r="R5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="S5" s="5"/>
-      <c r="T5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="5"/>
       <c r="U5" s="2">
         <v>2</v>
       </c>
@@ -1027,8 +1027,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1044,8 +1044,8 @@
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -1057,8 +1057,8 @@
       <c r="R6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="S6" s="5"/>
-      <c r="T6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="5"/>
       <c r="U6" s="2">
         <v>3</v>
       </c>
@@ -1072,10 +1072,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1091,10 +1091,10 @@
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="6"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1106,10 +1106,10 @@
       <c r="R7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="S7" s="5" t="s">
+      <c r="S7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="5"/>
       <c r="U7" s="2">
         <v>4</v>
       </c>
@@ -1123,15 +1123,15 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="2">
@@ -1140,8 +1140,8 @@
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1153,8 +1153,8 @@
       <c r="R8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S8" s="5"/>
-      <c r="T8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="5"/>
       <c r="U8" s="2">
         <v>5</v>
       </c>
@@ -1168,23 +1168,23 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="5"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1196,8 +1196,8 @@
       <c r="R9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="S9" s="5"/>
-      <c r="T9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="5"/>
       <c r="U9" s="2">
         <v>6</v>
       </c>
@@ -1211,17 +1211,17 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="2">
@@ -1230,10 +1230,10 @@
       <c r="J10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="6"/>
+      <c r="L10" s="5"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1245,10 +1245,10 @@
       <c r="R10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S10" s="5" t="s">
+      <c r="S10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="T10" s="6"/>
+      <c r="T10" s="5"/>
       <c r="U10" s="2">
         <v>7</v>
       </c>
@@ -1262,23 +1262,23 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="5"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1290,8 +1290,8 @@
       <c r="R11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S11" s="5"/>
-      <c r="T11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="5"/>
       <c r="U11" s="2">
         <v>8</v>
       </c>
@@ -1305,15 +1305,15 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="2">
@@ -1322,8 +1322,8 @@
       <c r="J12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="5"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1335,8 +1335,8 @@
       <c r="R12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S12" s="5"/>
-      <c r="T12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="5"/>
       <c r="U12" s="2">
         <v>9</v>
       </c>
@@ -1350,27 +1350,27 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="6"/>
+      <c r="L13" s="5"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1382,10 +1382,10 @@
       <c r="R13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S13" s="5" t="s">
+      <c r="S13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="5"/>
       <c r="U13" s="2">
         <v>10</v>
       </c>
@@ -1399,15 +1399,15 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="2">
@@ -1416,8 +1416,8 @@
       <c r="J14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="5"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1429,8 +1429,8 @@
       <c r="R14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S14" s="5"/>
-      <c r="T14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="5"/>
       <c r="U14" s="2">
         <v>11</v>
       </c>
@@ -1444,25 +1444,25 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="5"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1474,8 +1474,8 @@
       <c r="R15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S15" s="5"/>
-      <c r="T15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="5"/>
       <c r="U15" s="2">
         <v>12</v>
       </c>
@@ -1489,25 +1489,25 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L16" s="6"/>
+      <c r="L16" s="5"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1519,10 +1519,10 @@
       <c r="R16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S16" s="5" t="s">
+      <c r="S16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="5"/>
       <c r="U16" s="2">
         <v>13</v>
       </c>
@@ -1536,15 +1536,15 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>83</v>
       </c>
       <c r="I17" s="2">
@@ -1553,8 +1553,8 @@
       <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="5"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1566,8 +1566,8 @@
       <c r="R17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S17" s="5"/>
-      <c r="T17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="5"/>
       <c r="U17" s="2">
         <v>14</v>
       </c>
@@ -1581,25 +1581,25 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="5"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1611,8 +1611,8 @@
       <c r="R18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S18" s="5"/>
-      <c r="T18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="5"/>
       <c r="U18" s="2">
         <v>15</v>
       </c>
@@ -1626,25 +1626,25 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="6"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="L19" s="6"/>
+      <c r="L19" s="5"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1656,10 +1656,10 @@
       <c r="R19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="S19" s="5" t="s">
+      <c r="S19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="5"/>
       <c r="U19" s="2">
         <v>16</v>
       </c>
@@ -1673,15 +1673,15 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I20" s="2">
@@ -1690,8 +1690,8 @@
       <c r="J20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="5"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1703,8 +1703,8 @@
       <c r="R20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="S20" s="5"/>
-      <c r="T20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="5"/>
       <c r="U20" s="2">
         <v>17</v>
       </c>
@@ -1718,25 +1718,25 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="6"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="5"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1748,8 +1748,8 @@
       <c r="R21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="S21" s="5"/>
-      <c r="T21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="5"/>
       <c r="U21" s="2">
         <v>18</v>
       </c>
@@ -1763,15 +1763,15 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="6"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -1781,7 +1781,7 @@
       <c r="K22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="6"/>
+      <c r="L22" s="5"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="S22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="5"/>
       <c r="U22" s="2">
         <v>19</v>
       </c>
@@ -1810,15 +1810,15 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>85</v>
       </c>
       <c r="I23" s="2">
@@ -1828,7 +1828,7 @@
         <v>73</v>
       </c>
       <c r="K23" s="8"/>
-      <c r="L23" s="6"/>
+      <c r="L23" s="5"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>73</v>
       </c>
       <c r="S23" s="8"/>
-      <c r="T23" s="6"/>
+      <c r="T23" s="5"/>
       <c r="U23" s="2">
         <v>20</v>
       </c>
@@ -1855,17 +1855,17 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="6"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>74</v>
       </c>
       <c r="K24" s="8"/>
-      <c r="L24" s="6"/>
+      <c r="L24" s="5"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>74</v>
       </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="6"/>
+      <c r="T24" s="5"/>
       <c r="U24" s="2">
         <v>21</v>
       </c>
@@ -1900,15 +1900,15 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25" s="6"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>91</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="6"/>
+      <c r="L25" s="5"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>91</v>
       </c>
       <c r="S25" s="9"/>
-      <c r="T25" s="6"/>
+      <c r="T25" s="5"/>
       <c r="U25" s="2">
         <v>22</v>
       </c>
@@ -1943,15 +1943,15 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="6" t="s">
         <v>86</v>
       </c>
       <c r="I26" s="2">
@@ -1963,7 +1963,7 @@
       <c r="K26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L26" s="6"/>
+      <c r="L26" s="5"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -1978,7 +1978,7 @@
       <c r="S26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="T26" s="6"/>
+      <c r="T26" s="5"/>
       <c r="U26" s="2">
         <v>23</v>
       </c>
@@ -1992,17 +1992,17 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="5"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27" s="6"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>87</v>
       </c>
       <c r="K27" s="2"/>
-      <c r="L27" s="6"/>
+      <c r="L27" s="5"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>87</v>
       </c>
       <c r="S27" s="8"/>
-      <c r="T27" s="6"/>
+      <c r="T27" s="5"/>
       <c r="U27" s="2">
         <v>24</v>
       </c>
@@ -2037,15 +2037,15 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="6"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>88</v>
       </c>
       <c r="K28" s="2"/>
-      <c r="L28" s="6"/>
+      <c r="L28" s="5"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>88</v>
       </c>
       <c r="S28" s="9"/>
-      <c r="T28" s="6"/>
+      <c r="T28" s="5"/>
       <c r="U28" s="2">
         <v>25</v>
       </c>
@@ -2080,15 +2080,15 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>79</v>
       </c>
       <c r="I29" s="2">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="6"/>
+      <c r="L29" s="5"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>93</v>
       </c>
       <c r="S29" s="2"/>
-      <c r="T29" s="6"/>
+      <c r="T29" s="5"/>
       <c r="U29" s="2">
         <v>26</v>
       </c>
@@ -2123,23 +2123,23 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="6"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="6"/>
+      <c r="L30" s="5"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>94</v>
       </c>
       <c r="S30" s="2"/>
-      <c r="T30" s="6"/>
+      <c r="T30" s="5"/>
       <c r="U30" s="2">
         <v>27</v>
       </c>
@@ -2166,21 +2166,21 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="5"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="5"/>
+      <c r="G31" s="6"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="6"/>
+      <c r="L31" s="5"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
-      <c r="T31" s="6"/>
+      <c r="T31" s="5"/>
       <c r="U31" s="2">
         <v>28</v>
       </c>
@@ -2205,21 +2205,21 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="5"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="6"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="6"/>
+      <c r="L32" s="5"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
-      <c r="T32" s="6"/>
+      <c r="T32" s="5"/>
       <c r="U32" s="2">
         <v>29</v>
       </c>
@@ -2247,14 +2247,14 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="6"/>
+      <c r="D33" s="5"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>90</v>
       </c>
       <c r="I33" s="2">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="6"/>
+      <c r="L33" s="5"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
-      <c r="T33" s="6"/>
+      <c r="T33" s="5"/>
       <c r="U33" s="2">
         <v>30</v>
       </c>
@@ -2287,23 +2287,23 @@
       <c r="B34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="5"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="5"/>
+      <c r="G34" s="6"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="6"/>
+      <c r="L34" s="5"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
-      <c r="T34" s="6"/>
+      <c r="T34" s="5"/>
       <c r="U34" s="2">
         <v>31</v>
       </c>
@@ -2328,21 +2328,21 @@
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="5"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="5"/>
+      <c r="G35" s="6"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="6"/>
+      <c r="L35" s="5"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
-      <c r="T35" s="6"/>
+      <c r="T35" s="5"/>
       <c r="U35" s="2">
         <v>32</v>
       </c>
@@ -2540,35 +2540,22 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:T35"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="S4:S6"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="S13:S15"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="S19:S21"/>
-    <mergeCell ref="S22:S25"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
@@ -2585,22 +2572,35 @@
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K7:K9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:T35"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="S10:S12"/>
+    <mergeCell ref="S13:S15"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="S19:S21"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="S26:S28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66A770B-AE2F-4F93-A763-DD2557FD89C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04921801-E03F-4A1A-9ADB-38A129F092AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="111">
   <si>
     <t>Freq:</t>
   </si>
@@ -194,15 +194,6 @@
     <t>FOVX</t>
   </si>
   <si>
-    <t>Gimbal FOV</t>
-  </si>
-  <si>
-    <t>Gimbal Pitch</t>
-  </si>
-  <si>
-    <t>Gimbal Pivot</t>
-  </si>
-  <si>
     <t>time since detected scan radars</t>
   </si>
   <si>
@@ -317,13 +308,67 @@
     <t>TSD</t>
   </si>
   <si>
-    <t>Zoom</t>
-  </si>
-  <si>
     <t>forward radar ang</t>
   </si>
   <si>
-    <t>gimbal controls (might be removed)</t>
+    <t>vel x</t>
+  </si>
+  <si>
+    <t>vel y</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> vel z</t>
+  </si>
+  <si>
+    <t>ang vel x</t>
+  </si>
+  <si>
+    <t>ang vel y</t>
+  </si>
+  <si>
+    <t>ang vel z</t>
+  </si>
+  <si>
+    <t>target x</t>
+  </si>
+  <si>
+    <t>target y</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> target z</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>phys sensor</t>
+  </si>
+  <si>
+    <t>TVC</t>
+  </si>
+  <si>
+    <t>Old radar tracking 0-1</t>
+  </si>
+  <si>
+    <t>tgt age</t>
+  </si>
+  <si>
+    <t>SOI</t>
+  </si>
+  <si>
+    <t>Sensor Of Interest</t>
+  </si>
+  <si>
+    <t>Manual Zoom button</t>
+  </si>
+  <si>
+    <t>Ticks since selected tgt detect</t>
+  </si>
+  <si>
+    <t>Zoom Key</t>
+  </si>
+  <si>
+    <t>Monitor Pressed</t>
   </si>
 </sst>
 </file>
@@ -346,7 +391,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,8 +410,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -426,11 +477,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -441,25 +529,40 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -776,98 +879,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:AF71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="6.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="1"/>
+    <col min="12" max="12" width="3.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
     <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
     <col min="16" max="16" width="9.140625" style="1"/>
     <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
     <col min="18" max="18" width="20.85546875" style="1" customWidth="1"/>
     <col min="19" max="19" width="17.5703125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" style="1"/>
+    <col min="20" max="20" width="3.42578125" style="1" customWidth="1"/>
     <col min="21" max="21" width="7.28515625" style="1" customWidth="1"/>
     <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
     <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="9.140625" style="1"/>
+    <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.42578125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="I1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="Q1" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-    </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="8"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="Q2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="8"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -877,7 +1006,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -887,6 +1016,7 @@
       <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="H3" s="10"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -896,7 +1026,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -906,129 +1036,135 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" s="5"/>
-      <c r="U3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="8"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="8"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="G4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="10"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="Q4" s="2">
-        <v>1</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="5"/>
-      <c r="U4" s="2">
-        <v>1</v>
-      </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P4" s="8"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="8"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="4"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="Q5" s="2">
-        <v>2</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S5" s="6"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="2">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="8"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="8"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1038,44 +1174,49 @@
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="H6" s="10"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="Q6" s="2">
-        <v>3</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="2">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="8"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1085,1159 +1226,1283 @@
       <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="H7" s="10"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="4"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="Q7" s="2">
-        <v>4</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="T7" s="5"/>
-      <c r="U7" s="2">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P7" s="8"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="8"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="4"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="Q8" s="2">
-        <v>5</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S8" s="6"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="2">
-        <v>5</v>
-      </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="8"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="4"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="Q9" s="2">
-        <v>6</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S9" s="6"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="2">
-        <v>6</v>
-      </c>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="8"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="8"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="10"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="4"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="Q10" s="2">
-        <v>7</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="T10" s="5"/>
-      <c r="U10" s="2">
-        <v>7</v>
-      </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="8"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="4"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="Q11" s="2">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S11" s="6"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="2">
-        <v>8</v>
-      </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="8"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="G12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="10"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="4"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="Q12" s="2">
-        <v>9</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="S12" s="6"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="2">
-        <v>9</v>
-      </c>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="8"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="8"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L13" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="Q13" s="2">
-        <v>10</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="T13" s="5"/>
-      <c r="U13" s="2">
-        <v>10</v>
-      </c>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P13" s="8"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="8"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="10"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="4"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="Q14" s="2">
-        <v>11</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="S14" s="6"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="2">
-        <v>11</v>
-      </c>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P14" s="8"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="8"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="6"/>
+      <c r="H15" s="10"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="4"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="Q15" s="2">
-        <v>12</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S15" s="6"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="2">
-        <v>12</v>
-      </c>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P15" s="8"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="8"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="6"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="L16" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="4"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="Q16" s="2">
-        <v>13</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="T16" s="5"/>
-      <c r="U16" s="2">
-        <v>13</v>
-      </c>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="8"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>83</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="4"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="Q17" s="2">
-        <v>14</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="S17" s="6"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="2">
-        <v>14</v>
-      </c>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P17" s="8"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
+      <c r="AF17" s="8"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="4"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="Q18" s="2">
-        <v>15</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S18" s="6"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="2">
-        <v>15</v>
-      </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P18" s="8"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="8"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="4"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="Q19" s="2">
-        <v>16</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="S19" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="T19" s="5"/>
-      <c r="U19" s="2">
-        <v>16</v>
-      </c>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P19" s="8"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="8"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="10"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="4"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="Q20" s="2">
-        <v>17</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="S20" s="6"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="2">
-        <v>17</v>
-      </c>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P20" s="8"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="8"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="4"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="4"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="Q21" s="2">
-        <v>18</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="S21" s="6"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="2">
-        <v>18</v>
-      </c>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="8"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="8"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="4"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="L22" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="4"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="Q22" s="2">
-        <v>19</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="T22" s="5"/>
-      <c r="U22" s="2">
-        <v>19</v>
-      </c>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="8"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="8"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="4"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="4"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="Q23" s="2">
-        <v>20</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S23" s="8"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="2">
-        <v>20</v>
-      </c>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="8"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="8"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="4"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="Q24" s="2">
-        <v>21</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="S24" s="8"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="2">
-        <v>21</v>
-      </c>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P24" s="8"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="8"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="4"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="Q25" s="2">
-        <v>22</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="2">
-        <v>22</v>
-      </c>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="8"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="10"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L26" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L26" s="4"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="Q26" s="2">
-        <v>23</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="T26" s="5"/>
-      <c r="U26" s="2">
-        <v>23</v>
-      </c>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P26" s="8"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+      <c r="AF26" s="8"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="4"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="Q27" s="2">
-        <v>24</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="S27" s="8"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="2">
-        <v>24</v>
-      </c>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="8"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="8"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" s="4"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="Q28" s="2">
-        <v>25</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="2">
-        <v>25</v>
-      </c>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="8"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="4"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="10"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
-      <c r="J29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="4"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="Q29" s="2">
-        <v>26</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="2">
-        <v>26</v>
-      </c>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P29" s="8"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="8"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="10"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
-      <c r="J30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="4"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="Q30" s="2">
-        <v>27</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="S30" s="2"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="2">
-        <v>27</v>
-      </c>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P30" s="8"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="8"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="4"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="Q31" s="2">
-        <v>28</v>
-      </c>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="2">
-        <v>28</v>
-      </c>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P31" s="8"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="8"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="10"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="5"/>
+      <c r="J32" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L32" s="4"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="Q32" s="2">
-        <v>29</v>
-      </c>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="2">
-        <v>29</v>
-      </c>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P32" s="8"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="8"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
+      <c r="AF32" s="8"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2247,299 +2512,1246 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="10"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
-      <c r="J33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="4"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="Q33" s="2">
-        <v>30</v>
-      </c>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="2">
-        <v>30</v>
-      </c>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P33" s="8"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="8"/>
+    </row>
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="10"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="4"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="Q34" s="2">
-        <v>31</v>
-      </c>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="2">
-        <v>31</v>
-      </c>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P34" s="8"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="8"/>
+    </row>
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="10"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="4"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="Q35" s="2">
+      <c r="P35" s="8"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="8"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="9"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="4"/>
+      <c r="M39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="9"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="2">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>2</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="2">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="5"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="2">
+        <v>2</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>3</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="2">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="2">
+        <v>3</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="2">
+        <v>3</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>4</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="2">
+        <v>4</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="2">
+        <v>4</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="2">
+        <v>4</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="2">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="2">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="2">
+        <v>5</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="2">
+        <v>6</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="2">
+        <v>6</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K45" s="5"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="2">
+        <v>6</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="2">
+        <v>7</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="2">
+        <v>7</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K46" s="5"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="2">
+        <v>7</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="2">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="2">
+        <v>8</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K47" s="5"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="2">
+        <v>8</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="2">
+        <v>9</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="2">
+        <v>9</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K48" s="5"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="2">
+        <v>9</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>10</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="2">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="2">
+        <v>10</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="2">
+        <v>10</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>11</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="2">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="2">
+        <v>11</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K50" s="5"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="2">
+        <v>11</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>12</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="2">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="2">
+        <v>12</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K51" s="5"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="2">
+        <v>12</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>13</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="2">
+        <v>13</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="2">
+        <v>13</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L52" s="4"/>
+      <c r="M52" s="2">
+        <v>13</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>14</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="2">
+        <v>14</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="2">
+        <v>14</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K53" s="5"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="2">
+        <v>14</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>15</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="2">
+        <v>15</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="2">
+        <v>15</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="2">
+        <v>15</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>16</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="2">
+        <v>16</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="2">
+        <v>16</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L55" s="4"/>
+      <c r="M55" s="2">
+        <v>16</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>17</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="2">
+        <v>17</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="2">
+        <v>17</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="2">
+        <v>17</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>18</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="2">
+        <v>18</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="2">
+        <v>18</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="2">
+        <v>18</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>19</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="2">
+        <v>19</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="2">
+        <v>19</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L58" s="4"/>
+      <c r="M58" s="2">
+        <v>19</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>20</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="2">
+        <v>20</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="2">
+        <v>20</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>21</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="2">
+        <v>21</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="2">
+        <v>21</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>22</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="2">
+        <v>22</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="2">
+        <v>22</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="2">
+        <v>22</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>23</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="2">
+        <v>23</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="2">
+        <v>23</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="2">
+        <v>23</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>24</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="2">
+        <v>24</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="2">
+        <v>24</v>
+      </c>
+      <c r="J63" s="2"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="2">
+        <v>24</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>25</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="2">
+        <v>25</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="2">
+        <v>25</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="2">
+        <v>25</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>26</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="2">
+        <v>26</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="2">
+        <v>26</v>
+      </c>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="2">
+        <v>26</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>27</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="2">
+        <v>27</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="2">
+        <v>27</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="2">
+        <v>27</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>28</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="2">
+        <v>28</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="2">
+        <v>28</v>
+      </c>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="2">
+        <v>28</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>29</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="2">
+        <v>29</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="2">
+        <v>29</v>
+      </c>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="2">
+        <v>29</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>30</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="2">
+        <v>30</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="2">
+        <v>30</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="2">
+        <v>30</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>31</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="2">
+        <v>31</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="2">
+        <v>31</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="2">
+        <v>31</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
         <v>32</v>
       </c>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="2">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="2">
         <v>32</v>
       </c>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="G41" s="4"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C46" s="4"/>
-      <c r="D46" s="10"/>
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C47" s="4"/>
-      <c r="D47" s="10"/>
-      <c r="G47" s="4"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C48" s="4"/>
-      <c r="D48" s="10"/>
-      <c r="G48" s="10"/>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C49" s="4"/>
-      <c r="D49" s="10"/>
-      <c r="G49" s="10"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C50" s="4"/>
-      <c r="D50" s="10"/>
-      <c r="G50" s="4"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C51" s="4"/>
-      <c r="D51" s="10"/>
-      <c r="G51" s="4"/>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C52" s="4"/>
-      <c r="D52" s="10"/>
-      <c r="G52" s="4"/>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C53" s="4"/>
-      <c r="D53" s="10"/>
-      <c r="G53" s="10"/>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="G54" s="10"/>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="G55" s="10"/>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="G56" s="10"/>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="G57" s="10"/>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="G58" s="10"/>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="G59" s="4"/>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C60" s="4"/>
-      <c r="D60" s="10"/>
-      <c r="G60" s="4"/>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C61" s="4"/>
-      <c r="D61" s="10"/>
-      <c r="G61" s="4"/>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C62" s="4"/>
-      <c r="D62" s="10"/>
-      <c r="G62" s="4"/>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="G63" s="4"/>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="G64" s="4"/>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="G65" s="4"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C66" s="4"/>
-      <c r="D66" s="10"/>
-      <c r="G66" s="4"/>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="4"/>
-      <c r="D67" s="10"/>
-      <c r="G67" s="4"/>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C68" s="4"/>
-      <c r="D68" s="10"/>
-      <c r="G68" s="4"/>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="D69" s="10"/>
-      <c r="G69" s="4"/>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C70" s="4"/>
-      <c r="D70" s="10"/>
-      <c r="G70" s="4"/>
-    </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C71" s="4"/>
-      <c r="D71" s="10"/>
-      <c r="G71" s="4"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="2">
+        <v>32</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="2">
+        <v>32</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="60">
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="X1:X35"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C4:C6"/>
@@ -2556,51 +3768,38 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K10:K12"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:T35"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="S4:S6"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="S10:S12"/>
-    <mergeCell ref="S13:S15"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="S19:S21"/>
-    <mergeCell ref="S22:S25"/>
-    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K26:K28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04921801-E03F-4A1A-9ADB-38A129F092AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CD0B7C-690D-4730-A739-9D77EDC80CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="121">
   <si>
     <t>Freq:</t>
   </si>
@@ -369,13 +369,43 @@
   </si>
   <si>
     <t>Monitor Pressed</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>rear</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>middle</t>
+  </si>
+  <si>
+    <t>bool 1</t>
+  </si>
+  <si>
+    <t>bool 2</t>
+  </si>
+  <si>
+    <t>bool 3</t>
+  </si>
+  <si>
+    <t>bool 4</t>
+  </si>
+  <si>
+    <t>number out</t>
+  </si>
+  <si>
+    <t>RWR Shit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +416,20 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -518,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -529,25 +573,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,8 +594,26 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,10 +949,10 @@
     <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
     <col min="16" max="16" width="9.140625" style="1"/>
     <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.85546875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5703125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="3.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12" style="1" customWidth="1"/>
     <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
     <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
     <col min="24" max="24" width="9.140625" style="1"/>
@@ -916,85 +966,76 @@
     <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="4" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="8"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="X1" s="17"/>
+      <c r="AF1" s="5"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="4" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="8"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="X2" s="17"/>
+      <c r="AF2" s="5"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1006,7 +1047,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1016,7 +1057,7 @@
       <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="10"/>
+      <c r="H3" s="14"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1067,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="13"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1036,23 +1077,24 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="8"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" s="17"/>
+      <c r="AF3" s="5"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1061,52 +1103,53 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="14"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="8"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
+        <v>1</v>
+      </c>
+      <c r="X4" s="17"/>
+      <c r="AF4" s="5"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1115,46 +1158,47 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="10"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="14"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="13"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="8"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>2</v>
+      </c>
+      <c r="X5" s="17"/>
+      <c r="AF5" s="5"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1163,8 +1207,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1174,37 +1218,38 @@
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="14"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="13"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="8"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
+        <v>3</v>
+      </c>
+      <c r="X6" s="17"/>
+      <c r="AF6" s="5"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1213,10 +1258,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1226,39 +1271,40 @@
       <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="10"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="13"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="8"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>4</v>
+      </c>
+      <c r="X7" s="17"/>
+      <c r="AF7" s="5"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1267,48 +1313,49 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="14"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="4"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="8"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1">
+        <v>5</v>
+      </c>
+      <c r="X8" s="17"/>
+      <c r="AF8" s="5"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1317,46 +1364,47 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="4"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="8"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>6</v>
+      </c>
+      <c r="X9" s="17"/>
+      <c r="AF9" s="5"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1365,52 +1413,53 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="4"/>
+      <c r="L10" s="13"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="9"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="8"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1">
+        <v>7</v>
+      </c>
+      <c r="X10" s="17"/>
+      <c r="AF10" s="5"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1419,46 +1468,47 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="4"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="8"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>8</v>
+      </c>
+      <c r="X11" s="17"/>
+      <c r="AF11" s="5"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1467,48 +1517,49 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="4"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="8"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1">
+        <v>9</v>
+      </c>
+      <c r="X12" s="17"/>
+      <c r="AF12" s="5"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1517,50 +1568,51 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="13"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="8"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>10</v>
+      </c>
+      <c r="X13" s="17"/>
+      <c r="AF13" s="5"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1569,8 +1621,8 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1580,37 +1632,38 @@
       <c r="G14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="4"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="8"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" s="1">
+        <v>11</v>
+      </c>
+      <c r="X14" s="17"/>
+      <c r="AF14" s="5"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1619,44 +1672,45 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="4"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="8"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>12</v>
+      </c>
+      <c r="X15" s="17"/>
+      <c r="AF15" s="5"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1665,46 +1719,47 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="10"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="4"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="8"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" s="1">
+        <v>13</v>
+      </c>
+      <c r="X16" s="17"/>
+      <c r="AF16" s="5"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1713,48 +1768,49 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="4"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="13"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="14"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="4"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-      <c r="AC17" s="9"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
-      <c r="AF17" s="8"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>14</v>
+      </c>
+      <c r="X17" s="17"/>
+      <c r="AF17" s="5"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1763,48 +1819,49 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="13"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="14"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="4"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="8"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" s="1">
+        <v>15</v>
+      </c>
+      <c r="X18" s="17"/>
+      <c r="AF18" s="5"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1813,48 +1870,49 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="4"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="13"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="14"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="L19" s="4"/>
+      <c r="L19" s="13"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="8"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
+        <v>16</v>
+      </c>
+      <c r="X19" s="17"/>
+      <c r="AF19" s="5"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1863,48 +1921,34 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="10"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="4"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="8"/>
+      <c r="P20" s="5"/>
+      <c r="X20" s="17"/>
+      <c r="AF20" s="5"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1913,48 +1957,34 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="13"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="4"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="8"/>
+      <c r="P21" s="5"/>
+      <c r="X21" s="17"/>
+      <c r="AF21" s="5"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1963,48 +1993,34 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="13"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L22" s="4"/>
+      <c r="L22" s="13"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="8"/>
+      <c r="P22" s="5"/>
+      <c r="X22" s="17"/>
+      <c r="AF22" s="5"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2013,48 +2029,34 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="13"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="14"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="4"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="8"/>
+      <c r="P23" s="5"/>
+      <c r="X23" s="17"/>
+      <c r="AF23" s="5"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2063,48 +2065,34 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="13"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="10"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="4"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="9"/>
-      <c r="AD24" s="9"/>
-      <c r="AE24" s="9"/>
-      <c r="AF24" s="8"/>
+      <c r="P24" s="5"/>
+      <c r="X24" s="17"/>
+      <c r="AF24" s="5"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2113,46 +2101,32 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="13"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="10"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="4"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="9"/>
-      <c r="AF25" s="8"/>
+      <c r="P25" s="5"/>
+      <c r="X25" s="17"/>
+      <c r="AF25" s="5"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2161,50 +2135,36 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H26" s="10"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L26" s="4"/>
+      <c r="L26" s="13"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-      <c r="AF26" s="8"/>
+      <c r="P26" s="5"/>
+      <c r="X26" s="17"/>
+      <c r="AF26" s="5"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2213,48 +2173,34 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="10"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="4"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="9"/>
-      <c r="AF27" s="8"/>
+      <c r="P27" s="5"/>
+      <c r="X27" s="17"/>
+      <c r="AF27" s="5"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2263,46 +2209,32 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="10"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="14"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="4"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-      <c r="AF28" s="8"/>
+      <c r="P28" s="5"/>
+      <c r="X28" s="17"/>
+      <c r="AF28" s="5"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -2311,18 +2243,18 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="10"/>
+      <c r="H29" s="14"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2330,29 +2262,15 @@
         <v>109</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="4"/>
+      <c r="L29" s="13"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="9"/>
-      <c r="AD29" s="9"/>
-      <c r="AE29" s="9"/>
-      <c r="AF29" s="8"/>
+      <c r="P29" s="5"/>
+      <c r="X29" s="17"/>
+      <c r="AF29" s="5"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2361,18 +2279,18 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="10"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="14"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2380,29 +2298,15 @@
         <v>90</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="4"/>
+      <c r="L30" s="13"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="9"/>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="8"/>
+      <c r="P30" s="5"/>
+      <c r="X30" s="17"/>
+      <c r="AF30" s="5"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2411,16 +2315,16 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="13"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="10"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2428,29 +2332,15 @@
         <v>103</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="4"/>
+      <c r="L31" s="13"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
-      <c r="AC31" s="9"/>
-      <c r="AD31" s="9"/>
-      <c r="AE31" s="9"/>
-      <c r="AF31" s="8"/>
+      <c r="P31" s="5"/>
+      <c r="X31" s="17"/>
+      <c r="AF31" s="5"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2459,16 +2349,16 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="4"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="10"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="14"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2478,29 +2368,15 @@
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L32" s="4"/>
+      <c r="L32" s="13"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
-      <c r="AB32" s="9"/>
-      <c r="AC32" s="9"/>
-      <c r="AD32" s="9"/>
-      <c r="AE32" s="9"/>
-      <c r="AF32" s="8"/>
+      <c r="P32" s="5"/>
+      <c r="X32" s="17"/>
+      <c r="AF32" s="5"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2512,17 +2388,17 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="13"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H33" s="10"/>
+      <c r="H33" s="14"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2530,29 +2406,15 @@
         <v>110</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="4"/>
+      <c r="L33" s="13"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="9"/>
-      <c r="AE33" s="9"/>
-      <c r="AF33" s="8"/>
+      <c r="P33" s="5"/>
+      <c r="X33" s="17"/>
+      <c r="AF33" s="5"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2561,46 +2423,34 @@
       <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="13"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="10"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="4"/>
+      <c r="L34" s="13"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="9"/>
-      <c r="AE34" s="9"/>
-      <c r="AF34" s="8"/>
+      <c r="P34" s="5"/>
+      <c r="X34" s="17"/>
+      <c r="AF34" s="5"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2609,158 +2459,93 @@
       <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="4"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="10"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="4"/>
+      <c r="L35" s="13"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="9"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
-      <c r="AD35" s="9"/>
-      <c r="AE35" s="9"/>
-      <c r="AF35" s="8"/>
+      <c r="P35" s="5"/>
+      <c r="X35" s="17"/>
+      <c r="AF35" s="5"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="9"/>
-      <c r="AE36" s="9"/>
-      <c r="AF36" s="9"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="9"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="4" t="s">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-      <c r="AA37" s="9"/>
-      <c r="AB37" s="9"/>
-      <c r="AC37" s="9"/>
-      <c r="AD37" s="9"/>
-      <c r="AE37" s="9"/>
-      <c r="AF37" s="9"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4" t="s">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="4" t="s">
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="9"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="9"/>
-      <c r="AE38" s="9"/>
-      <c r="AF38" s="9"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2772,7 +2557,7 @@
       <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="D39" s="13"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2782,7 +2567,7 @@
       <c r="G39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="7"/>
+      <c r="H39" s="11"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2792,7 +2577,7 @@
       <c r="K39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L39" s="4"/>
+      <c r="L39" s="13"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2802,23 +2587,6 @@
       <c r="O39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="9"/>
-      <c r="AE39" s="9"/>
-      <c r="AF39" s="9"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -2827,26 +2595,26 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="13"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="7"/>
+      <c r="H40" s="11"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="L40" s="4"/>
+      <c r="L40" s="13"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2860,22 +2628,22 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="4"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="13"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="7"/>
+      <c r="H41" s="11"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="4"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2889,22 +2657,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="4"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="13"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="7"/>
+      <c r="H42" s="11"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="4"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2918,24 +2686,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="4"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="7"/>
+      <c r="H43" s="11"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="4"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2949,22 +2717,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="4"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="13"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="7"/>
+      <c r="H44" s="11"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="4"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2978,22 +2746,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="4"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="7"/>
+      <c r="H45" s="11"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="4"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -3007,24 +2775,24 @@
       <c r="B46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="4"/>
+      <c r="D46" s="13"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="7"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="4"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -3038,22 +2806,22 @@
       <c r="B47" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="4"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="13"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="7"/>
+      <c r="H47" s="11"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="4"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -3067,22 +2835,22 @@
       <c r="B48" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="4"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="13"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="7"/>
+      <c r="H48" s="11"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="4"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -3096,24 +2864,24 @@
       <c r="B49" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="4"/>
+      <c r="D49" s="13"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="7"/>
+      <c r="H49" s="11"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="4"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -3127,22 +2895,22 @@
       <c r="B50" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="4"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="13"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="7"/>
+      <c r="H50" s="11"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="4"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -3156,22 +2924,22 @@
       <c r="B51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="4"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="13"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="7"/>
+      <c r="H51" s="11"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="4"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -3185,26 +2953,26 @@
       <c r="B52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="4"/>
+      <c r="D52" s="13"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="7"/>
+      <c r="H52" s="11"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K52" s="5" t="s">
+      <c r="K52" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L52" s="4"/>
+      <c r="L52" s="13"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -3218,22 +2986,22 @@
       <c r="B53" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="4"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="13"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="7"/>
+      <c r="H53" s="11"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="4"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -3247,22 +3015,22 @@
       <c r="B54" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="4"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="13"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="7"/>
+      <c r="H54" s="11"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="K54" s="5"/>
-      <c r="L54" s="4"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3276,16 +3044,16 @@
       <c r="B55" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="4"/>
+      <c r="D55" s="13"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="7"/>
+      <c r="H55" s="11"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3295,7 +3063,7 @@
       <c r="K55" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L55" s="4"/>
+      <c r="L55" s="13"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3309,22 +3077,22 @@
       <c r="B56" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="4"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="7"/>
+      <c r="H56" s="11"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K56" s="6"/>
-      <c r="L56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="13"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3338,22 +3106,22 @@
       <c r="B57" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="4"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="7"/>
+      <c r="H57" s="11"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K57" s="6"/>
-      <c r="L57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="13"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3367,16 +3135,16 @@
       <c r="B58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="4"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="7"/>
+      <c r="H58" s="11"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3386,7 +3154,7 @@
       <c r="K58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L58" s="4"/>
+      <c r="L58" s="13"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3400,22 +3168,22 @@
       <c r="B59" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="4"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="7"/>
+      <c r="H59" s="11"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K59" s="6"/>
-      <c r="L59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="13"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3429,20 +3197,20 @@
       <c r="B60" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="4"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="7"/>
+      <c r="H60" s="11"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="13"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3456,20 +3224,20 @@
       <c r="B61" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="4"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="7"/>
+      <c r="H61" s="11"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="13"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3486,19 +3254,19 @@
       <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="4"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="7"/>
+      <c r="H62" s="11"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="13"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3513,19 +3281,19 @@
         <v>84</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="4"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="7"/>
+      <c r="H63" s="11"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="13"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3540,19 +3308,19 @@
         <v>85</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="4"/>
+      <c r="D64" s="13"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="7"/>
+      <c r="H64" s="11"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="13"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3569,19 +3337,19 @@
       <c r="C65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="4"/>
+      <c r="D65" s="13"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="7"/>
+      <c r="H65" s="11"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="4"/>
+      <c r="L65" s="13"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3592,21 +3360,23 @@
       <c r="A66" s="2">
         <v>27</v>
       </c>
-      <c r="B66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="4"/>
+      <c r="D66" s="13"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="7"/>
+      <c r="H66" s="11"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="4"/>
+      <c r="L66" s="13"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3619,19 +3389,19 @@
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="4"/>
+      <c r="D67" s="13"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="7"/>
+      <c r="H67" s="11"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="4"/>
+      <c r="L67" s="13"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3644,19 +3414,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="4"/>
+      <c r="D68" s="13"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="7"/>
+      <c r="H68" s="11"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="4"/>
+      <c r="L68" s="13"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3669,19 +3439,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="4"/>
+      <c r="D69" s="13"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="7"/>
+      <c r="H69" s="11"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="4"/>
+      <c r="L69" s="13"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3694,19 +3464,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="4"/>
+      <c r="D70" s="13"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="7"/>
+      <c r="H70" s="11"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="4"/>
+      <c r="L70" s="13"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3719,19 +3489,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="4"/>
+      <c r="D71" s="13"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="15"/>
+      <c r="H71" s="12"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="4"/>
+      <c r="L71" s="13"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3740,34 +3510,23 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="X1:X35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K26:K28"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="D38:D71"/>
@@ -3784,22 +3543,33 @@
     <mergeCell ref="C40:C42"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CD0B7C-690D-4730-A739-9D77EDC80CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64F8E07-AE90-466C-91F2-FB95F6DDF4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -576,10 +576,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -600,20 +612,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,61 +967,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="13" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="X1" s="17"/>
-      <c r="AF1" s="5"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="X1" s="7"/>
+      <c r="AF1" s="8"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="13" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="5"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8"/>
       <c r="Q2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1034,8 +1034,8 @@
       <c r="T2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="X2" s="17"/>
-      <c r="AF2" s="5"/>
+      <c r="X2" s="7"/>
+      <c r="AF2" s="8"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1047,7 +1047,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +1057,7 @@
       <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="17"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="13"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="5"/>
+      <c r="P3" s="8"/>
       <c r="Q3" s="1" t="s">
         <v>115</v>
       </c>
@@ -1093,8 +1093,8 @@
       <c r="U3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="X3" s="17"/>
-      <c r="AF3" s="5"/>
+      <c r="X3" s="7"/>
+      <c r="AF3" s="8"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1103,53 +1103,53 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" s="15" t="b">
+      <c r="P4" s="8"/>
+      <c r="Q4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="X4" s="17"/>
-      <c r="AF4" s="5"/>
+      <c r="X4" s="7"/>
+      <c r="AF4" s="8"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1158,47 +1158,47 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="14"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="13"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" s="16" t="b">
+      <c r="P5" s="8"/>
+      <c r="Q5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U5" s="1">
         <v>2</v>
       </c>
-      <c r="X5" s="17"/>
-      <c r="AF5" s="5"/>
+      <c r="X5" s="7"/>
+      <c r="AF5" s="8"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1207,8 +1207,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="13"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1218,38 +1218,38 @@
       <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="13"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" s="15" t="b">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="X6" s="17"/>
-      <c r="AF6" s="5"/>
+      <c r="X6" s="7"/>
+      <c r="AF6" s="8"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1258,10 +1258,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1271,40 +1271,40 @@
       <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="17"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="13"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" s="16" t="b">
+      <c r="P7" s="8"/>
+      <c r="Q7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U7" s="1">
         <v>4</v>
       </c>
-      <c r="X7" s="17"/>
-      <c r="AF7" s="5"/>
+      <c r="X7" s="7"/>
+      <c r="AF7" s="8"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1313,49 +1313,49 @@
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="13"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T8" s="15" t="b">
+      <c r="P8" s="8"/>
+      <c r="Q8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U8" s="1">
         <v>5</v>
       </c>
-      <c r="X8" s="17"/>
-      <c r="AF8" s="5"/>
+      <c r="X8" s="7"/>
+      <c r="AF8" s="8"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1364,47 +1364,47 @@
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="13"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="14"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="17"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" s="16" t="b">
+      <c r="P9" s="8"/>
+      <c r="Q9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U9" s="1">
         <v>6</v>
       </c>
-      <c r="X9" s="17"/>
-      <c r="AF9" s="5"/>
+      <c r="X9" s="7"/>
+      <c r="AF9" s="8"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1413,53 +1413,53 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="14"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="13"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="15" t="b">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U10" s="1">
         <v>7</v>
       </c>
-      <c r="X10" s="17"/>
-      <c r="AF10" s="5"/>
+      <c r="X10" s="7"/>
+      <c r="AF10" s="8"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1468,47 +1468,47 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="13"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="14"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="17"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" s="16" t="b">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U11" s="1">
         <v>8</v>
       </c>
-      <c r="X11" s="17"/>
-      <c r="AF11" s="5"/>
+      <c r="X11" s="7"/>
+      <c r="AF11" s="8"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1517,49 +1517,49 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="13"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="17"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T12" s="15" t="b">
+      <c r="P12" s="8"/>
+      <c r="Q12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U12" s="1">
         <v>9</v>
       </c>
-      <c r="X12" s="17"/>
-      <c r="AF12" s="5"/>
+      <c r="X12" s="7"/>
+      <c r="AF12" s="8"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1568,51 +1568,51 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="14"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="13"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" s="16" t="b">
+      <c r="P13" s="8"/>
+      <c r="Q13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U13" s="1">
         <v>10</v>
       </c>
-      <c r="X13" s="17"/>
-      <c r="AF13" s="5"/>
+      <c r="X13" s="7"/>
+      <c r="AF13" s="8"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1621,8 +1621,8 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1632,38 +1632,38 @@
       <c r="G14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="17"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S14" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="15" t="b">
+      <c r="P14" s="8"/>
+      <c r="Q14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U14" s="1">
         <v>11</v>
       </c>
-      <c r="X14" s="17"/>
-      <c r="AF14" s="5"/>
+      <c r="X14" s="7"/>
+      <c r="AF14" s="8"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1672,45 +1672,45 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="13"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="S15" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" s="16" t="b">
+      <c r="P15" s="8"/>
+      <c r="Q15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U15" s="1">
         <v>12</v>
       </c>
-      <c r="X15" s="17"/>
-      <c r="AF15" s="5"/>
+      <c r="X15" s="7"/>
+      <c r="AF15" s="8"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1719,47 +1719,47 @@
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="13"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="14"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="13"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T16" s="15" t="b">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U16" s="1">
         <v>13</v>
       </c>
-      <c r="X16" s="17"/>
-      <c r="AF16" s="5"/>
+      <c r="X16" s="7"/>
+      <c r="AF16" s="8"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1768,49 +1768,49 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="13"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T17" s="16" t="b">
+      <c r="P17" s="8"/>
+      <c r="Q17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="X17" s="17"/>
-      <c r="AF17" s="5"/>
+      <c r="X17" s="7"/>
+      <c r="AF17" s="8"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1819,49 +1819,49 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="14"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="13"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" s="15" t="b">
+      <c r="P18" s="8"/>
+      <c r="Q18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="X18" s="17"/>
-      <c r="AF18" s="5"/>
+      <c r="X18" s="7"/>
+      <c r="AF18" s="8"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1870,49 +1870,49 @@
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="14"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="L19" s="13"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" s="16" t="b">
+      <c r="P19" s="8"/>
+      <c r="Q19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="b">
         <v>0</v>
       </c>
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="X19" s="17"/>
-      <c r="AF19" s="5"/>
+      <c r="X19" s="7"/>
+      <c r="AF19" s="8"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1921,34 +1921,34 @@
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="13"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="13"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="5"/>
-      <c r="X20" s="17"/>
-      <c r="AF20" s="5"/>
+      <c r="P20" s="8"/>
+      <c r="X20" s="7"/>
+      <c r="AF20" s="8"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1957,34 +1957,34 @@
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="14"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="13"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="5"/>
-      <c r="X21" s="17"/>
-      <c r="AF21" s="5"/>
+      <c r="P21" s="8"/>
+      <c r="X21" s="7"/>
+      <c r="AF21" s="8"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1993,34 +1993,34 @@
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="13"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="14"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L22" s="13"/>
+      <c r="L22" s="10"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="5"/>
-      <c r="X22" s="17"/>
-      <c r="AF22" s="5"/>
+      <c r="P22" s="8"/>
+      <c r="X22" s="7"/>
+      <c r="AF22" s="8"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2029,34 +2029,34 @@
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="13"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="10"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="5"/>
-      <c r="X23" s="17"/>
-      <c r="AF23" s="5"/>
+      <c r="P23" s="8"/>
+      <c r="X23" s="7"/>
+      <c r="AF23" s="8"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2065,34 +2065,34 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="13"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="14"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="13"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="10"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="5"/>
-      <c r="X24" s="17"/>
-      <c r="AF24" s="5"/>
+      <c r="P24" s="8"/>
+      <c r="X24" s="7"/>
+      <c r="AF24" s="8"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2101,32 +2101,32 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="13"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="14"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K25" s="6"/>
-      <c r="L25" s="13"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="10"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="5"/>
-      <c r="X25" s="17"/>
-      <c r="AF25" s="5"/>
+      <c r="P25" s="8"/>
+      <c r="X25" s="7"/>
+      <c r="AF25" s="8"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2135,36 +2135,36 @@
       <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H26" s="14"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L26" s="13"/>
+      <c r="L26" s="10"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="5"/>
-      <c r="X26" s="17"/>
-      <c r="AF26" s="5"/>
+      <c r="P26" s="8"/>
+      <c r="X26" s="7"/>
+      <c r="AF26" s="8"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2173,34 +2173,34 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="13"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="14"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="13"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="10"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="5"/>
-      <c r="X27" s="17"/>
-      <c r="AF27" s="5"/>
+      <c r="P27" s="8"/>
+      <c r="X27" s="7"/>
+      <c r="AF27" s="8"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2209,32 +2209,32 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="14"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="13"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="10"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="5"/>
-      <c r="X28" s="17"/>
-      <c r="AF28" s="5"/>
+      <c r="P28" s="8"/>
+      <c r="X28" s="7"/>
+      <c r="AF28" s="8"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -2243,18 +2243,18 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="13"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="17"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2262,15 +2262,15 @@
         <v>109</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="13"/>
+      <c r="L29" s="10"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="5"/>
-      <c r="X29" s="17"/>
-      <c r="AF29" s="5"/>
+      <c r="P29" s="8"/>
+      <c r="X29" s="7"/>
+      <c r="AF29" s="8"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2279,18 +2279,18 @@
       <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="13"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="14"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="17"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2298,15 +2298,15 @@
         <v>90</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="13"/>
+      <c r="L30" s="10"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="5"/>
-      <c r="X30" s="17"/>
-      <c r="AF30" s="5"/>
+      <c r="P30" s="8"/>
+      <c r="X30" s="7"/>
+      <c r="AF30" s="8"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2315,16 +2315,16 @@
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="13"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="14"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="17"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2332,15 +2332,15 @@
         <v>103</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="13"/>
+      <c r="L31" s="10"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="5"/>
-      <c r="X31" s="17"/>
-      <c r="AF31" s="5"/>
+      <c r="P31" s="8"/>
+      <c r="X31" s="7"/>
+      <c r="AF31" s="8"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2349,16 +2349,16 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="14"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="17"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2368,15 +2368,15 @@
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L32" s="13"/>
+      <c r="L32" s="10"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="5"/>
-      <c r="X32" s="17"/>
-      <c r="AF32" s="5"/>
+      <c r="P32" s="8"/>
+      <c r="X32" s="7"/>
+      <c r="AF32" s="8"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2388,17 +2388,17 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="13"/>
+      <c r="D33" s="10"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H33" s="14"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2406,15 +2406,15 @@
         <v>110</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="13"/>
+      <c r="L33" s="10"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="5"/>
-      <c r="X33" s="17"/>
-      <c r="AF33" s="5"/>
+      <c r="P33" s="8"/>
+      <c r="X33" s="7"/>
+      <c r="AF33" s="8"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2423,18 +2423,18 @@
       <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="13"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="14"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="17"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2442,15 +2442,15 @@
         <v>120</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="13"/>
+      <c r="L34" s="10"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="5"/>
-      <c r="X34" s="17"/>
-      <c r="AF34" s="5"/>
+      <c r="P34" s="8"/>
+      <c r="X34" s="7"/>
+      <c r="AF34" s="8"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2459,93 +2459,93 @@
       <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="14"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="17"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="13"/>
+      <c r="L35" s="10"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="5"/>
-      <c r="X35" s="17"/>
-      <c r="AF35" s="5"/>
+      <c r="P35" s="8"/>
+      <c r="X35" s="7"/>
+      <c r="AF35" s="8"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="9"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="13"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="13" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="13" t="s">
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13" t="s">
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2557,7 +2557,7 @@
       <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="13"/>
+      <c r="D39" s="10"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2567,7 +2567,7 @@
       <c r="G39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="15"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="K39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L39" s="13"/>
+      <c r="L39" s="10"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2595,26 +2595,26 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="13"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="11"/>
+      <c r="H40" s="15"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="L40" s="13"/>
+      <c r="L40" s="10"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2628,22 +2628,22 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="13"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="11"/>
+      <c r="H41" s="15"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="13"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="10"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2657,22 +2657,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="13"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="11"/>
+      <c r="H42" s="15"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="13"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="10"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2686,24 +2686,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="13"/>
+      <c r="D43" s="10"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="11"/>
+      <c r="H43" s="15"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="6"/>
-      <c r="L43" s="13"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="10"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2717,22 +2717,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="13"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="11"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="13"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="10"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2746,22 +2746,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="13"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="11"/>
+      <c r="H45" s="15"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="13"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="10"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2775,24 +2775,24 @@
       <c r="B46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="13"/>
+      <c r="D46" s="10"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="11"/>
+      <c r="H46" s="15"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K46" s="6"/>
-      <c r="L46" s="13"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="10"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2806,22 +2806,22 @@
       <c r="B47" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="13"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="11"/>
+      <c r="H47" s="15"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K47" s="6"/>
-      <c r="L47" s="13"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="10"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2835,22 +2835,22 @@
       <c r="B48" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="13"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="10"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="11"/>
+      <c r="H48" s="15"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K48" s="6"/>
-      <c r="L48" s="13"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="10"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2864,24 +2864,24 @@
       <c r="B49" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="13"/>
+      <c r="D49" s="10"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="11"/>
+      <c r="H49" s="15"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K49" s="6"/>
-      <c r="L49" s="13"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="10"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2895,22 +2895,22 @@
       <c r="B50" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="13"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="11"/>
+      <c r="H50" s="15"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K50" s="6"/>
-      <c r="L50" s="13"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="10"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2924,22 +2924,22 @@
       <c r="B51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="13"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="10"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="11"/>
+      <c r="H51" s="15"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K51" s="6"/>
-      <c r="L51" s="13"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="10"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2953,26 +2953,26 @@
       <c r="B52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="13"/>
+      <c r="D52" s="10"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="11"/>
+      <c r="H52" s="15"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K52" s="6" t="s">
+      <c r="K52" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L52" s="13"/>
+      <c r="L52" s="10"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2986,22 +2986,22 @@
       <c r="B53" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="13"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="11"/>
+      <c r="H53" s="15"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K53" s="6"/>
-      <c r="L53" s="13"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="10"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -3015,22 +3015,22 @@
       <c r="B54" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="13"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="11"/>
+      <c r="H54" s="15"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="K54" s="6"/>
-      <c r="L54" s="13"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="10"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3044,16 +3044,16 @@
       <c r="B55" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="13"/>
+      <c r="D55" s="10"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="11"/>
+      <c r="H55" s="15"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="K55" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L55" s="13"/>
+      <c r="L55" s="10"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3077,14 +3077,14 @@
       <c r="B56" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="13"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="11"/>
+      <c r="H56" s="15"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>103</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="13"/>
+      <c r="L56" s="10"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3106,14 +3106,14 @@
       <c r="B57" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="13"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="11"/>
+      <c r="H57" s="15"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>109</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="13"/>
+      <c r="L57" s="10"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3135,16 +3135,16 @@
       <c r="B58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="13"/>
+      <c r="D58" s="10"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="11"/>
+      <c r="H58" s="15"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3154,7 +3154,7 @@
       <c r="K58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L58" s="13"/>
+      <c r="L58" s="10"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3168,14 +3168,14 @@
       <c r="B59" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="13"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="11"/>
+      <c r="H59" s="15"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>107</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="13"/>
+      <c r="L59" s="10"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3197,20 +3197,20 @@
       <c r="B60" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="13"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="11"/>
+      <c r="H60" s="15"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="13"/>
+      <c r="L60" s="10"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3224,20 +3224,20 @@
       <c r="B61" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="13"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="11"/>
+      <c r="H61" s="15"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="13"/>
+      <c r="L61" s="10"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3254,19 +3254,19 @@
       <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="13"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="11"/>
+      <c r="H62" s="15"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="13"/>
+      <c r="L62" s="10"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3281,19 +3281,19 @@
         <v>84</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="13"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="11"/>
+      <c r="H63" s="15"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="13"/>
+      <c r="L63" s="10"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3308,19 +3308,19 @@
         <v>85</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="13"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="11"/>
+      <c r="H64" s="15"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="13"/>
+      <c r="L64" s="10"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3337,19 +3337,19 @@
       <c r="C65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="13"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="11"/>
+      <c r="H65" s="15"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="13"/>
+      <c r="L65" s="10"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3364,19 +3364,19 @@
         <v>120</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="13"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="11"/>
+      <c r="H66" s="15"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="13"/>
+      <c r="L66" s="10"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3389,19 +3389,19 @@
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="13"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="11"/>
+      <c r="H67" s="15"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="13"/>
+      <c r="L67" s="10"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3414,19 +3414,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="13"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="11"/>
+      <c r="H68" s="15"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="13"/>
+      <c r="L68" s="10"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3439,19 +3439,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="13"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="11"/>
+      <c r="H69" s="15"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="13"/>
+      <c r="L69" s="10"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3464,19 +3464,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="13"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="11"/>
+      <c r="H70" s="15"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="13"/>
+      <c r="L70" s="10"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3489,19 +3489,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="13"/>
+      <c r="D71" s="10"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="12"/>
+      <c r="H71" s="16"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="13"/>
+      <c r="L71" s="10"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3510,6 +3510,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="G20:G22"/>
@@ -3526,50 +3570,6 @@
     <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eafacaeacfb09265/Skrivebord/! github/EISS/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64F8E07-AE90-466C-91F2-FB95F6DDF4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D64F8E07-AE90-466C-91F2-FB95F6DDF4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2540F9-C9C2-41FE-B30A-D0FC8812804C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -585,13 +585,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,98 +930,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="1"/>
-    <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="1"/>
+    <col min="9" max="9" width="7.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1"/>
+    <col min="14" max="14" width="11.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="1"/>
+    <col min="17" max="17" width="7.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.6640625" style="1" customWidth="1"/>
     <col min="21" max="21" width="12" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="2.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.42578125" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="12.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.109375" style="1"/>
+    <col min="25" max="25" width="6.88671875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.44140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.44140625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.44140625" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="17"/>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
       <c r="X1" s="7"/>
-      <c r="AF1" s="8"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="AF1" s="10"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="17"/>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="10"/>
       <c r="Q2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1035,9 +1035,9 @@
         <v>113</v>
       </c>
       <c r="X2" s="7"/>
-      <c r="AF2" s="8"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF2" s="10"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1047,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="8"/>
+      <c r="P3" s="10"/>
       <c r="Q3" s="1" t="s">
         <v>115</v>
       </c>
@@ -1094,9 +1094,9 @@
         <v>119</v>
       </c>
       <c r="X3" s="7"/>
-      <c r="AF3" s="8"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF3" s="10"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1106,7 +1106,7 @@
       <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -1126,13 +1126,13 @@
       <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="8"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1149,9 +1149,9 @@
         <v>1</v>
       </c>
       <c r="X4" s="7"/>
-      <c r="AF4" s="8"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF4" s="10"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
@@ -1175,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="8"/>
+      <c r="P5" s="10"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1198,9 +1198,9 @@
         <v>2</v>
       </c>
       <c r="X5" s="7"/>
-      <c r="AF5" s="8"/>
-    </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF5" s="10"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1226,13 +1226,13 @@
         <v>4</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
+      <c r="L6" s="8"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="8"/>
+      <c r="P6" s="10"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1249,9 +1249,9 @@
         <v>3</v>
       </c>
       <c r="X6" s="7"/>
-      <c r="AF6" s="8"/>
-    </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF6" s="10"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1261,7 +1261,7 @@
       <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1281,13 +1281,13 @@
       <c r="K7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="8"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="8"/>
+      <c r="P7" s="10"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1304,9 +1304,9 @@
         <v>4</v>
       </c>
       <c r="X7" s="7"/>
-      <c r="AF7" s="8"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF7" s="10"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -1332,13 +1332,13 @@
         <v>6</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
+      <c r="L8" s="8"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="8"/>
+      <c r="P8" s="10"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1355,9 +1355,9 @@
         <v>5</v>
       </c>
       <c r="X8" s="7"/>
-      <c r="AF8" s="8"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF8" s="10"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -1381,13 +1381,13 @@
         <v>7</v>
       </c>
       <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
+      <c r="L9" s="8"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="8"/>
+      <c r="P9" s="10"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1404,9 +1404,9 @@
         <v>6</v>
       </c>
       <c r="X9" s="7"/>
-      <c r="AF9" s="8"/>
-    </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF9" s="10"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
@@ -1436,13 +1436,13 @@
       <c r="K10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="10"/>
+      <c r="L10" s="8"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="8"/>
+      <c r="P10" s="10"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1459,9 +1459,9 @@
         <v>7</v>
       </c>
       <c r="X10" s="7"/>
-      <c r="AF10" s="8"/>
-    </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF10" s="10"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
@@ -1485,13 +1485,13 @@
         <v>56</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
+      <c r="L11" s="8"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="8"/>
+      <c r="P11" s="10"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1508,9 +1508,9 @@
         <v>8</v>
       </c>
       <c r="X11" s="7"/>
-      <c r="AF11" s="8"/>
-    </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF11" s="10"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
@@ -1536,13 +1536,13 @@
         <v>57</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="8"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="8"/>
+      <c r="P12" s="10"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1559,9 +1559,9 @@
         <v>9</v>
       </c>
       <c r="X12" s="7"/>
-      <c r="AF12" s="8"/>
-    </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF12" s="10"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
@@ -1589,13 +1589,13 @@
       <c r="K13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="10"/>
+      <c r="L13" s="8"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="8"/>
+      <c r="P13" s="10"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1612,9 +1612,9 @@
         <v>10</v>
       </c>
       <c r="X13" s="7"/>
-      <c r="AF13" s="8"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF13" s="10"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1640,13 +1640,13 @@
         <v>59</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
+      <c r="L14" s="8"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="8"/>
+      <c r="P14" s="10"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1663,9 +1663,9 @@
         <v>11</v>
       </c>
       <c r="X14" s="7"/>
-      <c r="AF14" s="8"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF14" s="10"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1687,13 +1687,13 @@
         <v>60</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="8"/>
+      <c r="P15" s="10"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1710,9 +1710,9 @@
         <v>12</v>
       </c>
       <c r="X15" s="7"/>
-      <c r="AF15" s="8"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF15" s="10"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1736,13 +1736,13 @@
       <c r="K16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="8"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="8"/>
+      <c r="P16" s="10"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1759,9 +1759,9 @@
         <v>13</v>
       </c>
       <c r="X16" s="7"/>
-      <c r="AF16" s="8"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF16" s="10"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1787,13 +1787,13 @@
         <v>62</v>
       </c>
       <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="8"/>
+      <c r="P17" s="10"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1810,9 +1810,9 @@
         <v>14</v>
       </c>
       <c r="X17" s="7"/>
-      <c r="AF17" s="8"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF17" s="10"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1838,13 +1838,13 @@
         <v>63</v>
       </c>
       <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
+      <c r="L18" s="8"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="8"/>
+      <c r="P18" s="10"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1861,9 @@
         <v>15</v>
       </c>
       <c r="X18" s="7"/>
-      <c r="AF18" s="8"/>
-    </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF18" s="10"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1889,13 +1889,13 @@
       <c r="K19" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="L19" s="10"/>
+      <c r="L19" s="8"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="8"/>
+      <c r="P19" s="10"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1912,9 +1912,9 @@
         <v>16</v>
       </c>
       <c r="X19" s="7"/>
-      <c r="AF19" s="8"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF19" s="10"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1940,17 +1940,17 @@
         <v>65</v>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
+      <c r="L20" s="8"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="8"/>
+      <c r="P20" s="10"/>
       <c r="X20" s="7"/>
-      <c r="AF20" s="8"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF20" s="10"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="C21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1976,17 +1976,17 @@
         <v>66</v>
       </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
+      <c r="L21" s="8"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="8"/>
+      <c r="P21" s="10"/>
       <c r="X21" s="7"/>
-      <c r="AF21" s="8"/>
-    </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF21" s="10"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -2012,17 +2012,17 @@
       <c r="K22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L22" s="10"/>
+      <c r="L22" s="8"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="8"/>
+      <c r="P22" s="10"/>
       <c r="X22" s="7"/>
-      <c r="AF22" s="8"/>
-    </row>
-    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF22" s="10"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -2048,17 +2048,17 @@
         <v>70</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="10"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="8"/>
+      <c r="P23" s="10"/>
       <c r="X23" s="7"/>
-      <c r="AF23" s="8"/>
-    </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF23" s="10"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2068,7 +2068,7 @@
       <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -2084,17 +2084,17 @@
         <v>71</v>
       </c>
       <c r="K24" s="9"/>
-      <c r="L24" s="10"/>
+      <c r="L24" s="8"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="8"/>
+      <c r="P24" s="10"/>
       <c r="X24" s="7"/>
-      <c r="AF24" s="8"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF24" s="10"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -2118,17 +2118,17 @@
         <v>88</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="10"/>
+      <c r="L25" s="8"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="8"/>
+      <c r="P25" s="10"/>
       <c r="X25" s="7"/>
-      <c r="AF25" s="8"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF25" s="10"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -2156,17 +2156,17 @@
       <c r="K26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L26" s="10"/>
+      <c r="L26" s="8"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="8"/>
+      <c r="P26" s="10"/>
       <c r="X26" s="7"/>
-      <c r="AF26" s="8"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF26" s="10"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2176,7 +2176,7 @@
       <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -2192,17 +2192,17 @@
         <v>84</v>
       </c>
       <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
+      <c r="L27" s="8"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="8"/>
+      <c r="P27" s="10"/>
       <c r="X27" s="7"/>
-      <c r="AF27" s="8"/>
-    </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF27" s="10"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
+      <c r="D28" s="8"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -2226,17 +2226,17 @@
         <v>85</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
+      <c r="L28" s="8"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="8"/>
+      <c r="P28" s="10"/>
       <c r="X28" s="7"/>
-      <c r="AF28" s="8"/>
-    </row>
-    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF28" s="10"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -2262,17 +2262,17 @@
         <v>109</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="10"/>
+      <c r="L29" s="8"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="8"/>
+      <c r="P29" s="10"/>
       <c r="X29" s="7"/>
-      <c r="AF29" s="8"/>
-    </row>
-    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF29" s="10"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="C30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="10"/>
+      <c r="D30" s="8"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -2298,17 +2298,17 @@
         <v>90</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="10"/>
+      <c r="L30" s="8"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="8"/>
+      <c r="P30" s="10"/>
       <c r="X30" s="7"/>
-      <c r="AF30" s="8"/>
-    </row>
-    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF30" s="10"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -2332,17 +2332,17 @@
         <v>103</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="10"/>
+      <c r="L31" s="8"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="8"/>
+      <c r="P31" s="10"/>
       <c r="X31" s="7"/>
-      <c r="AF31" s="8"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF31" s="10"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
+      <c r="D32" s="8"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
@@ -2368,17 +2368,17 @@
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="L32" s="8"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="8"/>
+      <c r="P32" s="10"/>
       <c r="X32" s="7"/>
-      <c r="AF32" s="8"/>
-    </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF32" s="10"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2388,7 +2388,7 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="10"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
@@ -2406,17 +2406,17 @@
         <v>110</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="10"/>
+      <c r="L33" s="8"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="8"/>
+      <c r="P33" s="10"/>
       <c r="X33" s="7"/>
-      <c r="AF33" s="8"/>
-    </row>
-    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF33" s="10"/>
+    </row>
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2426,7 +2426,7 @@
       <c r="C34" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="10"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
@@ -2442,17 +2442,17 @@
         <v>120</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="10"/>
+      <c r="L34" s="8"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="8"/>
+      <c r="P34" s="10"/>
       <c r="X34" s="7"/>
-      <c r="AF34" s="8"/>
-    </row>
-    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF34" s="10"/>
+    </row>
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>53</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
@@ -2474,17 +2474,17 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="10"/>
+      <c r="L35" s="8"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="8"/>
+      <c r="P35" s="10"/>
       <c r="X35" s="7"/>
-      <c r="AF35" s="8"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF35" s="10"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2501,53 +2501,53 @@
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
       <c r="H38" s="15"/>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10" t="s">
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2557,7 +2557,7 @@
       <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="10"/>
+      <c r="D39" s="8"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="K39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L39" s="10"/>
+      <c r="L39" s="8"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>1</v>
       </c>
@@ -2598,7 +2598,7 @@
       <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="10"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
@@ -2614,14 +2614,14 @@
       <c r="K40" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="L40" s="10"/>
+      <c r="L40" s="8"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
@@ -2643,14 +2643,14 @@
         <v>3</v>
       </c>
       <c r="K41" s="9"/>
-      <c r="L41" s="10"/>
+      <c r="L41" s="8"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
+      <c r="D42" s="8"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
@@ -2672,14 +2672,14 @@
         <v>4</v>
       </c>
       <c r="K42" s="9"/>
-      <c r="L42" s="10"/>
+      <c r="L42" s="8"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>4</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="10"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -2703,14 +2703,14 @@
         <v>5</v>
       </c>
       <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
+      <c r="L43" s="8"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>5</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
@@ -2732,14 +2732,14 @@
         <v>6</v>
       </c>
       <c r="K44" s="9"/>
-      <c r="L44" s="10"/>
+      <c r="L44" s="8"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>6</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
+      <c r="D45" s="8"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
@@ -2761,14 +2761,14 @@
         <v>7</v>
       </c>
       <c r="K45" s="9"/>
-      <c r="L45" s="10"/>
+      <c r="L45" s="8"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>7</v>
       </c>
@@ -2778,7 +2778,7 @@
       <c r="C46" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="10"/>
+      <c r="D46" s="8"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
@@ -2792,14 +2792,14 @@
         <v>91</v>
       </c>
       <c r="K46" s="9"/>
-      <c r="L46" s="10"/>
+      <c r="L46" s="8"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>8</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>56</v>
       </c>
       <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
@@ -2821,14 +2821,14 @@
         <v>92</v>
       </c>
       <c r="K47" s="9"/>
-      <c r="L47" s="10"/>
+      <c r="L47" s="8"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>9</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>57</v>
       </c>
       <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
+      <c r="D48" s="8"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
@@ -2850,14 +2850,14 @@
         <v>93</v>
       </c>
       <c r="K48" s="9"/>
-      <c r="L48" s="10"/>
+      <c r="L48" s="8"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>10</v>
       </c>
@@ -2867,7 +2867,7 @@
       <c r="C49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="10"/>
+      <c r="D49" s="8"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
@@ -2881,14 +2881,14 @@
         <v>94</v>
       </c>
       <c r="K49" s="9"/>
-      <c r="L49" s="10"/>
+      <c r="L49" s="8"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>11</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>59</v>
       </c>
       <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
+      <c r="D50" s="8"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
@@ -2910,14 +2910,14 @@
         <v>95</v>
       </c>
       <c r="K50" s="9"/>
-      <c r="L50" s="10"/>
+      <c r="L50" s="8"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>12</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>60</v>
       </c>
       <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
+      <c r="D51" s="8"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
@@ -2939,14 +2939,14 @@
         <v>96</v>
       </c>
       <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
+      <c r="L51" s="8"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>13</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="C52" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="10"/>
+      <c r="D52" s="8"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
@@ -2972,14 +2972,14 @@
       <c r="K52" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L52" s="10"/>
+      <c r="L52" s="8"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>14</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>62</v>
       </c>
       <c r="C53" s="9"/>
-      <c r="D53" s="10"/>
+      <c r="D53" s="8"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
@@ -3001,14 +3001,14 @@
         <v>98</v>
       </c>
       <c r="K53" s="9"/>
-      <c r="L53" s="10"/>
+      <c r="L53" s="8"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>15</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>63</v>
       </c>
       <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
@@ -3030,14 +3030,14 @@
         <v>99</v>
       </c>
       <c r="K54" s="9"/>
-      <c r="L54" s="10"/>
+      <c r="L54" s="8"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>16</v>
       </c>
@@ -3047,7 +3047,7 @@
       <c r="C55" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="10"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
@@ -3063,14 +3063,14 @@
       <c r="K55" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L55" s="10"/>
+      <c r="L55" s="8"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>17</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>65</v>
       </c>
       <c r="C56" s="9"/>
-      <c r="D56" s="10"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
@@ -3092,14 +3092,14 @@
         <v>103</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="10"/>
+      <c r="L56" s="8"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>18</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>66</v>
       </c>
       <c r="C57" s="9"/>
-      <c r="D57" s="10"/>
+      <c r="D57" s="8"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
@@ -3121,14 +3121,14 @@
         <v>109</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="10"/>
+      <c r="L57" s="8"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>19</v>
       </c>
@@ -3138,7 +3138,7 @@
       <c r="C58" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="10"/>
+      <c r="D58" s="8"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
@@ -3154,14 +3154,14 @@
       <c r="K58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L58" s="10"/>
+      <c r="L58" s="8"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>20</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>70</v>
       </c>
       <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
+      <c r="D59" s="8"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
@@ -3183,14 +3183,14 @@
         <v>107</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="10"/>
+      <c r="L59" s="8"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>21</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>71</v>
       </c>
       <c r="C60" s="9"/>
-      <c r="D60" s="10"/>
+      <c r="D60" s="8"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="10"/>
+      <c r="L60" s="8"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>22</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>88</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="10"/>
+      <c r="D61" s="8"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
@@ -3237,14 +3237,14 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="10"/>
+      <c r="L61" s="8"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>23</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="8"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="10"/>
+      <c r="L62" s="8"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>24</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>84</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="8"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="10"/>
+      <c r="L63" s="8"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>25</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>85</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="8"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="10"/>
+      <c r="L64" s="8"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>26</v>
       </c>
@@ -3337,7 +3337,7 @@
       <c r="C65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="10"/>
+      <c r="D65" s="8"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
@@ -3349,14 +3349,14 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="10"/>
+      <c r="L65" s="8"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>27</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>120</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="8"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
@@ -3376,20 +3376,20 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="10"/>
+      <c r="L66" s="8"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>28</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="8"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="8"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>29</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="8"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
@@ -3426,20 +3426,20 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="8"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>30</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="8"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
@@ -3451,20 +3451,20 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="8"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>31</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="10"/>
+      <c r="D70" s="8"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
@@ -3476,20 +3476,20 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="8"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>32</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="10"/>
+      <c r="D71" s="8"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="8"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3510,6 +3510,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
@@ -3526,50 +3570,6 @@
     <mergeCell ref="H1:H35"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K22:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eafacaeacfb09265/Skrivebord/! github/EISS/documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D64F8E07-AE90-466C-91F2-FB95F6DDF4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2540F9-C9C2-41FE-B30A-D0FC8812804C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC2FC26-C10F-460A-9837-C319B020F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="121">
   <si>
     <t>Freq:</t>
   </si>
@@ -585,13 +585,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,98 +930,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="1"/>
-    <col min="14" max="14" width="11.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="1"/>
-    <col min="17" max="17" width="7.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="12" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.44140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.109375" style="1"/>
-    <col min="25" max="25" width="6.88671875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.88671875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="19.44140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="2.6640625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5546875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16.44140625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.44140625" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.109375" style="1"/>
+    <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="1"/>
+    <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.42578125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
       <c r="H1" s="17"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
       <c r="X1" s="7"/>
-      <c r="AF1" s="10"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="AF1" s="8"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
       <c r="H2" s="17"/>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8"/>
       <c r="Q2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1035,9 +1035,9 @@
         <v>113</v>
       </c>
       <c r="X2" s="7"/>
-      <c r="AF2" s="10"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF2" s="8"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1047,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="8"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
       <c r="O3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="10"/>
+      <c r="P3" s="8"/>
       <c r="Q3" s="1" t="s">
         <v>115</v>
       </c>
@@ -1094,9 +1094,9 @@
         <v>119</v>
       </c>
       <c r="X3" s="7"/>
-      <c r="AF3" s="10"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF3" s="8"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1106,7 +1106,7 @@
       <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -1126,13 +1126,13 @@
       <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="8"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="10"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1149,9 +1149,9 @@
         <v>1</v>
       </c>
       <c r="X4" s="7"/>
-      <c r="AF4" s="10"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF4" s="8"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
@@ -1175,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="8"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="10"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1198,9 +1198,9 @@
         <v>2</v>
       </c>
       <c r="X5" s="7"/>
-      <c r="AF5" s="10"/>
-    </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF5" s="8"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1226,13 +1226,13 @@
         <v>4</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="10"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1249,9 +1249,9 @@
         <v>3</v>
       </c>
       <c r="X6" s="7"/>
-      <c r="AF6" s="10"/>
-    </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF6" s="8"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1261,7 +1261,7 @@
       <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1281,13 +1281,13 @@
       <c r="K7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="10"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1304,9 +1304,9 @@
         <v>4</v>
       </c>
       <c r="X7" s="7"/>
-      <c r="AF7" s="10"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF7" s="8"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -1332,13 +1332,13 @@
         <v>6</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="10"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1355,9 +1355,9 @@
         <v>5</v>
       </c>
       <c r="X8" s="7"/>
-      <c r="AF8" s="10"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF8" s="8"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -1381,13 +1381,13 @@
         <v>7</v>
       </c>
       <c r="K9" s="9"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="10"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1404,9 +1404,9 @@
         <v>6</v>
       </c>
       <c r="X9" s="7"/>
-      <c r="AF9" s="10"/>
-    </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF9" s="8"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
@@ -1436,13 +1436,13 @@
       <c r="K10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="8"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="10"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1459,9 +1459,9 @@
         <v>7</v>
       </c>
       <c r="X10" s="7"/>
-      <c r="AF10" s="10"/>
-    </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF10" s="8"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
@@ -1485,13 +1485,13 @@
         <v>56</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="10"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1508,9 +1508,9 @@
         <v>8</v>
       </c>
       <c r="X11" s="7"/>
-      <c r="AF11" s="10"/>
-    </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF11" s="8"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
@@ -1536,13 +1536,13 @@
         <v>57</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="10"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1559,9 +1559,9 @@
         <v>9</v>
       </c>
       <c r="X12" s="7"/>
-      <c r="AF12" s="10"/>
-    </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF12" s="8"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
@@ -1589,13 +1589,13 @@
       <c r="K13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="8"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="10"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1612,9 +1612,9 @@
         <v>10</v>
       </c>
       <c r="X13" s="7"/>
-      <c r="AF13" s="10"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF13" s="8"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1640,13 +1640,13 @@
         <v>59</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="10"/>
+      <c r="P14" s="8"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1663,9 +1663,9 @@
         <v>11</v>
       </c>
       <c r="X14" s="7"/>
-      <c r="AF14" s="10"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF14" s="8"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1687,13 +1687,13 @@
         <v>60</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="10"/>
+      <c r="P15" s="8"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1710,9 +1710,9 @@
         <v>12</v>
       </c>
       <c r="X15" s="7"/>
-      <c r="AF15" s="10"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF15" s="8"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1736,13 +1736,13 @@
       <c r="K16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L16" s="8"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="10"/>
+      <c r="P16" s="8"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1759,9 +1759,9 @@
         <v>13</v>
       </c>
       <c r="X16" s="7"/>
-      <c r="AF16" s="10"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF16" s="8"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
@@ -1787,13 +1787,13 @@
         <v>62</v>
       </c>
       <c r="K17" s="9"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="10"/>
+      <c r="P17" s="8"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1810,9 +1810,9 @@
         <v>14</v>
       </c>
       <c r="X17" s="7"/>
-      <c r="AF17" s="10"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF17" s="8"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
@@ -1838,13 +1838,13 @@
         <v>63</v>
       </c>
       <c r="K18" s="9"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="10"/>
+      <c r="P18" s="8"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1861,9 @@
         <v>15</v>
       </c>
       <c r="X18" s="7"/>
-      <c r="AF18" s="10"/>
-    </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF18" s="8"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
@@ -1889,13 +1889,13 @@
       <c r="K19" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="L19" s="8"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="10"/>
+      <c r="P19" s="8"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1912,9 +1912,9 @@
         <v>16</v>
       </c>
       <c r="X19" s="7"/>
-      <c r="AF19" s="10"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF19" s="8"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
@@ -1940,17 +1940,17 @@
         <v>65</v>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="10"/>
+      <c r="P20" s="8"/>
       <c r="X20" s="7"/>
-      <c r="AF20" s="10"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF20" s="8"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="C21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
@@ -1976,17 +1976,17 @@
         <v>66</v>
       </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="10"/>
+      <c r="P21" s="8"/>
       <c r="X21" s="7"/>
-      <c r="AF21" s="10"/>
-    </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF21" s="8"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
@@ -2012,17 +2012,17 @@
       <c r="K22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L22" s="8"/>
+      <c r="L22" s="10"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="10"/>
+      <c r="P22" s="8"/>
       <c r="X22" s="7"/>
-      <c r="AF22" s="10"/>
-    </row>
-    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF22" s="8"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>29</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
@@ -2044,21 +2044,19 @@
       <c r="I23" s="2">
         <v>20</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="J23" s="2"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="10"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="10"/>
+      <c r="P23" s="8"/>
       <c r="X23" s="7"/>
-      <c r="AF23" s="10"/>
-    </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF23" s="8"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2068,7 +2066,7 @@
       <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
@@ -2084,17 +2082,17 @@
         <v>71</v>
       </c>
       <c r="K24" s="9"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="10"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="10"/>
+      <c r="P24" s="8"/>
       <c r="X24" s="7"/>
-      <c r="AF24" s="10"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF24" s="8"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2102,7 +2100,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
@@ -2118,17 +2116,17 @@
         <v>88</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="8"/>
+      <c r="L25" s="10"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="10"/>
+      <c r="P25" s="8"/>
       <c r="X25" s="7"/>
-      <c r="AF25" s="10"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF25" s="8"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2136,7 +2134,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -2156,17 +2154,17 @@
       <c r="K26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L26" s="8"/>
+      <c r="L26" s="10"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="10"/>
+      <c r="P26" s="8"/>
       <c r="X26" s="7"/>
-      <c r="AF26" s="10"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF26" s="8"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2176,7 +2174,7 @@
       <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -2192,17 +2190,17 @@
         <v>84</v>
       </c>
       <c r="K27" s="9"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="10"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="10"/>
+      <c r="P27" s="8"/>
       <c r="X27" s="7"/>
-      <c r="AF27" s="10"/>
-    </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF27" s="8"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2210,7 +2208,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="9"/>
-      <c r="D28" s="8"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -2226,17 +2224,17 @@
         <v>85</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="10"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="10"/>
+      <c r="P28" s="8"/>
       <c r="X28" s="7"/>
-      <c r="AF28" s="10"/>
-    </row>
-    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF28" s="8"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2244,7 +2242,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -2262,17 +2260,17 @@
         <v>109</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="10"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="10"/>
+      <c r="P29" s="8"/>
       <c r="X29" s="7"/>
-      <c r="AF29" s="10"/>
-    </row>
-    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF29" s="8"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -2282,13 +2280,11 @@
       <c r="C30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="9"/>
       <c r="H30" s="17"/>
       <c r="I30" s="2">
@@ -2298,17 +2294,17 @@
         <v>90</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
+      <c r="L30" s="10"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="10"/>
+      <c r="P30" s="8"/>
       <c r="X30" s="7"/>
-      <c r="AF30" s="10"/>
-    </row>
-    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF30" s="8"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -2316,7 +2312,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="9"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="10"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -2332,17 +2328,17 @@
         <v>103</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="10"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="10"/>
+      <c r="P31" s="8"/>
       <c r="X31" s="7"/>
-      <c r="AF31" s="10"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF31" s="8"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2350,7 +2346,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
@@ -2368,17 +2364,17 @@
       <c r="K32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L32" s="8"/>
+      <c r="L32" s="10"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="10"/>
+      <c r="P32" s="8"/>
       <c r="X32" s="7"/>
-      <c r="AF32" s="10"/>
-    </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF32" s="8"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2388,7 +2384,7 @@
       <c r="C33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="10"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
@@ -2406,17 +2402,17 @@
         <v>110</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="10"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="10"/>
+      <c r="P33" s="8"/>
       <c r="X33" s="7"/>
-      <c r="AF33" s="10"/>
-    </row>
-    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF33" s="8"/>
+    </row>
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2426,7 +2422,7 @@
       <c r="C34" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="8"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
@@ -2442,17 +2438,17 @@
         <v>120</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="10"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="10"/>
+      <c r="P34" s="8"/>
       <c r="X34" s="7"/>
-      <c r="AF34" s="10"/>
-    </row>
-    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF34" s="8"/>
+    </row>
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2460,7 +2456,7 @@
         <v>53</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
@@ -2474,17 +2470,17 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="10"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="10"/>
+      <c r="P35" s="8"/>
       <c r="X35" s="7"/>
-      <c r="AF35" s="10"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF35" s="8"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2501,53 +2497,53 @@
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
       <c r="H38" s="15"/>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8" t="s">
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2557,7 +2553,7 @@
       <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="8"/>
+      <c r="D39" s="10"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2573,7 @@
       <c r="K39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L39" s="8"/>
+      <c r="L39" s="10"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +2584,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>1</v>
       </c>
@@ -2598,7 +2594,7 @@
       <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="8"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
@@ -2614,14 +2610,14 @@
       <c r="K40" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="L40" s="8"/>
+      <c r="L40" s="10"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2</v>
       </c>
@@ -2629,7 +2625,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="9"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
@@ -2643,14 +2639,14 @@
         <v>3</v>
       </c>
       <c r="K41" s="9"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="10"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -2658,7 +2654,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="9"/>
-      <c r="D42" s="8"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
@@ -2672,14 +2668,14 @@
         <v>4</v>
       </c>
       <c r="K42" s="9"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="10"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>4</v>
       </c>
@@ -2689,7 +2685,7 @@
       <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="8"/>
+      <c r="D43" s="10"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -2703,14 +2699,14 @@
         <v>5</v>
       </c>
       <c r="K43" s="9"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="10"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>5</v>
       </c>
@@ -2718,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="9"/>
-      <c r="D44" s="8"/>
+      <c r="D44" s="10"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
@@ -2732,14 +2728,14 @@
         <v>6</v>
       </c>
       <c r="K44" s="9"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="10"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>6</v>
       </c>
@@ -2747,7 +2743,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="9"/>
-      <c r="D45" s="8"/>
+      <c r="D45" s="10"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
@@ -2761,14 +2757,14 @@
         <v>7</v>
       </c>
       <c r="K45" s="9"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="10"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>7</v>
       </c>
@@ -2778,7 +2774,7 @@
       <c r="C46" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="8"/>
+      <c r="D46" s="10"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
@@ -2792,14 +2788,14 @@
         <v>91</v>
       </c>
       <c r="K46" s="9"/>
-      <c r="L46" s="8"/>
+      <c r="L46" s="10"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>8</v>
       </c>
@@ -2807,7 +2803,7 @@
         <v>56</v>
       </c>
       <c r="C47" s="9"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
@@ -2821,14 +2817,14 @@
         <v>92</v>
       </c>
       <c r="K47" s="9"/>
-      <c r="L47" s="8"/>
+      <c r="L47" s="10"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>9</v>
       </c>
@@ -2836,7 +2832,7 @@
         <v>57</v>
       </c>
       <c r="C48" s="9"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="10"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
@@ -2850,14 +2846,14 @@
         <v>93</v>
       </c>
       <c r="K48" s="9"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="10"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>10</v>
       </c>
@@ -2867,7 +2863,7 @@
       <c r="C49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="8"/>
+      <c r="D49" s="10"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
@@ -2881,14 +2877,14 @@
         <v>94</v>
       </c>
       <c r="K49" s="9"/>
-      <c r="L49" s="8"/>
+      <c r="L49" s="10"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>11</v>
       </c>
@@ -2896,7 +2892,7 @@
         <v>59</v>
       </c>
       <c r="C50" s="9"/>
-      <c r="D50" s="8"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
@@ -2910,14 +2906,14 @@
         <v>95</v>
       </c>
       <c r="K50" s="9"/>
-      <c r="L50" s="8"/>
+      <c r="L50" s="10"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>12</v>
       </c>
@@ -2925,7 +2921,7 @@
         <v>60</v>
       </c>
       <c r="C51" s="9"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="10"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
@@ -2939,14 +2935,14 @@
         <v>96</v>
       </c>
       <c r="K51" s="9"/>
-      <c r="L51" s="8"/>
+      <c r="L51" s="10"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>13</v>
       </c>
@@ -2956,7 +2952,7 @@
       <c r="C52" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="8"/>
+      <c r="D52" s="10"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
@@ -2972,14 +2968,14 @@
       <c r="K52" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L52" s="8"/>
+      <c r="L52" s="10"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>14</v>
       </c>
@@ -2987,7 +2983,7 @@
         <v>62</v>
       </c>
       <c r="C53" s="9"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
@@ -3001,14 +2997,14 @@
         <v>98</v>
       </c>
       <c r="K53" s="9"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="10"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>15</v>
       </c>
@@ -3016,7 +3012,7 @@
         <v>63</v>
       </c>
       <c r="C54" s="9"/>
-      <c r="D54" s="8"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
@@ -3030,14 +3026,14 @@
         <v>99</v>
       </c>
       <c r="K54" s="9"/>
-      <c r="L54" s="8"/>
+      <c r="L54" s="10"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>16</v>
       </c>
@@ -3047,7 +3043,7 @@
       <c r="C55" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="8"/>
+      <c r="D55" s="10"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
@@ -3063,14 +3059,14 @@
       <c r="K55" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L55" s="8"/>
+      <c r="L55" s="10"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>17</v>
       </c>
@@ -3078,7 +3074,7 @@
         <v>65</v>
       </c>
       <c r="C56" s="9"/>
-      <c r="D56" s="8"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
@@ -3092,14 +3088,14 @@
         <v>103</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="8"/>
+      <c r="L56" s="10"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>18</v>
       </c>
@@ -3107,7 +3103,7 @@
         <v>66</v>
       </c>
       <c r="C57" s="9"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
@@ -3121,14 +3117,14 @@
         <v>109</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="8"/>
+      <c r="L57" s="10"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>19</v>
       </c>
@@ -3138,7 +3134,7 @@
       <c r="C58" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="8"/>
+      <c r="D58" s="10"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
@@ -3154,14 +3150,14 @@
       <c r="K58" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L58" s="8"/>
+      <c r="L58" s="10"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>20</v>
       </c>
@@ -3169,7 +3165,7 @@
         <v>70</v>
       </c>
       <c r="C59" s="9"/>
-      <c r="D59" s="8"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
@@ -3183,14 +3179,14 @@
         <v>107</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="8"/>
+      <c r="L59" s="10"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>21</v>
       </c>
@@ -3198,7 +3194,7 @@
         <v>71</v>
       </c>
       <c r="C60" s="9"/>
-      <c r="D60" s="8"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
@@ -3210,14 +3206,14 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="8"/>
+      <c r="L60" s="10"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>22</v>
       </c>
@@ -3225,7 +3221,7 @@
         <v>88</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="8"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
@@ -3237,14 +3233,14 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="8"/>
+      <c r="L61" s="10"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>23</v>
       </c>
@@ -3254,7 +3250,7 @@
       <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="8"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
@@ -3266,14 +3262,14 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="8"/>
+      <c r="L62" s="10"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>24</v>
       </c>
@@ -3281,7 +3277,7 @@
         <v>84</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="8"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
@@ -3293,14 +3289,14 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="8"/>
+      <c r="L63" s="10"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>25</v>
       </c>
@@ -3308,7 +3304,7 @@
         <v>85</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="8"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
@@ -3320,14 +3316,14 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="8"/>
+      <c r="L64" s="10"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>26</v>
       </c>
@@ -3337,7 +3333,7 @@
       <c r="C65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="8"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
@@ -3349,14 +3345,14 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="8"/>
+      <c r="L65" s="10"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>27</v>
       </c>
@@ -3364,7 +3360,7 @@
         <v>120</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="8"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
@@ -3376,20 +3372,20 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="8"/>
+      <c r="L66" s="10"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>28</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
@@ -3401,20 +3397,20 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="8"/>
+      <c r="L67" s="10"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>29</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="8"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
@@ -3426,20 +3422,20 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="8"/>
+      <c r="L68" s="10"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>30</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="8"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
@@ -3451,20 +3447,20 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="8"/>
+      <c r="L69" s="10"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>31</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="8"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
@@ -3476,20 +3472,20 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="8"/>
+      <c r="L70" s="10"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>32</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="10"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
@@ -3501,7 +3497,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="8"/>
+      <c r="L71" s="10"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3510,6 +3506,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="G20:G22"/>
@@ -3526,50 +3566,6 @@
     <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eafacaeacfb09265/Skrivebord/! github/EISS/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC2FC26-C10F-460A-9837-C319B020F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4AC2FC26-C10F-460A-9837-C319B020F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49378A5C-6501-48F7-820C-887BE656F848}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,9 +149,6 @@
     <t>selection coordinate</t>
   </si>
   <si>
-    <t>new check dist</t>
-  </si>
-  <si>
     <t>new check azim</t>
   </si>
   <si>
@@ -399,6 +396,9 @@
   </si>
   <si>
     <t>RWR Shit</t>
+  </si>
+  <si>
+    <t>new check dist nvm 01trigger</t>
   </si>
 </sst>
 </file>
@@ -585,13 +585,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,124 +930,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="1"/>
-    <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="1"/>
+    <col min="9" max="9" width="7.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1"/>
+    <col min="14" max="14" width="11.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="1"/>
+    <col min="17" max="17" width="7.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.6640625" style="1" customWidth="1"/>
     <col min="21" max="21" width="12" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="2.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.42578125" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="12.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.109375" style="1"/>
+    <col min="25" max="25" width="6.88671875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.44140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.44140625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.44140625" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="X1" s="7"/>
+      <c r="AF1" s="10"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X2" s="7"/>
+      <c r="AF2" s="10"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="X1" s="7"/>
-      <c r="AF1" s="8"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="X2" s="7"/>
-      <c r="AF2" s="8"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="3" t="s">
@@ -1065,9 +1065,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="L3" s="8"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1075,28 +1075,28 @@
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="P3" s="10"/>
       <c r="Q3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="X3" s="7"/>
-      <c r="AF3" s="8"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF3" s="10"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1106,15 +1106,15 @@
       <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" s="17"/>
       <c r="I4" s="2">
@@ -1126,13 +1126,13 @@
       <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="8"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1149,9 +1149,9 @@
         <v>1</v>
       </c>
       <c r="X4" s="7"/>
-      <c r="AF4" s="8"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF4" s="10"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1159,12 +1159,12 @@
         <v>3</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="17"/>
@@ -1175,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="8"/>
+      <c r="P5" s="10"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1198,9 +1198,9 @@
         <v>2</v>
       </c>
       <c r="X5" s="7"/>
-      <c r="AF5" s="8"/>
-    </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF5" s="10"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1208,15 +1208,15 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="2">
@@ -1226,13 +1226,13 @@
         <v>4</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
+      <c r="L6" s="8"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="8"/>
+      <c r="P6" s="10"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1249,9 +1249,9 @@
         <v>3</v>
       </c>
       <c r="X6" s="7"/>
-      <c r="AF6" s="8"/>
-    </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF6" s="10"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1261,15 +1261,15 @@
       <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="2">
@@ -1281,13 +1281,13 @@
       <c r="K7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="8"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="8"/>
+      <c r="P7" s="10"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1304,9 +1304,9 @@
         <v>4</v>
       </c>
       <c r="X7" s="7"/>
-      <c r="AF7" s="8"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF7" s="10"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1314,15 +1314,15 @@
         <v>6</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="2">
@@ -1332,13 +1332,13 @@
         <v>6</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
+      <c r="L8" s="8"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="8"/>
+      <c r="P8" s="10"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1355,9 +1355,9 @@
         <v>5</v>
       </c>
       <c r="X8" s="7"/>
-      <c r="AF8" s="8"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF8" s="10"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1365,12 +1365,12 @@
         <v>7</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="17"/>
@@ -1381,13 +1381,13 @@
         <v>7</v>
       </c>
       <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
+      <c r="L9" s="8"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="8"/>
+      <c r="P9" s="10"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1404,9 +1404,9 @@
         <v>6</v>
       </c>
       <c r="X9" s="7"/>
-      <c r="AF9" s="8"/>
-    </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF9" s="10"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1416,33 +1416,33 @@
       <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="L10" s="8"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="8"/>
+      <c r="P10" s="10"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1459,9 +1459,9 @@
         <v>7</v>
       </c>
       <c r="X10" s="7"/>
-      <c r="AF10" s="8"/>
-    </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF10" s="10"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1469,12 +1469,12 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="17"/>
@@ -1482,16 +1482,16 @@
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
+      <c r="L11" s="8"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="8"/>
+      <c r="P11" s="10"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1508,9 +1508,9 @@
         <v>8</v>
       </c>
       <c r="X11" s="7"/>
-      <c r="AF11" s="8"/>
-    </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF11" s="10"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1518,31 +1518,31 @@
         <v>10</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="8"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="8"/>
+      <c r="P12" s="10"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1559,9 +1559,9 @@
         <v>9</v>
       </c>
       <c r="X12" s="7"/>
-      <c r="AF12" s="8"/>
-    </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF12" s="10"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1571,12 +1571,12 @@
       <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
@@ -1584,18 +1584,18 @@
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" s="10"/>
+        <v>80</v>
+      </c>
+      <c r="L13" s="8"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="8"/>
+      <c r="P13" s="10"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1612,9 +1612,9 @@
         <v>10</v>
       </c>
       <c r="X13" s="7"/>
-      <c r="AF13" s="8"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF13" s="10"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1622,31 +1622,31 @@
         <v>12</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
+      <c r="L14" s="8"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="8"/>
+      <c r="P14" s="10"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1663,9 +1663,9 @@
         <v>11</v>
       </c>
       <c r="X14" s="7"/>
-      <c r="AF14" s="8"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF14" s="10"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1675,7 +1675,7 @@
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1684,16 +1684,16 @@
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="8"/>
+      <c r="P15" s="10"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1710,9 +1710,9 @@
         <v>12</v>
       </c>
       <c r="X15" s="7"/>
-      <c r="AF15" s="8"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF15" s="10"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1731,18 +1731,18 @@
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L16" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="L16" s="8"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="8"/>
+      <c r="P16" s="10"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1759,9 +1759,9 @@
         <v>13</v>
       </c>
       <c r="X16" s="7"/>
-      <c r="AF16" s="8"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF16" s="10"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1769,31 +1769,31 @@
         <v>15</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="8"/>
+      <c r="P17" s="10"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1810,9 +1810,9 @@
         <v>14</v>
       </c>
       <c r="X17" s="7"/>
-      <c r="AF17" s="8"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF17" s="10"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1822,12 +1822,12 @@
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="17"/>
@@ -1835,16 +1835,16 @@
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
+      <c r="L18" s="8"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="8"/>
+      <c r="P18" s="10"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1861,9 @@
         <v>15</v>
       </c>
       <c r="X18" s="7"/>
-      <c r="AF18" s="8"/>
-    </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF18" s="10"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1871,12 +1871,12 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="17"/>
@@ -1884,18 +1884,18 @@
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L19" s="10"/>
+        <v>82</v>
+      </c>
+      <c r="L19" s="8"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="8"/>
+      <c r="P19" s="10"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1912,9 +1912,9 @@
         <v>16</v>
       </c>
       <c r="X19" s="7"/>
-      <c r="AF19" s="8"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF19" s="10"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1922,35 +1922,35 @@
         <v>18</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
+      <c r="L20" s="8"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="8"/>
+      <c r="P20" s="10"/>
       <c r="X20" s="7"/>
-      <c r="AF20" s="8"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF20" s="10"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1960,12 +1960,12 @@
       <c r="C21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="17"/>
@@ -1973,20 +1973,20 @@
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
+      <c r="L21" s="8"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="8"/>
+      <c r="P21" s="10"/>
       <c r="X21" s="7"/>
-      <c r="AF21" s="8"/>
-    </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF21" s="10"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1994,12 +1994,12 @@
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="17"/>
@@ -2007,22 +2007,22 @@
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L22" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="L22" s="8"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="8"/>
+      <c r="P22" s="10"/>
       <c r="X22" s="7"/>
-      <c r="AF22" s="8"/>
-    </row>
-    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF22" s="10"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2030,15 +2030,15 @@
         <v>29</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="2">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="10"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="8"/>
+      <c r="P23" s="10"/>
       <c r="X23" s="7"/>
-      <c r="AF23" s="8"/>
-    </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF23" s="10"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2066,12 +2066,12 @@
       <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="17"/>
@@ -2079,20 +2079,20 @@
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K24" s="9"/>
-      <c r="L24" s="10"/>
+      <c r="L24" s="8"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="8"/>
+      <c r="P24" s="10"/>
       <c r="X24" s="7"/>
-      <c r="AF24" s="8"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF24" s="10"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2100,12 +2100,12 @@
         <v>34</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="17"/>
@@ -2113,20 +2113,20 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="10"/>
+      <c r="L25" s="8"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="8"/>
+      <c r="P25" s="10"/>
       <c r="X25" s="7"/>
-      <c r="AF25" s="8"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF25" s="10"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2134,37 +2134,37 @@
         <v>35</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K26" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="L26" s="10"/>
+      <c r="L26" s="8"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="8"/>
+      <c r="P26" s="10"/>
       <c r="X26" s="7"/>
-      <c r="AF26" s="8"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF26" s="10"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2174,12 +2174,12 @@
       <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="17"/>
@@ -2187,20 +2187,20 @@
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
+      <c r="L27" s="8"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="8"/>
+      <c r="P27" s="10"/>
       <c r="X27" s="7"/>
-      <c r="AF27" s="8"/>
-    </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF27" s="10"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2208,12 +2208,12 @@
         <v>31</v>
       </c>
       <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
+      <c r="D28" s="8"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="17"/>
@@ -2221,20 +2221,20 @@
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
+      <c r="L28" s="8"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="8"/>
+      <c r="P28" s="10"/>
       <c r="X28" s="7"/>
-      <c r="AF28" s="8"/>
-    </row>
-    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF28" s="10"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2242,45 +2242,45 @@
         <v>32</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
+      <c r="D29" s="8"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="10"/>
+      <c r="L29" s="8"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="8"/>
+      <c r="P29" s="10"/>
       <c r="X29" s="7"/>
-      <c r="AF29" s="8"/>
-    </row>
-    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF29" s="10"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="D30" s="8"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -2291,33 +2291,33 @@
         <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="10"/>
+      <c r="L30" s="8"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="8"/>
+      <c r="P30" s="10"/>
       <c r="X30" s="7"/>
-      <c r="AF30" s="8"/>
-    </row>
-    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF30" s="10"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
+      <c r="D31" s="8"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="17"/>
@@ -2325,33 +2325,33 @@
         <v>28</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="10"/>
+      <c r="L31" s="8"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="8"/>
+      <c r="P31" s="10"/>
       <c r="X31" s="7"/>
-      <c r="AF31" s="8"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF31" s="10"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
+      <c r="D32" s="8"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="17"/>
@@ -2359,75 +2359,75 @@
         <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L32" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="L32" s="8"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="8"/>
+      <c r="P32" s="10"/>
       <c r="X32" s="7"/>
-      <c r="AF32" s="8"/>
-    </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF32" s="10"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="10"/>
+      <c r="L33" s="8"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="8"/>
+      <c r="P33" s="10"/>
       <c r="X33" s="7"/>
-      <c r="AF33" s="8"/>
-    </row>
-    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF33" s="10"/>
+    </row>
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="D34" s="8"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="17"/>
@@ -2435,33 +2435,33 @@
         <v>31</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="10"/>
+      <c r="L34" s="8"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="8"/>
+      <c r="P34" s="10"/>
       <c r="X34" s="7"/>
-      <c r="AF34" s="8"/>
-    </row>
-    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF34" s="10"/>
+    </row>
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="17"/>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="10"/>
+      <c r="L35" s="8"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="8"/>
+      <c r="P35" s="10"/>
       <c r="X35" s="7"/>
-      <c r="AF35" s="8"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF35" s="10"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2497,53 +2497,53 @@
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="I37" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
       <c r="H38" s="15"/>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2551,9 +2551,9 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="D39" s="8"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H39" s="15"/>
       <c r="I39" s="3" t="s">
@@ -2571,9 +2571,9 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L39" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="L39" s="8"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2581,10 +2581,10 @@
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>1</v>
       </c>
@@ -2594,7 +2594,7 @@
       <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="10"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
@@ -2608,16 +2608,16 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="L40" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="L40" s="8"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
@@ -2639,14 +2639,14 @@
         <v>3</v>
       </c>
       <c r="K41" s="9"/>
-      <c r="L41" s="10"/>
+      <c r="L41" s="8"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
+      <c r="D42" s="8"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
@@ -2668,14 +2668,14 @@
         <v>4</v>
       </c>
       <c r="K42" s="9"/>
-      <c r="L42" s="10"/>
+      <c r="L42" s="8"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>4</v>
       </c>
@@ -2685,7 +2685,7 @@
       <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="10"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -2699,14 +2699,14 @@
         <v>5</v>
       </c>
       <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
+      <c r="L43" s="8"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>5</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
@@ -2728,14 +2728,14 @@
         <v>6</v>
       </c>
       <c r="K44" s="9"/>
-      <c r="L44" s="10"/>
+      <c r="L44" s="8"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>6</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
+      <c r="D45" s="8"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
@@ -2757,24 +2757,24 @@
         <v>7</v>
       </c>
       <c r="K45" s="9"/>
-      <c r="L45" s="10"/>
+      <c r="L45" s="8"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="D46" s="8"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
@@ -2785,25 +2785,25 @@
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K46" s="9"/>
-      <c r="L46" s="10"/>
+      <c r="L46" s="8"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
@@ -2814,25 +2814,25 @@
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K47" s="9"/>
-      <c r="L47" s="10"/>
+      <c r="L47" s="8"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
+      <c r="D48" s="8"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
@@ -2843,27 +2843,27 @@
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K48" s="9"/>
-      <c r="L48" s="10"/>
+      <c r="L48" s="8"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="10"/>
+        <v>80</v>
+      </c>
+      <c r="D49" s="8"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
@@ -2874,25 +2874,25 @@
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K49" s="9"/>
-      <c r="L49" s="10"/>
+      <c r="L49" s="8"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
+      <c r="D50" s="8"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
@@ -2903,25 +2903,25 @@
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K50" s="9"/>
-      <c r="L50" s="10"/>
+      <c r="L50" s="8"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
+      <c r="D51" s="8"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
@@ -2932,27 +2932,27 @@
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
+      <c r="L51" s="8"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="D52" s="8"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
@@ -2963,27 +2963,27 @@
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L52" s="10"/>
+        <v>99</v>
+      </c>
+      <c r="L52" s="8"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="9"/>
-      <c r="D53" s="10"/>
+      <c r="D53" s="8"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
@@ -2994,25 +2994,25 @@
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K53" s="9"/>
-      <c r="L53" s="10"/>
+      <c r="L53" s="8"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
@@ -3023,27 +3023,27 @@
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K54" s="9"/>
-      <c r="L54" s="10"/>
+      <c r="L54" s="8"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>16</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D55" s="10"/>
+        <v>82</v>
+      </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
@@ -3054,27 +3054,27 @@
         <v>16</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L55" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="L55" s="8"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>17</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" s="9"/>
-      <c r="D56" s="10"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
@@ -3085,25 +3085,25 @@
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="10"/>
+      <c r="L56" s="8"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>18</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" s="9"/>
-      <c r="D57" s="10"/>
+      <c r="D57" s="8"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
@@ -3114,27 +3114,27 @@
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="10"/>
+      <c r="L57" s="8"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="D58" s="8"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
@@ -3145,27 +3145,27 @@
         <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L58" s="10"/>
+        <v>103</v>
+      </c>
+      <c r="L58" s="8"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>20</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
+      <c r="D59" s="8"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
@@ -3176,25 +3176,25 @@
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="10"/>
+      <c r="L59" s="8"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="9"/>
-      <c r="D60" s="10"/>
+      <c r="D60" s="8"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
@@ -3206,22 +3206,22 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="10"/>
+      <c r="L60" s="8"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>22</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="10"/>
+      <c r="D61" s="8"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
@@ -3233,24 +3233,24 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="10"/>
+      <c r="L61" s="8"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="8"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
@@ -3262,22 +3262,22 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="10"/>
+      <c r="L62" s="8"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="8"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
@@ -3289,22 +3289,22 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="10"/>
+      <c r="L63" s="8"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>25</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="8"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
@@ -3316,24 +3316,24 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="10"/>
+      <c r="L64" s="8"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>26</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="D65" s="8"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
@@ -3345,22 +3345,22 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="10"/>
+      <c r="L65" s="8"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>27</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="8"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
@@ -3372,20 +3372,20 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="10"/>
+      <c r="L66" s="8"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>28</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="8"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
@@ -3397,20 +3397,20 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="8"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>29</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="8"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
@@ -3422,20 +3422,20 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="8"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>30</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="8"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
@@ -3447,20 +3447,20 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="8"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>31</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="10"/>
+      <c r="D70" s="8"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
@@ -3472,20 +3472,20 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="8"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>32</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="10"/>
+      <c r="D71" s="8"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="8"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3506,6 +3506,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
@@ -3522,50 +3566,6 @@
     <mergeCell ref="H1:H35"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K22:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eafacaeacfb09265/Skrivebord/! github/EISS/documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4AC2FC26-C10F-460A-9837-C319B020F622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49378A5C-6501-48F7-820C-887BE656F848}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D5A160-1793-408D-AE30-941C16F66750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="124">
   <si>
     <t>Freq:</t>
   </si>
@@ -149,9 +149,6 @@
     <t>selection coordinate</t>
   </si>
   <si>
-    <t>new check azim</t>
-  </si>
-  <si>
     <t>new check elev</t>
   </si>
   <si>
@@ -399,6 +396,18 @@
   </si>
   <si>
     <t>new check dist nvm 01trigger</t>
+  </si>
+  <si>
+    <t>plane rwr not directional</t>
+  </si>
+  <si>
+    <t>disregard this, not in use</t>
+  </si>
+  <si>
+    <t>new check azim nvm 01ACM</t>
+  </si>
+  <si>
+    <t>ACM Mode</t>
   </si>
 </sst>
 </file>
@@ -585,13 +594,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,124 +939,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA91CC7-EF17-44C0-8F91-86ED01CBB552}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="1"/>
-    <col min="9" max="9" width="7.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="1"/>
-    <col min="14" max="14" width="11.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="1"/>
-    <col min="17" max="17" width="7.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="7.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
     <col min="19" max="19" width="8" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="12" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.44140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.109375" style="1"/>
-    <col min="25" max="25" width="6.88671875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.88671875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="19.44140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="2.6640625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5546875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16.44140625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.44140625" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.109375" style="1"/>
+    <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="1"/>
+    <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.42578125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="X1" s="7"/>
+      <c r="AF1" s="8"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="X2" s="7"/>
+      <c r="AF2" s="8"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="X1" s="7"/>
-      <c r="AF1" s="10"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X2" s="7"/>
-      <c r="AF2" s="10"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1055,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="3" t="s">
@@ -1065,9 +1074,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="L3" s="10"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1075,28 +1084,28 @@
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="P3" s="8"/>
       <c r="Q3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="X3" s="7"/>
-      <c r="AF3" s="10"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF3" s="8"/>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1106,15 +1115,15 @@
       <c r="C4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4" s="17"/>
       <c r="I4" s="2">
@@ -1126,13 +1135,13 @@
       <c r="K4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="8"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="10"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1149,9 +1158,9 @@
         <v>1</v>
       </c>
       <c r="X4" s="7"/>
-      <c r="AF4" s="10"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF4" s="8"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1159,12 +1168,12 @@
         <v>3</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="17"/>
@@ -1175,13 +1184,13 @@
         <v>3</v>
       </c>
       <c r="K5" s="9"/>
-      <c r="L5" s="8"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="10"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1198,9 +1207,9 @@
         <v>2</v>
       </c>
       <c r="X5" s="7"/>
-      <c r="AF5" s="10"/>
-    </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF5" s="8"/>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1208,15 +1217,15 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="2">
@@ -1226,13 +1235,13 @@
         <v>4</v>
       </c>
       <c r="K6" s="9"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="10"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1249,9 +1258,9 @@
         <v>3</v>
       </c>
       <c r="X6" s="7"/>
-      <c r="AF6" s="10"/>
-    </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF6" s="8"/>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1261,15 +1270,15 @@
       <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="2">
@@ -1281,13 +1290,13 @@
       <c r="K7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="10"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1304,9 +1313,9 @@
         <v>4</v>
       </c>
       <c r="X7" s="7"/>
-      <c r="AF7" s="10"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF7" s="8"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -1314,15 +1323,15 @@
         <v>6</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="2">
@@ -1332,13 +1341,13 @@
         <v>6</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="10"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1355,9 +1364,9 @@
         <v>5</v>
       </c>
       <c r="X8" s="7"/>
-      <c r="AF8" s="10"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF8" s="8"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1365,12 +1374,12 @@
         <v>7</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="17"/>
@@ -1381,13 +1390,13 @@
         <v>7</v>
       </c>
       <c r="K9" s="9"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="10"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1404,9 +1413,9 @@
         <v>6</v>
       </c>
       <c r="X9" s="7"/>
-      <c r="AF9" s="10"/>
-    </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF9" s="8"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1416,33 +1425,33 @@
       <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="L10" s="10"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="10"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1459,9 +1468,9 @@
         <v>7</v>
       </c>
       <c r="X10" s="7"/>
-      <c r="AF10" s="10"/>
-    </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF10" s="8"/>
+    </row>
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -1469,12 +1478,12 @@
         <v>9</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="17"/>
@@ -1482,16 +1491,16 @@
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="10"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1508,9 +1517,9 @@
         <v>8</v>
       </c>
       <c r="X11" s="7"/>
-      <c r="AF11" s="10"/>
-    </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF11" s="8"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -1518,31 +1527,31 @@
         <v>10</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="10"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1559,9 +1568,9 @@
         <v>9</v>
       </c>
       <c r="X12" s="7"/>
-      <c r="AF12" s="10"/>
-    </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF12" s="8"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -1571,12 +1580,12 @@
       <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
@@ -1584,18 +1593,18 @@
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L13" s="8"/>
+        <v>79</v>
+      </c>
+      <c r="L13" s="10"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="10"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1612,9 +1621,9 @@
         <v>10</v>
       </c>
       <c r="X13" s="7"/>
-      <c r="AF13" s="10"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF13" s="8"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1622,31 +1631,31 @@
         <v>12</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="10"/>
+      <c r="P14" s="8"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1663,9 +1672,9 @@
         <v>11</v>
       </c>
       <c r="X14" s="7"/>
-      <c r="AF14" s="10"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF14" s="8"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -1675,7 +1684,7 @@
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1684,16 +1693,16 @@
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="10"/>
+      <c r="P15" s="8"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1710,9 +1719,9 @@
         <v>12</v>
       </c>
       <c r="X15" s="7"/>
-      <c r="AF15" s="10"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF15" s="8"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1720,7 +1729,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1731,18 +1740,18 @@
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L16" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="L16" s="10"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="10"/>
+      <c r="P16" s="8"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1759,9 +1768,9 @@
         <v>13</v>
       </c>
       <c r="X16" s="7"/>
-      <c r="AF16" s="10"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF16" s="8"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1769,31 +1778,31 @@
         <v>15</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K17" s="9"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="10"/>
+      <c r="P17" s="8"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1810,9 +1819,9 @@
         <v>14</v>
       </c>
       <c r="X17" s="7"/>
-      <c r="AF17" s="10"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF17" s="8"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1822,12 +1831,12 @@
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="17"/>
@@ -1835,16 +1844,16 @@
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K18" s="9"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="10"/>
+      <c r="P18" s="8"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1861,9 +1870,9 @@
         <v>15</v>
       </c>
       <c r="X18" s="7"/>
-      <c r="AF18" s="10"/>
-    </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF18" s="8"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -1871,12 +1880,12 @@
         <v>17</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="17"/>
@@ -1884,18 +1893,18 @@
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="L19" s="10"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="10"/>
+      <c r="P19" s="8"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1912,9 +1921,9 @@
         <v>16</v>
       </c>
       <c r="X19" s="7"/>
-      <c r="AF19" s="10"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF19" s="8"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1922,35 +1931,42 @@
         <v>18</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K20" s="9"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="10"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
       <c r="X20" s="7"/>
-      <c r="AF20" s="10"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF20" s="8"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1960,12 +1976,12 @@
       <c r="C21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="17"/>
@@ -1973,20 +1989,20 @@
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="10"/>
+      <c r="P21" s="8"/>
       <c r="X21" s="7"/>
-      <c r="AF21" s="10"/>
-    </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF21" s="8"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1994,12 +2010,12 @@
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="17"/>
@@ -2007,22 +2023,22 @@
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L22" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="L22" s="10"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="10"/>
+      <c r="P22" s="8"/>
       <c r="X22" s="7"/>
-      <c r="AF22" s="10"/>
-    </row>
-    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF22" s="8"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -2030,15 +2046,15 @@
         <v>29</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="2">
@@ -2046,17 +2062,17 @@
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="10"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="10"/>
+      <c r="P23" s="8"/>
       <c r="X23" s="7"/>
-      <c r="AF23" s="10"/>
-    </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF23" s="8"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -2066,12 +2082,12 @@
       <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="17"/>
@@ -2079,20 +2095,20 @@
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K24" s="9"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="10"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="10"/>
+      <c r="P24" s="8"/>
       <c r="X24" s="7"/>
-      <c r="AF24" s="10"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF24" s="8"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -2100,12 +2116,12 @@
         <v>34</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="17"/>
@@ -2113,20 +2129,20 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K25" s="9"/>
-      <c r="L25" s="8"/>
+      <c r="L25" s="10"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="10"/>
+      <c r="P25" s="8"/>
       <c r="X25" s="7"/>
-      <c r="AF25" s="10"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF25" s="8"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -2134,37 +2150,37 @@
         <v>35</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K26" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="L26" s="8"/>
+      <c r="L26" s="10"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="10"/>
+      <c r="P26" s="8"/>
       <c r="X26" s="7"/>
-      <c r="AF26" s="10"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF26" s="8"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -2174,12 +2190,12 @@
       <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="17"/>
@@ -2187,20 +2203,20 @@
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K27" s="9"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="10"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="10"/>
+      <c r="P27" s="8"/>
       <c r="X27" s="7"/>
-      <c r="AF27" s="10"/>
-    </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF27" s="8"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -2208,12 +2224,12 @@
         <v>31</v>
       </c>
       <c r="C28" s="9"/>
-      <c r="D28" s="8"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="17"/>
@@ -2221,20 +2237,20 @@
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="10"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="10"/>
+      <c r="P28" s="8"/>
       <c r="X28" s="7"/>
-      <c r="AF28" s="10"/>
-    </row>
-    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF28" s="8"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -2242,45 +2258,45 @@
         <v>32</v>
       </c>
       <c r="C29" s="9"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="10"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="10"/>
+      <c r="P29" s="8"/>
       <c r="X29" s="7"/>
-      <c r="AF29" s="10"/>
-    </row>
-    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF29" s="8"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="D30" s="10"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -2291,33 +2307,33 @@
         <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
+      <c r="L30" s="10"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="10"/>
+      <c r="P30" s="8"/>
       <c r="X30" s="7"/>
-      <c r="AF30" s="10"/>
-    </row>
-    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF30" s="8"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="C31" s="9"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="10"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="17"/>
@@ -2325,33 +2341,33 @@
         <v>28</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="10"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="10"/>
+      <c r="P31" s="8"/>
       <c r="X31" s="7"/>
-      <c r="AF31" s="10"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF31" s="8"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="17"/>
@@ -2359,75 +2375,75 @@
         <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L32" s="8"/>
+        <v>103</v>
+      </c>
+      <c r="L32" s="10"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="10"/>
+      <c r="P32" s="8"/>
       <c r="X32" s="7"/>
-      <c r="AF32" s="10"/>
-    </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF32" s="8"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="D33" s="10"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="10"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="10"/>
+      <c r="P33" s="8"/>
       <c r="X33" s="7"/>
-      <c r="AF33" s="10"/>
-    </row>
-    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF33" s="8"/>
+    </row>
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="D34" s="10"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="17"/>
@@ -2435,33 +2451,33 @@
         <v>31</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="10"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="10"/>
+      <c r="P34" s="8"/>
       <c r="X34" s="7"/>
-      <c r="AF34" s="10"/>
-    </row>
-    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF34" s="8"/>
+    </row>
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="17"/>
@@ -2470,17 +2486,17 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="10"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="10"/>
+      <c r="P35" s="8"/>
       <c r="X35" s="7"/>
-      <c r="AF35" s="10"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AF35" s="8"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2497,53 +2513,53 @@
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="I37" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
       <c r="H38" s="15"/>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2551,9 +2567,9 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="D39" s="10"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2561,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H39" s="15"/>
       <c r="I39" s="3" t="s">
@@ -2571,9 +2587,9 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L39" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="L39" s="10"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2581,10 +2597,10 @@
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>1</v>
       </c>
@@ -2594,7 +2610,7 @@
       <c r="C40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="8"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
@@ -2608,16 +2624,16 @@
         <v>2</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L40" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="L40" s="10"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2</v>
       </c>
@@ -2625,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="9"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
@@ -2639,14 +2655,14 @@
         <v>3</v>
       </c>
       <c r="K41" s="9"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="10"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -2654,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="9"/>
-      <c r="D42" s="8"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
@@ -2668,14 +2684,14 @@
         <v>4</v>
       </c>
       <c r="K42" s="9"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="10"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>4</v>
       </c>
@@ -2685,7 +2701,7 @@
       <c r="C43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="8"/>
+      <c r="D43" s="10"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -2699,14 +2715,14 @@
         <v>5</v>
       </c>
       <c r="K43" s="9"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="10"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>5</v>
       </c>
@@ -2714,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="9"/>
-      <c r="D44" s="8"/>
+      <c r="D44" s="10"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
@@ -2728,14 +2744,14 @@
         <v>6</v>
       </c>
       <c r="K44" s="9"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="10"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>6</v>
       </c>
@@ -2743,7 +2759,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="9"/>
-      <c r="D45" s="8"/>
+      <c r="D45" s="10"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
@@ -2757,24 +2773,24 @@
         <v>7</v>
       </c>
       <c r="K45" s="9"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="10"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="D46" s="10"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
@@ -2785,25 +2801,25 @@
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K46" s="9"/>
-      <c r="L46" s="8"/>
+      <c r="L46" s="10"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" s="9"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
@@ -2814,25 +2830,25 @@
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K47" s="9"/>
-      <c r="L47" s="8"/>
+      <c r="L47" s="10"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" s="9"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="10"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
@@ -2843,27 +2859,27 @@
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K48" s="9"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="10"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="8"/>
+        <v>79</v>
+      </c>
+      <c r="D49" s="10"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
@@ -2874,25 +2890,25 @@
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K49" s="9"/>
-      <c r="L49" s="8"/>
+      <c r="L49" s="10"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" s="9"/>
-      <c r="D50" s="8"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
@@ -2903,25 +2919,25 @@
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K50" s="9"/>
-      <c r="L50" s="8"/>
+      <c r="L50" s="10"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51" s="9"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="10"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
@@ -2932,27 +2948,27 @@
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K51" s="9"/>
-      <c r="L51" s="8"/>
+      <c r="L51" s="10"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="D52" s="10"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
@@ -2963,27 +2979,27 @@
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L52" s="8"/>
+        <v>98</v>
+      </c>
+      <c r="L52" s="10"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="9"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
@@ -2994,25 +3010,25 @@
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K53" s="9"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="10"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="9"/>
-      <c r="D54" s="8"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
@@ -3023,27 +3039,27 @@
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K54" s="9"/>
-      <c r="L54" s="8"/>
+      <c r="L54" s="10"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>16</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D55" s="10"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
@@ -3054,27 +3070,27 @@
         <v>16</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L55" s="8"/>
+        <v>103</v>
+      </c>
+      <c r="L55" s="10"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>17</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" s="9"/>
-      <c r="D56" s="8"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
@@ -3085,25 +3101,25 @@
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="8"/>
+      <c r="L56" s="10"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>18</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" s="9"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
@@ -3114,27 +3130,27 @@
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="8"/>
+      <c r="L57" s="10"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" s="8"/>
+        <v>74</v>
+      </c>
+      <c r="D58" s="10"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
@@ -3145,27 +3161,27 @@
         <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L58" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="L58" s="10"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>20</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="9"/>
-      <c r="D59" s="8"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
@@ -3176,25 +3192,25 @@
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="8"/>
+      <c r="L59" s="10"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="9"/>
-      <c r="D60" s="8"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
@@ -3206,22 +3222,22 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="8"/>
+      <c r="L60" s="10"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>22</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="8"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
@@ -3233,24 +3249,24 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="8"/>
+      <c r="L61" s="10"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" s="8"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
@@ -3262,22 +3278,22 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="8"/>
+      <c r="L62" s="10"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="8"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
@@ -3289,22 +3305,22 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="8"/>
+      <c r="L63" s="10"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>25</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="8"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
@@ -3316,24 +3332,24 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="8"/>
+      <c r="L64" s="10"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>26</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" s="8"/>
+        <v>103</v>
+      </c>
+      <c r="D65" s="10"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
@@ -3345,22 +3361,22 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="8"/>
+      <c r="L65" s="10"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>27</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="8"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
@@ -3372,20 +3388,22 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="8"/>
+      <c r="L66" s="10"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>28</v>
       </c>
-      <c r="B67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
@@ -3397,20 +3415,20 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="8"/>
+      <c r="L67" s="10"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>29</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="8"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
@@ -3422,20 +3440,20 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="8"/>
+      <c r="L68" s="10"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>30</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="8"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
@@ -3447,20 +3465,20 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="8"/>
+      <c r="L69" s="10"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>31</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="8"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
@@ -3472,20 +3490,20 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="8"/>
+      <c r="L70" s="10"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>32</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="10"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
@@ -3497,7 +3515,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="8"/>
+      <c r="L71" s="10"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3505,7 +3523,52 @@
       <c r="O71" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="61">
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C30:C32"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="G20:G22"/>
@@ -3522,50 +3585,6 @@
     <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="K22:K25"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D5A160-1793-408D-AE30-941C16F66750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB78BD11-35A0-45E7-B9D1-66BA854F8990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="119">
   <si>
     <t>Freq:</t>
   </si>
@@ -77,15 +77,6 @@
     <t>friend user2</t>
   </si>
   <si>
-    <t>msl x</t>
-  </si>
-  <si>
-    <t>msl y</t>
-  </si>
-  <si>
-    <t>msl z</t>
-  </si>
-  <si>
     <t>old r x</t>
   </si>
   <si>
@@ -101,9 +92,6 @@
     <t>friend xyz</t>
   </si>
   <si>
-    <t>msl xyz</t>
-  </si>
-  <si>
     <t>my rot</t>
   </si>
   <si>
@@ -137,27 +125,6 @@
     <t>new 3 elev</t>
   </si>
   <si>
-    <t>select x</t>
-  </si>
-  <si>
-    <t>select y</t>
-  </si>
-  <si>
-    <t>select z</t>
-  </si>
-  <si>
-    <t>selection coordinate</t>
-  </si>
-  <si>
-    <t>new check elev</t>
-  </si>
-  <si>
-    <t>new check data</t>
-  </si>
-  <si>
-    <t>new check current azim</t>
-  </si>
-  <si>
     <t>TWS</t>
   </si>
   <si>
@@ -173,9 +140,6 @@
     <t>viclink receive freq</t>
   </si>
   <si>
-    <t>msllink receive freq</t>
-  </si>
-  <si>
     <t>my user 1</t>
   </si>
   <si>
@@ -188,12 +152,6 @@
     <t>FOVX</t>
   </si>
   <si>
-    <t>time since detected scan radars</t>
-  </si>
-  <si>
-    <t>time since detected new check</t>
-  </si>
-  <si>
     <t>time since detected</t>
   </si>
   <si>
@@ -224,15 +182,6 @@
     <t>friendly trans z</t>
   </si>
   <si>
-    <t>missile trans1 x</t>
-  </si>
-  <si>
-    <t>missile trans1 y</t>
-  </si>
-  <si>
-    <t>missile trans1 z</t>
-  </si>
-  <si>
     <t>my username</t>
   </si>
   <si>
@@ -242,18 +191,9 @@
     <t>enemy trans1 index</t>
   </si>
   <si>
-    <t>enemy trans2 index</t>
-  </si>
-  <si>
     <t>friendly trans1 index</t>
   </si>
   <si>
-    <t>new check elevation slew</t>
-  </si>
-  <si>
-    <t>new check azim slew speed</t>
-  </si>
-  <si>
     <t>old check slew Y</t>
   </si>
   <si>
@@ -263,9 +203,6 @@
     <t>transmit indexes</t>
   </si>
   <si>
-    <t>new check radar slews</t>
-  </si>
-  <si>
     <t>old check radar slews</t>
   </si>
   <si>
@@ -281,9 +218,6 @@
     <t>friendly transmit 1</t>
   </si>
   <si>
-    <t>missile transmit 1</t>
-  </si>
-  <si>
     <t>selected target y</t>
   </si>
   <si>
@@ -296,15 +230,9 @@
     <t>selected target</t>
   </si>
   <si>
-    <t>missile trans1 index</t>
-  </si>
-  <si>
     <t>TSD</t>
   </si>
   <si>
-    <t>forward radar ang</t>
-  </si>
-  <si>
     <t>vel x</t>
   </si>
   <si>
@@ -395,19 +323,76 @@
     <t>RWR Shit</t>
   </si>
   <si>
-    <t>new check dist nvm 01trigger</t>
-  </si>
-  <si>
     <t>plane rwr not directional</t>
   </si>
   <si>
     <t>disregard this, not in use</t>
   </si>
   <si>
-    <t>new check azim nvm 01ACM</t>
-  </si>
-  <si>
     <t>ACM Mode</t>
+  </si>
+  <si>
+    <t>01 ACM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 01 trigger</t>
+  </si>
+  <si>
+    <t>time since detected scan radar 1</t>
+  </si>
+  <si>
+    <t>my rx</t>
+  </si>
+  <si>
+    <t>my ry</t>
+  </si>
+  <si>
+    <t>my rz</t>
+  </si>
+  <si>
+    <t>friend selected x</t>
+  </si>
+  <si>
+    <t>friend selected y</t>
+  </si>
+  <si>
+    <t>friend selected z</t>
+  </si>
+  <si>
+    <t>time since detected scan radar 2</t>
+  </si>
+  <si>
+    <t>time since detected scan radar 3</t>
+  </si>
+  <si>
+    <t>new2 data</t>
+  </si>
+  <si>
+    <t>new 2 dist</t>
+  </si>
+  <si>
+    <t>new 2 azim</t>
+  </si>
+  <si>
+    <t>new 2 elev</t>
+  </si>
+  <si>
+    <t>radar 1 ang (front sweep)</t>
+  </si>
+  <si>
+    <t>radar 2 ang (front circle)</t>
+  </si>
+  <si>
+    <t>radar 3 ang (rear circle)</t>
+  </si>
+  <si>
+    <t>enemy trans index</t>
+  </si>
+  <si>
+    <t>friendly trans index</t>
+  </si>
+  <si>
+    <t>friendly selected</t>
   </si>
 </sst>
 </file>
@@ -571,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,9 +575,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -623,6 +605,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -942,7 +939,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
@@ -976,75 +973,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="10" t="s">
+      <c r="A1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="AF1" s="7"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="X1" s="7"/>
-      <c r="AF1" s="8"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="X2" s="7"/>
-      <c r="AF2" s="8"/>
+      <c r="AF2" s="7"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1054,9 +1049,9 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1064,9 +1059,9 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="H3" s="16"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1074,9 +1069,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="L3" s="9"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1084,26 +1079,25 @@
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="P3" s="7"/>
       <c r="Q3" s="1" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" s="7"/>
-      <c r="AF3" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="AF3" s="7"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1112,36 +1106,36 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="10"/>
+      <c r="C4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="16"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="10"/>
+      <c r="K4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="9"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="8"/>
+      <c r="P4" s="7"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1157,8 +1151,7 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="X4" s="7"/>
-      <c r="AF4" s="8"/>
+      <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1167,30 +1160,30 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="16"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="8"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1206,8 +1199,7 @@
       <c r="U5" s="1">
         <v>2</v>
       </c>
-      <c r="X5" s="7"/>
-      <c r="AF5" s="8"/>
+      <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1216,32 +1208,32 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="H6" s="16"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="8"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1257,46 +1249,41 @@
       <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="X6" s="7"/>
-      <c r="AF6" s="8"/>
+      <c r="AF6" s="7"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="17"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="16"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="9"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="8"/>
+      <c r="P7" s="7"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1312,42 +1299,37 @@
       <c r="U7" s="1">
         <v>4</v>
       </c>
-      <c r="X7" s="7"/>
-      <c r="AF7" s="8"/>
+      <c r="AF7" s="7"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
+        <v>102</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="17"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
+        <v>102</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="8"/>
+      <c r="P8" s="7"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1363,40 +1345,37 @@
       <c r="U8" s="1">
         <v>5</v>
       </c>
-      <c r="X8" s="7"/>
-      <c r="AF8" s="8"/>
+      <c r="AF8" s="7"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+        <v>103</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
+        <v>103</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="9"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="8"/>
+      <c r="P9" s="7"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1412,8 +1391,7 @@
       <c r="U9" s="1">
         <v>6</v>
       </c>
-      <c r="X9" s="7"/>
-      <c r="AF9" s="8"/>
+      <c r="AF9" s="7"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1422,36 +1400,36 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="10"/>
+      <c r="C10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="9"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="17"/>
+        <v>52</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="16"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L10" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="9"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="8"/>
+      <c r="P10" s="7"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1467,8 +1445,7 @@
       <c r="U10" s="1">
         <v>7</v>
       </c>
-      <c r="X10" s="7"/>
-      <c r="AF10" s="8"/>
+      <c r="AF10" s="7"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1477,30 +1454,30 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="17"/>
+        <v>53</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="8"/>
+      <c r="P11" s="7"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1516,8 +1493,7 @@
       <c r="U11" s="1">
         <v>8</v>
       </c>
-      <c r="X11" s="7"/>
-      <c r="AF11" s="8"/>
+      <c r="AF11" s="7"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1526,32 +1502,32 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="16"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="8"/>
+      <c r="P12" s="7"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1567,8 +1543,7 @@
       <c r="U12" s="1">
         <v>9</v>
       </c>
-      <c r="X12" s="7"/>
-      <c r="AF12" s="8"/>
+      <c r="AF12" s="7"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1577,34 +1552,34 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="10"/>
+      <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="16"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="L13" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="9"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="8"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1620,8 +1595,7 @@
       <c r="U13" s="1">
         <v>10</v>
       </c>
-      <c r="X13" s="7"/>
-      <c r="AF13" s="8"/>
+      <c r="AF13" s="7"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1630,32 +1604,32 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="17"/>
+        <v>78</v>
+      </c>
+      <c r="H14" s="16"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
+        <v>43</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="8"/>
+      <c r="P14" s="7"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1671,38 +1645,37 @@
       <c r="U14" s="1">
         <v>11</v>
       </c>
-      <c r="X14" s="7"/>
-      <c r="AF14" s="8"/>
+      <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="9"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="8"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1718,40 +1691,39 @@
       <c r="U15" s="1">
         <v>12</v>
       </c>
-      <c r="X15" s="7"/>
-      <c r="AF15" s="8"/>
+      <c r="AF15" s="7"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+        <v>111</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="17"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="9"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="8"/>
+      <c r="P16" s="7"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1739,41 @@
       <c r="U16" s="1">
         <v>13</v>
       </c>
-      <c r="X16" s="7"/>
-      <c r="AF16" s="8"/>
+      <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+        <v>112</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="16"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="9"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="8"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1818,42 +1789,41 @@
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="X17" s="7"/>
-      <c r="AF17" s="8"/>
+      <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="9"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="16"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="9"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="8"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1869,42 +1839,41 @@
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="X18" s="7"/>
-      <c r="AF18" s="8"/>
+      <c r="AF18" s="7"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="17"/>
+        <v>41</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="16"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="9"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="8"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1920,644 +1889,609 @@
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="X19" s="7"/>
-      <c r="AF19" s="8"/>
+      <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="17"/>
+        <v>42</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="16"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
+        <v>105</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="9"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="X20" s="7"/>
-      <c r="AF20" s="8"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="9"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="17"/>
+        <v>43</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
+        <v>106</v>
+      </c>
+      <c r="K21" s="19"/>
+      <c r="L21" s="9"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="8"/>
-      <c r="X21" s="7"/>
-      <c r="AF21" s="8"/>
+      <c r="P21" s="7"/>
+      <c r="AF21" s="7"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="17"/>
+        <v>44</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="10"/>
+        <v>116</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22" s="9"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="8"/>
-      <c r="X22" s="7"/>
-      <c r="AF22" s="8"/>
+      <c r="P22" s="7"/>
+      <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" s="17"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="10"/>
+      <c r="J23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="9"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="8"/>
-      <c r="X23" s="7"/>
-      <c r="AF23" s="8"/>
+      <c r="P23" s="7"/>
+      <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="10"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="16"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="9"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="8"/>
-      <c r="X24" s="7"/>
-      <c r="AF24" s="8"/>
+      <c r="P24" s="7"/>
+      <c r="AF24" s="7"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="16"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="10"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="9"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="8"/>
-      <c r="X25" s="7"/>
-      <c r="AF25" s="8"/>
+      <c r="P25" s="7"/>
+      <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="17"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="16"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="L26" s="10"/>
+        <v>62</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="9"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="8"/>
-      <c r="X26" s="7"/>
-      <c r="AF26" s="8"/>
+      <c r="P26" s="7"/>
+      <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="C27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="16"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
+        <v>60</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="9"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="8"/>
-      <c r="X27" s="7"/>
-      <c r="AF27" s="8"/>
+      <c r="P27" s="7"/>
+      <c r="AF27" s="7"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
+        <v>27</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="17"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="16"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="9"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="8"/>
-      <c r="X28" s="7"/>
-      <c r="AF28" s="8"/>
+      <c r="P28" s="7"/>
+      <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
+        <v>28</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H29" s="17"/>
+        <v>116</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="16"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="10"/>
+      <c r="L29" s="9"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="8"/>
-      <c r="X29" s="7"/>
-      <c r="AF29" s="8"/>
+      <c r="P29" s="7"/>
+      <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="10"/>
+        <v>99</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="16"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="10"/>
+      <c r="L30" s="9"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="8"/>
-      <c r="X30" s="7"/>
-      <c r="AF30" s="8"/>
+      <c r="P30" s="7"/>
+      <c r="AF30" s="7"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="17"/>
+        <v>117</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="16"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="10"/>
+      <c r="L31" s="9"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="8"/>
-      <c r="X31" s="7"/>
-      <c r="AF31" s="8"/>
+      <c r="P31" s="7"/>
+      <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="9"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="17"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L32" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="L32" s="9"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="8"/>
-      <c r="X32" s="7"/>
-      <c r="AF32" s="8"/>
+      <c r="P32" s="7"/>
+      <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="10"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="17"/>
+        <v>62</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="16"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="10"/>
+      <c r="L33" s="9"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="8"/>
-      <c r="X33" s="7"/>
-      <c r="AF33" s="8"/>
+      <c r="P33" s="7"/>
+      <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="10"/>
+        <v>107</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="9"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="16"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="10"/>
+      <c r="L34" s="9"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="8"/>
-      <c r="X34" s="7"/>
-      <c r="AF34" s="8"/>
+      <c r="P34" s="7"/>
+      <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
+        <v>108</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="17"/>
+        <v>61</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="16"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
-      <c r="J35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="10"/>
+      <c r="L35" s="9"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="8"/>
-      <c r="X35" s="7"/>
-      <c r="AF35" s="8"/>
+      <c r="P35" s="7"/>
+      <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="13"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="12"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
+      <c r="A37" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
+      <c r="A38" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2567,9 +2501,9 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="D39" s="9"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2577,9 +2511,9 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H39" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="H39" s="14"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2587,9 +2521,9 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L39" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="L39" s="9"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2597,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
@@ -2607,26 +2541,26 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="10"/>
+      <c r="C40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="9"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="15"/>
+      <c r="H40" s="14"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L40" s="10"/>
+      <c r="K40" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L40" s="9"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2640,22 +2574,22 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="15"/>
+      <c r="H41" s="14"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="10"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="9"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2669,22 +2603,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="15"/>
+      <c r="H42" s="14"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="10"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="9"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2698,24 +2632,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="10"/>
+      <c r="C43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="9"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="15"/>
+      <c r="H43" s="14"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="9"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2729,22 +2663,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="15"/>
+      <c r="H44" s="14"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="10"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="9"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2758,22 +2692,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="15"/>
+      <c r="H45" s="14"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="10"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="9"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2785,26 +2719,26 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="9"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="15"/>
+      <c r="H46" s="14"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="K46" s="8"/>
+      <c r="L46" s="9"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2816,24 +2750,24 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="9"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="15"/>
+      <c r="H47" s="14"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="10"/>
+        <v>66</v>
+      </c>
+      <c r="K47" s="8"/>
+      <c r="L47" s="9"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2845,24 +2779,24 @@
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="15"/>
+      <c r="H48" s="14"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="K48" s="8"/>
+      <c r="L48" s="9"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2874,26 +2808,26 @@
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="9"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="15"/>
+      <c r="H49" s="14"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="10"/>
+        <v>68</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="9"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2905,24 +2839,24 @@
         <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
+        <v>43</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="15"/>
+      <c r="H50" s="14"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="K50" s="8"/>
+      <c r="L50" s="9"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2934,24 +2868,24 @@
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="15"/>
+      <c r="H51" s="14"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="K51" s="8"/>
+      <c r="L51" s="9"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2963,28 +2897,28 @@
         <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="10"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="15"/>
+      <c r="H52" s="14"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L52" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L52" s="9"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2996,24 +2930,24 @@
         <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="15"/>
+      <c r="H53" s="14"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="K53" s="8"/>
+      <c r="L53" s="9"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -3025,24 +2959,24 @@
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="15"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="9"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3053,29 +2987,25 @@
       <c r="A55" s="2">
         <v>16</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" s="10"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="15"/>
+      <c r="H55" s="14"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L55" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="L55" s="9"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3086,25 +3016,23 @@
       <c r="A56" s="2">
         <v>17</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="10"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="15"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K56" s="4"/>
-      <c r="L56" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="K56" s="2"/>
+      <c r="L56" s="9"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3115,25 +3043,23 @@
       <c r="A57" s="2">
         <v>18</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="10"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="15"/>
+      <c r="H57" s="14"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K57" s="4"/>
-      <c r="L57" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="K57" s="2"/>
+      <c r="L57" s="9"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3145,28 +3071,28 @@
         <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D58" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="9"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="15"/>
+      <c r="H58" s="14"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L58" s="10"/>
+        <v>78</v>
+      </c>
+      <c r="L58" s="9"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3177,25 +3103,23 @@
       <c r="A59" s="2">
         <v>20</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="15"/>
+      <c r="H59" s="14"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="K59" s="2"/>
+      <c r="L59" s="9"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3207,22 +3131,22 @@
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="C60" s="8"/>
+      <c r="D60" s="9"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="15"/>
+      <c r="H60" s="14"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="10"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="9"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3233,23 +3157,21 @@
       <c r="A61" s="2">
         <v>22</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="10"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="15"/>
+      <c r="H61" s="14"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="10"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="9"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3261,24 +3183,24 @@
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="D62" s="9"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="15"/>
+      <c r="H62" s="14"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="10"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="9"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3290,22 +3212,22 @@
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="15"/>
+      <c r="H63" s="14"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="10"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="9"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3317,22 +3239,22 @@
         <v>25</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="15"/>
+      <c r="H64" s="14"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="10"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="9"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3344,24 +3266,24 @@
         <v>26</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="D65" s="9"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="15"/>
+      <c r="H65" s="14"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="10"/>
+      <c r="L65" s="9"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3373,22 +3295,22 @@
         <v>27</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="15"/>
+      <c r="H66" s="14"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="10"/>
+      <c r="L66" s="9"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3400,22 +3322,22 @@
         <v>28</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="15"/>
+      <c r="H67" s="14"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="9"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3428,19 +3350,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="15"/>
+      <c r="H68" s="14"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="9"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3453,19 +3375,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="9"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="15"/>
+      <c r="H69" s="14"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="9"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3478,19 +3400,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="10"/>
+      <c r="D70" s="9"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="15"/>
+      <c r="H70" s="14"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="9"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3503,19 +3425,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="10"/>
+      <c r="D71" s="9"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="16"/>
+      <c r="H71" s="15"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="9"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3523,12 +3445,22 @@
       <c r="O71" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="54">
+    <mergeCell ref="C33:C35"/>
     <mergeCell ref="Q20:U20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
     <mergeCell ref="K40:K51"/>
     <mergeCell ref="A36:O36"/>
     <mergeCell ref="H37:H71"/>
@@ -3537,22 +3469,10 @@
     <mergeCell ref="L38:L71"/>
     <mergeCell ref="M38:O38"/>
     <mergeCell ref="K52:K54"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G8:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G17:G19"/>
     <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G29:G32"/>
     <mergeCell ref="K26:K28"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:C38"/>
@@ -3563,17 +3483,13 @@
     <mergeCell ref="C46:C48"/>
     <mergeCell ref="C40:C42"/>
     <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
     <mergeCell ref="D2:D35"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C30:C32"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
@@ -3584,7 +3500,6 @@
     <mergeCell ref="K13:K15"/>
     <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K22:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB78BD11-35A0-45E7-B9D1-66BA854F8990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B0C664-EEA1-4629-8040-D1414B9D1799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="123">
   <si>
     <t>Freq:</t>
   </si>
@@ -393,6 +393,18 @@
   </si>
   <si>
     <t>friendly selected</t>
+  </si>
+  <si>
+    <t>friend selected1 x</t>
+  </si>
+  <si>
+    <t>friend selected1 y</t>
+  </si>
+  <si>
+    <t>friend selected1 z</t>
+  </si>
+  <si>
+    <t>friendly selected transmit 1</t>
   </si>
 </sst>
 </file>
@@ -576,13 +588,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,21 +632,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -973,60 +985,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="AF1" s="7"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="AF1" s="14"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="9" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="7"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="14"/>
       <c r="Q2" s="1" t="s">
         <v>88</v>
       </c>
@@ -1039,7 +1051,7 @@
       <c r="T2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="7"/>
+      <c r="AF2" s="14"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1051,7 +1063,7 @@
       <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1073,7 @@
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="16"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1071,7 +1083,7 @@
       <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="9"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1093,7 @@
       <c r="O3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="7"/>
+      <c r="P3" s="14"/>
       <c r="Q3" s="1" t="s">
         <v>89</v>
       </c>
@@ -1097,7 +1109,7 @@
       <c r="U3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AF3" s="7"/>
+      <c r="AF3" s="14"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1106,36 +1118,36 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="16"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="9"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="7"/>
+      <c r="P4" s="14"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1151,7 +1163,7 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="AF4" s="7"/>
+      <c r="AF4" s="14"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1160,30 +1172,30 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="7"/>
+      <c r="P5" s="14"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1199,7 +1211,7 @@
       <c r="U5" s="1">
         <v>2</v>
       </c>
-      <c r="AF5" s="7"/>
+      <c r="AF5" s="14"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1208,8 +1220,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1219,21 +1231,21 @@
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="7"/>
+      <c r="P6" s="14"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1249,7 +1261,7 @@
       <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="AF6" s="7"/>
+      <c r="AF6" s="14"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1258,32 +1270,32 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="16"/>
+      <c r="H7" s="21"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="9"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="7"/>
+      <c r="P7" s="14"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1299,7 +1311,7 @@
       <c r="U7" s="1">
         <v>4</v>
       </c>
-      <c r="AF7" s="7"/>
+      <c r="AF7" s="14"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1308,28 +1320,28 @@
       <c r="B8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="16"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="7"/>
+      <c r="P8" s="14"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1345,7 +1357,7 @@
       <c r="U8" s="1">
         <v>5</v>
       </c>
-      <c r="AF8" s="7"/>
+      <c r="AF8" s="14"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1354,28 +1366,28 @@
       <c r="B9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="16"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="7"/>
+      <c r="P9" s="14"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1391,7 +1403,7 @@
       <c r="U9" s="1">
         <v>6</v>
       </c>
-      <c r="AF9" s="7"/>
+      <c r="AF9" s="14"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1400,36 +1412,36 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="7"/>
+      <c r="P10" s="14"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1445,7 +1457,7 @@
       <c r="U10" s="1">
         <v>7</v>
       </c>
-      <c r="AF10" s="7"/>
+      <c r="AF10" s="14"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1454,30 +1466,30 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="21"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="7"/>
+      <c r="P11" s="14"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1493,7 +1505,7 @@
       <c r="U11" s="1">
         <v>8</v>
       </c>
-      <c r="AF11" s="7"/>
+      <c r="AF11" s="14"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1502,32 +1514,32 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="7"/>
+      <c r="P12" s="14"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1555,7 @@
       <c r="U12" s="1">
         <v>9</v>
       </c>
-      <c r="AF12" s="7"/>
+      <c r="AF12" s="14"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1552,34 +1564,34 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="16"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="21"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L13" s="9"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="7"/>
+      <c r="P13" s="14"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1595,7 +1607,7 @@
       <c r="U13" s="1">
         <v>10</v>
       </c>
-      <c r="AF13" s="7"/>
+      <c r="AF13" s="14"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1604,8 +1616,8 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1615,21 +1627,21 @@
       <c r="G14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="21"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="7"/>
+      <c r="P14" s="14"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1645,7 +1657,7 @@
       <c r="U14" s="1">
         <v>11</v>
       </c>
-      <c r="AF14" s="7"/>
+      <c r="AF14" s="14"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1654,28 +1666,28 @@
       <c r="B15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="16"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="7"/>
+      <c r="P15" s="14"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1703,7 @@
       <c r="U15" s="1">
         <v>12</v>
       </c>
-      <c r="AF15" s="7"/>
+      <c r="AF15" s="14"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1700,30 +1712,30 @@
       <c r="B16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="16"/>
+      <c r="H16" s="21"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="7"/>
+      <c r="P16" s="14"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1739,7 +1751,7 @@
       <c r="U16" s="1">
         <v>13</v>
       </c>
-      <c r="AF16" s="7"/>
+      <c r="AF16" s="14"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1748,32 +1760,32 @@
       <c r="B17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="16"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="7"/>
+      <c r="P17" s="14"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1789,7 +1801,7 @@
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="AF17" s="7"/>
+      <c r="AF17" s="14"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1798,32 +1810,32 @@
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="9"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="16"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="7"/>
+      <c r="P18" s="14"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1839,7 +1851,7 @@
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="AF18" s="7"/>
+      <c r="AF18" s="14"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1848,32 +1860,32 @@
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="16"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="L19" s="9"/>
+        <v>119</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="10"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="7"/>
+      <c r="P19" s="14"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1901,7 @@
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="AF19" s="7"/>
+      <c r="AF19" s="14"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1898,40 +1910,40 @@
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="16"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K20" s="18"/>
-      <c r="L20" s="9"/>
+        <v>120</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="10"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7" t="s">
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="AF20" s="7"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="AF20" s="14"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1940,33 +1952,33 @@
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="16"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="9"/>
+        <v>121</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="7"/>
-      <c r="AF21" s="7"/>
+      <c r="P21" s="14"/>
+      <c r="AF21" s="14"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1975,16 +1987,16 @@
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="16"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -1994,14 +2006,14 @@
       <c r="K22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L22" s="9"/>
+      <c r="L22" s="10"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="7"/>
-      <c r="AF22" s="7"/>
+      <c r="P22" s="14"/>
+      <c r="AF22" s="14"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2010,18 +2022,18 @@
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="16"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
@@ -2029,30 +2041,34 @@
         <v>114</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="9"/>
+      <c r="L23" s="10"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="7"/>
-      <c r="AF23" s="7"/>
+      <c r="P23" s="14"/>
+      <c r="AF23" s="14"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="10"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="16"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="21"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -2062,74 +2078,82 @@
       <c r="K24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L24" s="9"/>
+      <c r="L24" s="10"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="7"/>
-      <c r="AF24" s="7"/>
+      <c r="P24" s="14"/>
+      <c r="AF24" s="14"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="16"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="21"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="9"/>
+      <c r="L25" s="10"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="7"/>
-      <c r="AF25" s="7"/>
+      <c r="P25" s="14"/>
+      <c r="AF25" s="14"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="16"/>
+      <c r="F26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="21"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K26" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="10"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="7"/>
-      <c r="AF26" s="7"/>
+      <c r="P26" s="14"/>
+      <c r="AF26" s="14"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2138,31 +2162,33 @@
       <c r="B27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="16"/>
+      <c r="F27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="21"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="10"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="7"/>
-      <c r="AF27" s="7"/>
+      <c r="P27" s="14"/>
+      <c r="AF27" s="14"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2171,29 +2197,31 @@
       <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="16"/>
+      <c r="F28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="21"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="10"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="7"/>
-      <c r="AF28" s="7"/>
+      <c r="P28" s="14"/>
+      <c r="AF28" s="14"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -2202,8 +2230,8 @@
       <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -2213,7 +2241,7 @@
       <c r="G29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H29" s="16"/>
+      <c r="H29" s="21"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2221,14 +2249,14 @@
         <v>83</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="9"/>
+      <c r="L29" s="10"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="7"/>
-      <c r="AF29" s="7"/>
+      <c r="P29" s="14"/>
+      <c r="AF29" s="14"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2238,13 +2266,13 @@
         <v>99</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="16"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2252,14 +2280,14 @@
         <v>113</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="9"/>
+      <c r="L30" s="10"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="7"/>
-      <c r="AF30" s="7"/>
+      <c r="P30" s="14"/>
+      <c r="AF30" s="14"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2269,7 +2297,7 @@
         <v>98</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="10"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -2279,7 +2307,7 @@
       <c r="G31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H31" s="16"/>
+      <c r="H31" s="21"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2287,14 +2315,14 @@
         <v>77</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="9"/>
+      <c r="L31" s="10"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="7"/>
-      <c r="AF31" s="7"/>
+      <c r="P31" s="14"/>
+      <c r="AF31" s="14"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2302,13 +2330,13 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="16"/>
+      <c r="H32" s="21"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2318,14 +2346,14 @@
       <c r="K32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L32" s="9"/>
+      <c r="L32" s="10"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="7"/>
-      <c r="AF32" s="7"/>
+      <c r="P32" s="14"/>
+      <c r="AF32" s="14"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2334,20 +2362,20 @@
       <c r="B33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="9"/>
+      <c r="D33" s="10"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H33" s="16"/>
+      <c r="H33" s="21"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2355,14 +2383,14 @@
         <v>84</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="9"/>
+      <c r="L33" s="10"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="7"/>
-      <c r="AF33" s="7"/>
+      <c r="P33" s="14"/>
+      <c r="AF33" s="14"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2371,16 +2399,16 @@
       <c r="B34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="9"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="16"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="21"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2388,14 +2416,14 @@
         <v>95</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="9"/>
+      <c r="L34" s="10"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="7"/>
-      <c r="AF34" s="7"/>
+      <c r="P34" s="14"/>
+      <c r="AF34" s="14"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2404,16 +2432,16 @@
       <c r="B35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="9"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="16"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="21"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
@@ -2421,77 +2449,77 @@
         <v>115</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="9"/>
+      <c r="L35" s="10"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="7"/>
-      <c r="AF35" s="7"/>
+      <c r="P35" s="14"/>
+      <c r="AF35" s="14"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="12"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="17"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="9" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="9" t="s">
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9" t="s">
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2503,7 +2531,7 @@
       <c r="C39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="9"/>
+      <c r="D39" s="10"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2513,7 +2541,7 @@
       <c r="G39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="14"/>
+      <c r="H39" s="19"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2523,7 +2551,7 @@
       <c r="K39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L39" s="9"/>
+      <c r="L39" s="10"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2541,26 +2569,26 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="9"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="14"/>
+      <c r="H40" s="19"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="L40" s="9"/>
+      <c r="L40" s="10"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2574,22 +2602,22 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="14"/>
+      <c r="H41" s="19"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="10"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2603,22 +2631,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="14"/>
+      <c r="H42" s="19"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="8"/>
-      <c r="L42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="10"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2632,24 +2660,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="9"/>
+      <c r="D43" s="10"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="14"/>
+      <c r="H43" s="19"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="8"/>
-      <c r="L43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="10"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2663,22 +2691,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="10"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="14"/>
+      <c r="H44" s="19"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="8"/>
-      <c r="L44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="10"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2692,22 +2720,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="10"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="14"/>
+      <c r="H45" s="19"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="8"/>
-      <c r="L45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="10"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2721,24 +2749,24 @@
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="9"/>
+      <c r="D46" s="10"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="14"/>
+      <c r="H46" s="19"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K46" s="8"/>
-      <c r="L46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="10"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2752,22 +2780,22 @@
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="14"/>
+      <c r="H47" s="19"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K47" s="8"/>
-      <c r="L47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="10"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2781,22 +2809,22 @@
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="10"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="14"/>
+      <c r="H48" s="19"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K48" s="8"/>
-      <c r="L48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="10"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2810,24 +2838,24 @@
       <c r="B49" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="9"/>
+      <c r="D49" s="10"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="14"/>
+      <c r="H49" s="19"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="10"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2841,22 +2869,22 @@
       <c r="B50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="14"/>
+      <c r="H50" s="19"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="8"/>
-      <c r="L50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="10"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2870,22 +2898,22 @@
       <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="10"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="14"/>
+      <c r="H51" s="19"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K51" s="8"/>
-      <c r="L51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="10"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2899,26 +2927,26 @@
       <c r="B52" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="9"/>
+      <c r="D52" s="10"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="14"/>
+      <c r="H52" s="19"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="K52" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L52" s="9"/>
+      <c r="L52" s="10"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2932,22 +2960,22 @@
       <c r="B53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="14"/>
+      <c r="H53" s="19"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K53" s="8"/>
-      <c r="L53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="10"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -2961,22 +2989,22 @@
       <c r="B54" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="14"/>
+      <c r="H54" s="19"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K54" s="8"/>
-      <c r="L54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="10"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -2989,13 +3017,13 @@
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="9"/>
+      <c r="D55" s="10"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="14"/>
+      <c r="H55" s="19"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3005,7 +3033,7 @@
       <c r="K55" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L55" s="9"/>
+      <c r="L55" s="10"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3018,13 +3046,13 @@
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="9"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="14"/>
+      <c r="H56" s="19"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3032,7 +3060,7 @@
         <v>77</v>
       </c>
       <c r="K56" s="2"/>
-      <c r="L56" s="9"/>
+      <c r="L56" s="10"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3045,13 +3073,13 @@
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="9"/>
+      <c r="D57" s="10"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="14"/>
+      <c r="H57" s="19"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3059,7 +3087,7 @@
         <v>83</v>
       </c>
       <c r="K57" s="2"/>
-      <c r="L57" s="9"/>
+      <c r="L57" s="10"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3073,16 +3101,16 @@
       <c r="B58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="9"/>
+      <c r="D58" s="10"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="14"/>
+      <c r="H58" s="19"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3092,7 +3120,7 @@
       <c r="K58" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L58" s="9"/>
+      <c r="L58" s="10"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3104,14 +3132,14 @@
         <v>20</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="14"/>
+      <c r="H59" s="19"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3119,7 +3147,7 @@
         <v>81</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="9"/>
+      <c r="L59" s="10"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3133,20 +3161,20 @@
       <c r="B60" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="14"/>
+      <c r="H60" s="19"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="9"/>
+      <c r="L60" s="10"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3158,20 +3186,20 @@
         <v>22</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="14"/>
+      <c r="H61" s="19"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="9"/>
+      <c r="L61" s="10"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3188,19 +3216,19 @@
       <c r="C62" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D62" s="9"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="14"/>
+      <c r="H62" s="19"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="9"/>
+      <c r="L62" s="10"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3215,19 +3243,19 @@
         <v>60</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="10"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="14"/>
+      <c r="H63" s="19"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="9"/>
+      <c r="L63" s="10"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3242,19 +3270,19 @@
         <v>61</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="9"/>
+      <c r="D64" s="10"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="14"/>
+      <c r="H64" s="19"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="9"/>
+      <c r="L64" s="10"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3271,19 +3299,19 @@
       <c r="C65" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="9"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="14"/>
+      <c r="H65" s="19"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="9"/>
+      <c r="L65" s="10"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3298,19 +3326,19 @@
         <v>95</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="14"/>
+      <c r="H66" s="19"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="9"/>
+      <c r="L66" s="10"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3325,19 +3353,19 @@
         <v>97</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="10"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="14"/>
+      <c r="H67" s="19"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="9"/>
+      <c r="L67" s="10"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3350,19 +3378,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="14"/>
+      <c r="H68" s="19"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="9"/>
+      <c r="L68" s="10"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3375,19 +3403,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="9"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="14"/>
+      <c r="H69" s="19"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="9"/>
+      <c r="L69" s="10"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3400,19 +3428,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="14"/>
+      <c r="H70" s="19"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="9"/>
+      <c r="L70" s="10"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3425,19 +3453,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="10"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="15"/>
+      <c r="H71" s="20"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="9"/>
+      <c r="L71" s="10"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3445,12 +3473,19 @@
       <c r="O71" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="Q20:U20"/>
+  <mergeCells count="56">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
     <mergeCell ref="AF1:AF35"/>
     <mergeCell ref="P1:P35"/>
     <mergeCell ref="H1:H35"/>
@@ -3461,6 +3496,12 @@
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="K40:K51"/>
     <mergeCell ref="A36:O36"/>
     <mergeCell ref="H37:H71"/>
@@ -3469,24 +3510,10 @@
     <mergeCell ref="L38:L71"/>
     <mergeCell ref="M38:O38"/>
     <mergeCell ref="K52:K54"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="K26:K28"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="D38:D71"/>
     <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="G23:G25"/>
@@ -3499,7 +3526,10 @@
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="K13:K15"/>
     <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
     <mergeCell ref="K19:K21"/>
+    <mergeCell ref="C43:C45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B0C664-EEA1-4629-8040-D1414B9D1799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D2EB42-D284-4EE3-B8C1-88539B951E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
   <si>
     <t>Freq:</t>
   </si>
@@ -405,6 +405,18 @@
   </si>
   <si>
     <t>friendly selected transmit 1</t>
+  </si>
+  <si>
+    <t>laser dist</t>
+  </si>
+  <si>
+    <t>laser hor slew</t>
+  </si>
+  <si>
+    <t>laser ver slew</t>
+  </si>
+  <si>
+    <t>laser slew</t>
   </si>
 </sst>
 </file>
@@ -594,10 +606,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -610,6 +622,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -628,9 +643,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -952,7 +964,7 @@
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1"/>
     <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="29.7109375" style="1" customWidth="1"/>
@@ -985,25 +997,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="10" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="14" t="s">
         <v>94</v>
@@ -1015,29 +1027,29 @@
       <c r="AF1" s="14"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="10" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="1" t="s">
         <v>88</v>
@@ -1063,7 +1075,7 @@
       <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1073,7 +1085,7 @@
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="15"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1095,7 @@
       <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="9"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1118,30 +1130,30 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="9"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="21"/>
+      <c r="H4" s="15"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -1172,24 +1184,24 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="21"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="9"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -1220,8 +1232,8 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
@@ -1231,15 +1243,15 @@
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="21"/>
+      <c r="H6" s="15"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -1270,26 +1282,26 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="21"/>
+      <c r="H7" s="15"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="9"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1320,22 +1332,22 @@
       <c r="B8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="21"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1366,22 +1378,22 @@
       <c r="B9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="21"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="9"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1412,30 +1424,30 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="10"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1466,24 +1478,24 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="21"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="15"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1514,26 +1526,26 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="21"/>
+      <c r="H12" s="15"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1564,28 +1576,28 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="21"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="15"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L13" s="10"/>
+      <c r="L13" s="9"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1616,8 +1628,8 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1627,15 +1639,15 @@
       <c r="G14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="21"/>
+      <c r="H14" s="15"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1666,22 +1678,22 @@
       <c r="B15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="21"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="9"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1712,24 +1724,24 @@
       <c r="B16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="21"/>
+      <c r="H16" s="15"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="9"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1760,26 +1772,26 @@
       <c r="B17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="21"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="9"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1810,26 +1822,26 @@
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="21"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="15"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="9"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1860,16 +1872,16 @@
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="21"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="15"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
@@ -1879,7 +1891,7 @@
       <c r="K19" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L19" s="10"/>
+      <c r="L19" s="9"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1910,18 +1922,18 @@
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="21"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
@@ -1929,7 +1941,7 @@
         <v>120</v>
       </c>
       <c r="K20" s="12"/>
-      <c r="L20" s="10"/>
+      <c r="L20" s="9"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1952,18 +1964,18 @@
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="21"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="15"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
@@ -1971,7 +1983,7 @@
         <v>121</v>
       </c>
       <c r="K21" s="13"/>
-      <c r="L21" s="10"/>
+      <c r="L21" s="9"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1987,16 +1999,16 @@
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="21"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -2006,7 +2018,7 @@
       <c r="K22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L22" s="10"/>
+      <c r="L22" s="9"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -2022,18 +2034,18 @@
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="21"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
@@ -2041,7 +2053,7 @@
         <v>114</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="10"/>
+      <c r="L23" s="9"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -2060,15 +2072,15 @@
       <c r="C24" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="21"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -2078,7 +2090,7 @@
       <c r="K24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L24" s="10"/>
+      <c r="L24" s="9"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -2095,21 +2107,21 @@
         <v>105</v>
       </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="10"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="21"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="10"/>
+      <c r="L25" s="9"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -2126,7 +2138,7 @@
         <v>106</v>
       </c>
       <c r="C26" s="13"/>
-      <c r="D26" s="10"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
@@ -2136,17 +2148,17 @@
       <c r="G26" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H26" s="21"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="10"/>
+      <c r="L26" s="9"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -2162,10 +2174,10 @@
       <c r="B27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
@@ -2173,15 +2185,15 @@
         <v>120</v>
       </c>
       <c r="G27" s="12"/>
-      <c r="H27" s="21"/>
+      <c r="H27" s="15"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="9"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -2197,8 +2209,8 @@
       <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
@@ -2206,15 +2218,15 @@
         <v>121</v>
       </c>
       <c r="G28" s="13"/>
-      <c r="H28" s="21"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="9"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -2230,8 +2242,8 @@
       <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -2241,7 +2253,7 @@
       <c r="G29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H29" s="21"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2249,7 +2261,7 @@
         <v>83</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="10"/>
+      <c r="L29" s="9"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -2266,13 +2278,13 @@
         <v>99</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="10"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="21"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2280,7 +2292,7 @@
         <v>113</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="10"/>
+      <c r="L30" s="9"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -2297,7 +2309,7 @@
         <v>98</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="10"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -2307,7 +2319,7 @@
       <c r="G31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H31" s="21"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2315,7 +2327,7 @@
         <v>77</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="10"/>
+      <c r="L31" s="9"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -2330,13 +2342,13 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="10"/>
+      <c r="D32" s="9"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="21"/>
+      <c r="H32" s="15"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2346,7 +2358,7 @@
       <c r="K32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="L32" s="9"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -2365,17 +2377,17 @@
       <c r="C33" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="10"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H33" s="21"/>
+      <c r="H33" s="15"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2383,7 +2395,7 @@
         <v>84</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="10"/>
+      <c r="L33" s="9"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -2400,15 +2412,15 @@
         <v>107</v>
       </c>
       <c r="C34" s="12"/>
-      <c r="D34" s="10"/>
+      <c r="D34" s="9"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="21"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="15"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2416,7 +2428,7 @@
         <v>95</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="10"/>
+      <c r="L34" s="9"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -2433,15 +2445,15 @@
         <v>108</v>
       </c>
       <c r="C35" s="13"/>
-      <c r="D35" s="10"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="21"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="15"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
@@ -2449,7 +2461,7 @@
         <v>115</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="10"/>
+      <c r="L35" s="9"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -2459,67 +2471,67 @@
       <c r="AF35" s="14"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="17"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="10" t="s">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="10" t="s">
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10" t="s">
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2531,7 +2543,7 @@
       <c r="C39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="10"/>
+      <c r="D39" s="9"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2541,7 +2553,7 @@
       <c r="G39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="19"/>
+      <c r="H39" s="20"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2551,7 +2563,7 @@
       <c r="K39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L39" s="10"/>
+      <c r="L39" s="9"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2569,26 +2581,30 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="10"/>
+      <c r="D40" s="9"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="19"/>
+      <c r="F40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="20"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="L40" s="10"/>
+      <c r="L40" s="9"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2602,22 +2618,24 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="19"/>
+      <c r="F41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G41" s="13"/>
+      <c r="H41" s="20"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="9"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2631,22 +2649,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="19"/>
+      <c r="H42" s="20"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="9"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2660,24 +2678,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="10"/>
+      <c r="D43" s="9"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="19"/>
+      <c r="H43" s="20"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="9"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2691,22 +2709,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="19"/>
+      <c r="H44" s="20"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="9"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2720,22 +2738,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="19"/>
+      <c r="H45" s="20"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="9"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2749,24 +2767,24 @@
       <c r="B46" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="10"/>
+      <c r="D46" s="9"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="19"/>
+      <c r="H46" s="20"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="9"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2780,22 +2798,22 @@
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="9"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="19"/>
+      <c r="H47" s="20"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="9"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2809,22 +2827,22 @@
       <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="19"/>
+      <c r="H48" s="20"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="9"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2838,24 +2856,24 @@
       <c r="B49" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="10"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="19"/>
+      <c r="H49" s="20"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="9"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2869,22 +2887,22 @@
       <c r="B50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="19"/>
+      <c r="H50" s="20"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="9"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2898,22 +2916,22 @@
       <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="19"/>
+      <c r="H51" s="20"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="9"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2927,26 +2945,26 @@
       <c r="B52" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="10"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="19"/>
+      <c r="H52" s="20"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="L52" s="10"/>
+      <c r="L52" s="9"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2960,22 +2978,22 @@
       <c r="B53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="9"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="19"/>
+      <c r="H53" s="20"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="9"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -2989,22 +3007,22 @@
       <c r="B54" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="19"/>
+      <c r="H54" s="20"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="9"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3015,15 +3033,19 @@
       <c r="A55" s="2">
         <v>16</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="10"/>
+      <c r="B55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" s="9"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="19"/>
+      <c r="H55" s="20"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3033,7 +3055,7 @@
       <c r="K55" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L55" s="10"/>
+      <c r="L55" s="9"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3044,15 +3066,17 @@
       <c r="A56" s="2">
         <v>17</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="10"/>
+      <c r="B56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="19"/>
+      <c r="H56" s="20"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3060,7 +3084,7 @@
         <v>77</v>
       </c>
       <c r="K56" s="2"/>
-      <c r="L56" s="10"/>
+      <c r="L56" s="9"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3071,15 +3095,17 @@
       <c r="A57" s="2">
         <v>18</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="10"/>
+      <c r="B57" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="13"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="19"/>
+      <c r="H57" s="20"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3087,7 +3113,7 @@
         <v>83</v>
       </c>
       <c r="K57" s="2"/>
-      <c r="L57" s="10"/>
+      <c r="L57" s="9"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3101,16 +3127,16 @@
       <c r="B58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="10"/>
+      <c r="D58" s="9"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="19"/>
+      <c r="H58" s="20"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3120,7 +3146,7 @@
       <c r="K58" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L58" s="10"/>
+      <c r="L58" s="9"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3131,15 +3157,19 @@
       <c r="A59" s="2">
         <v>20</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
+      <c r="B59" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="9"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="19"/>
+      <c r="H59" s="20"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3147,7 +3177,7 @@
         <v>81</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="10"/>
+      <c r="L59" s="9"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3161,20 +3191,22 @@
       <c r="B60" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="10"/>
+      <c r="C60" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="9"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="19"/>
+      <c r="H60" s="20"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="10"/>
+      <c r="L60" s="9"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3186,20 +3218,20 @@
         <v>22</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="10"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="19"/>
+      <c r="H61" s="20"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="10"/>
+      <c r="L61" s="9"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3213,22 +3245,22 @@
       <c r="B62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="19"/>
+      <c r="H62" s="20"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="10"/>
+      <c r="L62" s="9"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3242,20 +3274,20 @@
       <c r="B63" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="10"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="19"/>
+      <c r="H63" s="20"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="10"/>
+      <c r="L63" s="9"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3269,20 +3301,20 @@
       <c r="B64" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="10"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="19"/>
+      <c r="H64" s="20"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="10"/>
+      <c r="L64" s="9"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3299,19 +3331,19 @@
       <c r="C65" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="10"/>
+      <c r="D65" s="9"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="19"/>
+      <c r="H65" s="20"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="10"/>
+      <c r="L65" s="9"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3322,23 +3354,21 @@
       <c r="A66" s="2">
         <v>27</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="10"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="19"/>
+      <c r="H66" s="20"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="10"/>
+      <c r="L66" s="9"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3353,19 +3383,19 @@
         <v>97</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="19"/>
+      <c r="H67" s="20"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="10"/>
+      <c r="L67" s="9"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3378,19 +3408,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="19"/>
+      <c r="H68" s="20"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="10"/>
+      <c r="L68" s="9"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3403,19 +3433,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="9"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="19"/>
+      <c r="H69" s="20"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="10"/>
+      <c r="L69" s="9"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3428,19 +3458,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="10"/>
+      <c r="D70" s="9"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="19"/>
+      <c r="H70" s="20"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="10"/>
+      <c r="L70" s="9"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3453,19 +3483,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="10"/>
+      <c r="D71" s="9"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="20"/>
+      <c r="H71" s="21"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="10"/>
+      <c r="L71" s="9"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3473,19 +3503,29 @@
       <c r="O71" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
+  <mergeCells count="58">
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G40:G41"/>
     <mergeCell ref="AF1:AF35"/>
     <mergeCell ref="P1:P35"/>
     <mergeCell ref="H1:H35"/>
@@ -3502,6 +3542,12 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
     <mergeCell ref="K40:K51"/>
     <mergeCell ref="A36:O36"/>
     <mergeCell ref="H37:H71"/>
@@ -3511,25 +3557,11 @@
     <mergeCell ref="M38:O38"/>
     <mergeCell ref="K52:K54"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D2EB42-D284-4EE3-B8C1-88539B951E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB766ED-7A4D-4A40-83FB-A66B0184BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -3504,28 +3504,24 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="AF1:AF35"/>
     <mergeCell ref="P1:P35"/>
     <mergeCell ref="H1:H35"/>
@@ -3542,26 +3538,30 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
     <mergeCell ref="K26:K28"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB766ED-7A4D-4A40-83FB-A66B0184BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72161FF-C2F7-4247-A710-15801BAB3500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -612,19 +612,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -643,6 +631,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1006,7 +1006,7 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
-      <c r="H1" s="15"/>
+      <c r="H1" s="18"/>
       <c r="I1" s="9" t="s">
         <v>64</v>
       </c>
@@ -1016,15 +1016,15 @@
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14" t="s">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="AF1" s="14"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="AF1" s="11"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="15"/>
+      <c r="H2" s="18"/>
       <c r="I2" s="9" t="s">
         <v>31</v>
       </c>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
-      <c r="P2" s="14"/>
+      <c r="P2" s="11"/>
       <c r="Q2" s="1" t="s">
         <v>88</v>
       </c>
@@ -1063,7 +1063,7 @@
       <c r="T2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="14"/>
+      <c r="AF2" s="11"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1085,7 +1085,7 @@
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="15"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1105,7 +1105,7 @@
       <c r="O3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="14"/>
+      <c r="P3" s="11"/>
       <c r="Q3" s="1" t="s">
         <v>89</v>
       </c>
@@ -1121,7 +1121,7 @@
       <c r="U3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AF3" s="14"/>
+      <c r="AF3" s="11"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1143,7 +1143,7 @@
       <c r="G4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="14"/>
+      <c r="P4" s="11"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1175,7 +1175,7 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="AF4" s="14"/>
+      <c r="AF4" s="11"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1193,7 +1193,7 @@
         <v>35</v>
       </c>
       <c r="G5" s="10"/>
-      <c r="H5" s="15"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="14"/>
+      <c r="P5" s="11"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1223,7 +1223,7 @@
       <c r="U5" s="1">
         <v>2</v>
       </c>
-      <c r="AF5" s="14"/>
+      <c r="AF5" s="11"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1243,7 +1243,7 @@
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="18"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="14"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="AF6" s="14"/>
+      <c r="AF6" s="11"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="18"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="14"/>
+      <c r="P7" s="11"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="U7" s="1">
         <v>4</v>
       </c>
-      <c r="AF7" s="14"/>
+      <c r="AF7" s="11"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="18"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="14"/>
+      <c r="P8" s="11"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="U8" s="1">
         <v>5</v>
       </c>
-      <c r="AF8" s="14"/>
+      <c r="AF8" s="11"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="18"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="14"/>
+      <c r="P9" s="11"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="U9" s="1">
         <v>6</v>
       </c>
-      <c r="AF9" s="14"/>
+      <c r="AF9" s="11"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1437,7 +1437,7 @@
       <c r="G10" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="15"/>
+      <c r="H10" s="18"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="14"/>
+      <c r="P10" s="11"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1469,7 +1469,7 @@
       <c r="U10" s="1">
         <v>7</v>
       </c>
-      <c r="AF10" s="14"/>
+      <c r="AF10" s="11"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1487,7 +1487,7 @@
         <v>53</v>
       </c>
       <c r="G11" s="10"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="18"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="14"/>
+      <c r="P11" s="11"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="U11" s="1">
         <v>8</v>
       </c>
-      <c r="AF11" s="14"/>
+      <c r="AF11" s="11"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1537,7 +1537,7 @@
       <c r="G12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="18"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="14"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="U12" s="1">
         <v>9</v>
       </c>
-      <c r="AF12" s="14"/>
+      <c r="AF12" s="11"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1587,7 +1587,7 @@
         <v>37</v>
       </c>
       <c r="G13" s="10"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="18"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="14"/>
+      <c r="P13" s="11"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="U13" s="1">
         <v>10</v>
       </c>
-      <c r="AF13" s="14"/>
+      <c r="AF13" s="11"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1639,7 +1639,7 @@
       <c r="G14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="18"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="14"/>
+      <c r="P14" s="11"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="U14" s="1">
         <v>11</v>
       </c>
-      <c r="AF14" s="14"/>
+      <c r="AF14" s="11"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1685,7 +1685,7 @@
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="15"/>
+      <c r="H15" s="18"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="14"/>
+      <c r="P15" s="11"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1715,7 +1715,7 @@
       <c r="U15" s="1">
         <v>12</v>
       </c>
-      <c r="AF15" s="14"/>
+      <c r="AF15" s="11"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="18"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="14"/>
+      <c r="P16" s="11"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1763,7 +1763,7 @@
       <c r="U16" s="1">
         <v>13</v>
       </c>
-      <c r="AF16" s="14"/>
+      <c r="AF16" s="11"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1783,7 +1783,7 @@
       <c r="G17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="15"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="14"/>
+      <c r="P17" s="11"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="AF17" s="14"/>
+      <c r="AF17" s="11"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1833,7 +1833,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="10"/>
-      <c r="H18" s="15"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="14"/>
+      <c r="P18" s="11"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="AF18" s="14"/>
+      <c r="AF18" s="11"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1881,14 +1881,14 @@
         <v>41</v>
       </c>
       <c r="G19" s="10"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="19" t="s">
         <v>122</v>
       </c>
       <c r="L19" s="9"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="14"/>
+      <c r="P19" s="11"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1913,7 +1913,7 @@
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="AF19" s="14"/>
+      <c r="AF19" s="11"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1933,29 +1933,29 @@
       <c r="G20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K20" s="12"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="9"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14" t="s">
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="AF20" s="14"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="AF20" s="11"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1975,22 +1975,22 @@
         <v>43</v>
       </c>
       <c r="G21" s="10"/>
-      <c r="H21" s="15"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K21" s="13"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="9"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="14"/>
-      <c r="AF21" s="14"/>
+      <c r="P21" s="11"/>
+      <c r="AF21" s="11"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -2008,7 +2008,7 @@
         <v>44</v>
       </c>
       <c r="G22" s="10"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -2024,8 +2024,8 @@
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="14"/>
-      <c r="AF22" s="14"/>
+      <c r="P22" s="11"/>
+      <c r="AF22" s="11"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2045,7 +2045,7 @@
       <c r="G23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="15"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
@@ -2059,8 +2059,8 @@
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="14"/>
-      <c r="AF23" s="14"/>
+      <c r="P23" s="11"/>
+      <c r="AF23" s="11"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2069,7 +2069,7 @@
       <c r="B24" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="19" t="s">
         <v>118</v>
       </c>
       <c r="D24" s="9"/>
@@ -2080,7 +2080,7 @@
         <v>46</v>
       </c>
       <c r="G24" s="10"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="18"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -2096,8 +2096,8 @@
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="14"/>
-      <c r="AF24" s="14"/>
+      <c r="P24" s="11"/>
+      <c r="AF24" s="11"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2106,7 +2106,7 @@
       <c r="B25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="12"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="9"/>
       <c r="E25" s="2">
         <v>22</v>
@@ -2115,7 +2115,7 @@
         <v>47</v>
       </c>
       <c r="G25" s="10"/>
-      <c r="H25" s="15"/>
+      <c r="H25" s="18"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
@@ -2127,8 +2127,8 @@
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="14"/>
-      <c r="AF25" s="14"/>
+      <c r="P25" s="11"/>
+      <c r="AF25" s="11"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2137,7 +2137,7 @@
       <c r="B26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="13"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="9"/>
       <c r="E26" s="2">
         <v>23</v>
@@ -2145,10 +2145,10 @@
       <c r="F26" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H26" s="15"/>
+      <c r="H26" s="18"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
@@ -2164,8 +2164,8 @@
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="14"/>
-      <c r="AF26" s="14"/>
+      <c r="P26" s="11"/>
+      <c r="AF26" s="11"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2184,8 +2184,8 @@
       <c r="F27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="15"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="18"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -2199,8 +2199,8 @@
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="14"/>
-      <c r="AF27" s="14"/>
+      <c r="P27" s="11"/>
+      <c r="AF27" s="11"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2217,8 +2217,8 @@
       <c r="F28" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="18"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -2232,8 +2232,8 @@
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="14"/>
-      <c r="AF28" s="14"/>
+      <c r="P28" s="11"/>
+      <c r="AF28" s="11"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -2253,7 +2253,7 @@
       <c r="G29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H29" s="15"/>
+      <c r="H29" s="18"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2267,8 +2267,8 @@
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="14"/>
-      <c r="AF29" s="14"/>
+      <c r="P29" s="11"/>
+      <c r="AF29" s="11"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="15"/>
+      <c r="H30" s="18"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2298,8 +2298,8 @@
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="14"/>
-      <c r="AF30" s="14"/>
+      <c r="P30" s="11"/>
+      <c r="AF30" s="11"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2319,7 +2319,7 @@
       <c r="G31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H31" s="15"/>
+      <c r="H31" s="18"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2333,8 +2333,8 @@
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="14"/>
-      <c r="AF31" s="14"/>
+      <c r="P31" s="11"/>
+      <c r="AF31" s="11"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="15"/>
+      <c r="H32" s="18"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2364,8 +2364,8 @@
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="14"/>
-      <c r="AF32" s="14"/>
+      <c r="P32" s="11"/>
+      <c r="AF32" s="11"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2374,7 +2374,7 @@
       <c r="B33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="19" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="9"/>
@@ -2387,7 +2387,7 @@
       <c r="G33" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H33" s="15"/>
+      <c r="H33" s="18"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2401,8 +2401,8 @@
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="14"/>
-      <c r="AF33" s="14"/>
+      <c r="P33" s="11"/>
+      <c r="AF33" s="11"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2411,7 +2411,7 @@
       <c r="B34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="12"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="9"/>
       <c r="E34" s="2">
         <v>31</v>
@@ -2420,7 +2420,7 @@
         <v>60</v>
       </c>
       <c r="G34" s="10"/>
-      <c r="H34" s="15"/>
+      <c r="H34" s="18"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2434,8 +2434,8 @@
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="14"/>
-      <c r="AF34" s="14"/>
+      <c r="P34" s="11"/>
+      <c r="AF34" s="11"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2444,7 +2444,7 @@
       <c r="B35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="13"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="9"/>
       <c r="E35" s="2">
         <v>32</v>
@@ -2453,7 +2453,7 @@
         <v>61</v>
       </c>
       <c r="G35" s="10"/>
-      <c r="H35" s="15"/>
+      <c r="H35" s="18"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
@@ -2467,25 +2467,25 @@
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="14"/>
-      <c r="AF35" s="14"/>
+      <c r="P35" s="11"/>
+      <c r="AF35" s="11"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="18"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="14"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
@@ -2497,7 +2497,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="19"/>
+      <c r="H37" s="15"/>
       <c r="I37" s="9" t="s">
         <v>76</v>
       </c>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="20"/>
+      <c r="H38" s="16"/>
       <c r="I38" s="9" t="s">
         <v>31</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="G39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="20"/>
+      <c r="H39" s="16"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2591,10 +2591,10 @@
       <c r="F40" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="20"/>
+      <c r="H40" s="16"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
@@ -2626,8 +2626,8 @@
       <c r="F41" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="20"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="16"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="20"/>
+      <c r="H42" s="16"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="20"/>
+      <c r="H43" s="16"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="20"/>
+      <c r="H44" s="16"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="20"/>
+      <c r="H45" s="16"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="20"/>
+      <c r="H46" s="16"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="20"/>
+      <c r="H47" s="16"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="20"/>
+      <c r="H48" s="16"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="20"/>
+      <c r="H49" s="16"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="20"/>
+      <c r="H50" s="16"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="20"/>
+      <c r="H51" s="16"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="20"/>
+      <c r="H52" s="16"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="20"/>
+      <c r="H53" s="16"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="20"/>
+      <c r="H54" s="16"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="B55" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="19" t="s">
         <v>122</v>
       </c>
       <c r="D55" s="9"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="20"/>
+      <c r="H55" s="16"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3069,14 +3069,14 @@
       <c r="B56" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="12"/>
+      <c r="C56" s="20"/>
       <c r="D56" s="9"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="20"/>
+      <c r="H56" s="16"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3098,14 +3098,14 @@
       <c r="B57" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="13"/>
+      <c r="C57" s="21"/>
       <c r="D57" s="9"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="20"/>
+      <c r="H57" s="16"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="20"/>
+      <c r="H58" s="16"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="20"/>
+      <c r="H59" s="16"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="20"/>
+      <c r="H60" s="16"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="20"/>
+      <c r="H61" s="16"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
@@ -3245,7 +3245,7 @@
       <c r="B62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D62" s="9"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="20"/>
+      <c r="H62" s="16"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
@@ -3274,14 +3274,14 @@
       <c r="B63" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="12"/>
+      <c r="C63" s="20"/>
       <c r="D63" s="9"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="20"/>
+      <c r="H63" s="16"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
@@ -3301,14 +3301,14 @@
       <c r="B64" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C64" s="13"/>
+      <c r="C64" s="21"/>
       <c r="D64" s="9"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="20"/>
+      <c r="H64" s="16"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="20"/>
+      <c r="H65" s="16"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="20"/>
+      <c r="H66" s="16"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="20"/>
+      <c r="H67" s="16"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="20"/>
+      <c r="H68" s="16"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="20"/>
+      <c r="H69" s="16"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="20"/>
+      <c r="H70" s="16"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="21"/>
+      <c r="H71" s="17"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
@@ -3504,24 +3504,27 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C43:C45"/>
     <mergeCell ref="AF1:AF35"/>
     <mergeCell ref="P1:P35"/>
     <mergeCell ref="H1:H35"/>
@@ -3538,30 +3541,27 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="D38:D71"/>
     <mergeCell ref="E38:G38"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72161FF-C2F7-4247-A710-15801BAB3500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC343C7-E2F8-41B8-89C5-34230C50D488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="123">
   <si>
     <t>Freq:</t>
   </si>
@@ -62,21 +62,9 @@
     <t>rz</t>
   </si>
   <si>
-    <t>friend x</t>
-  </si>
-  <si>
-    <t>friend y</t>
-  </si>
-  <si>
     <t>friend z</t>
   </si>
   <si>
-    <t>friend user1</t>
-  </si>
-  <si>
-    <t>friend user2</t>
-  </si>
-  <si>
     <t>old r x</t>
   </si>
   <si>
@@ -95,9 +83,6 @@
     <t>my rot</t>
   </si>
   <si>
-    <t>friend username</t>
-  </si>
-  <si>
     <t>old xyz</t>
   </si>
   <si>
@@ -137,15 +122,6 @@
     <t>Output</t>
   </si>
   <si>
-    <t>viclink receive freq</t>
-  </si>
-  <si>
-    <t>my user 1</t>
-  </si>
-  <si>
-    <t>my user 2</t>
-  </si>
-  <si>
     <t>FOVY</t>
   </si>
   <si>
@@ -182,9 +158,6 @@
     <t>friendly trans z</t>
   </si>
   <si>
-    <t>my username</t>
-  </si>
-  <si>
     <t>EVA</t>
   </si>
   <si>
@@ -417,6 +390,21 @@
   </si>
   <si>
     <t>laser slew</t>
+  </si>
+  <si>
+    <t>friend x / enemy x</t>
+  </si>
+  <si>
+    <t>friend y / enemy y</t>
+  </si>
+  <si>
+    <t>datalink send freq</t>
+  </si>
+  <si>
+    <t>datalink receive freq</t>
+  </si>
+  <si>
+    <t>debug number</t>
   </si>
 </sst>
 </file>
@@ -606,6 +594,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -613,6 +610,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -631,18 +631,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -997,73 +985,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="AF1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="AF1" s="14"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="11"/>
+      <c r="A2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="14"/>
       <c r="Q2" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF2" s="11"/>
+        <v>78</v>
+      </c>
+      <c r="AF2" s="14"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1073,9 +1061,9 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D3" s="12"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1083,9 +1071,9 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="18"/>
+        <v>25</v>
+      </c>
+      <c r="H3" s="15"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1093,9 +1081,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="L3" s="12"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1103,25 +1091,25 @@
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="11"/>
+        <v>25</v>
+      </c>
+      <c r="P3" s="14"/>
       <c r="Q3" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF3" s="11"/>
+        <v>84</v>
+      </c>
+      <c r="AF3" s="14"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1130,36 +1118,34 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="9"/>
+      <c r="C4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="12"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="18"/>
+        <v>122</v>
+      </c>
+      <c r="G4" s="13"/>
+      <c r="H4" s="15"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="9"/>
+      <c r="K4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="12"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="14"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1175,7 +1161,7 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="AF4" s="11"/>
+      <c r="AF4" s="14"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1184,30 +1170,28 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="18"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="9"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="12"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="14"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1223,7 +1207,7 @@
       <c r="U5" s="1">
         <v>2</v>
       </c>
-      <c r="AF5" s="11"/>
+      <c r="AF5" s="14"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1232,32 +1216,32 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="18"/>
+        <v>121</v>
+      </c>
+      <c r="H6" s="15"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="9"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="12"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="14"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1273,41 +1257,41 @@
       <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="AF6" s="11"/>
+      <c r="AF6" s="14"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="18"/>
+      <c r="H7" s="15"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="12"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="14"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1323,37 +1307,37 @@
       <c r="U7" s="1">
         <v>4</v>
       </c>
-      <c r="AF7" s="11"/>
+      <c r="AF7" s="14"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="18"/>
+      <c r="H8" s="15"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="12"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="14"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1369,37 +1353,37 @@
       <c r="U8" s="1">
         <v>5</v>
       </c>
-      <c r="AF8" s="11"/>
+      <c r="AF8" s="14"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
+        <v>94</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="18"/>
+      <c r="H9" s="15"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="9"/>
+        <v>94</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="12"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="14"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1415,45 +1399,45 @@
       <c r="U9" s="1">
         <v>6</v>
       </c>
-      <c r="AF9" s="11"/>
+      <c r="AF9" s="14"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="18"/>
+        <v>43</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="15"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="14"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1469,39 +1453,39 @@
       <c r="U10" s="1">
         <v>7</v>
       </c>
-      <c r="AF10" s="11"/>
+      <c r="AF10" s="14"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
+        <v>119</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="12"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="18"/>
+        <v>44</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="15"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="12"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="14"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1517,41 +1501,41 @@
       <c r="U11" s="1">
         <v>8</v>
       </c>
-      <c r="AF11" s="11"/>
+      <c r="AF11" s="14"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="18"/>
+        <v>28</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="15"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="12"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="14"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1567,43 +1551,39 @@
       <c r="U12" s="1">
         <v>9</v>
       </c>
-      <c r="AF12" s="11"/>
+      <c r="AF12" s="14"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="18"/>
+        <v>29</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="15"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="12"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="14"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1619,41 +1599,39 @@
       <c r="U13" s="1">
         <v>10</v>
       </c>
-      <c r="AF13" s="11"/>
+      <c r="AF13" s="14"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="18"/>
+        <v>69</v>
+      </c>
+      <c r="H14" s="15"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="12"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="11"/>
+      <c r="P14" s="14"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1669,37 +1647,37 @@
       <c r="U14" s="1">
         <v>11</v>
       </c>
-      <c r="AF14" s="11"/>
+      <c r="AF14" s="14"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="12"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="K15" s="13"/>
+      <c r="L15" s="12"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="14"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1715,39 +1693,39 @@
       <c r="U15" s="1">
         <v>12</v>
       </c>
-      <c r="AF15" s="11"/>
+      <c r="AF15" s="14"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="15"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="12"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="11"/>
+      <c r="P16" s="14"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1763,41 +1741,41 @@
       <c r="U16" s="1">
         <v>13</v>
       </c>
-      <c r="AF16" s="11"/>
+      <c r="AF16" s="14"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="9"/>
+        <v>103</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="12"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="18"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="15"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="12"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="11"/>
+      <c r="P17" s="14"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1813,41 +1791,41 @@
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="AF17" s="11"/>
+      <c r="AF17" s="14"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="12"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="18"/>
+        <v>32</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="15"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="12"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="11"/>
+      <c r="P18" s="14"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1863,41 +1841,41 @@
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="AF18" s="11"/>
+      <c r="AF18" s="14"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="18"/>
+        <v>33</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="15"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="L19" s="9"/>
+        <v>110</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19" s="12"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="11"/>
+      <c r="P19" s="14"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -1913,428 +1891,428 @@
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="AF19" s="11"/>
+      <c r="AF19" s="14"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="12"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="18"/>
+        <v>34</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="15"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="12"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="AF20" s="11"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="AF20" s="14"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="12"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="18"/>
+        <v>35</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="15"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" s="21"/>
-      <c r="L21" s="9"/>
+        <v>112</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="11"/>
-      <c r="AF21" s="11"/>
+      <c r="P21" s="14"/>
+      <c r="AF21" s="14"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="18"/>
+        <v>36</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L22" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="L22" s="12"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="11"/>
-      <c r="AF22" s="11"/>
+      <c r="P22" s="14"/>
+      <c r="AF22" s="14"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="12"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="18"/>
+        <v>37</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="15"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="9"/>
+      <c r="L23" s="12"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="11"/>
-      <c r="AF23" s="11"/>
+      <c r="P23" s="14"/>
+      <c r="AF23" s="14"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="9"/>
+        <v>95</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="12"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="18"/>
+        <v>38</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L24" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="L24" s="12"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="11"/>
-      <c r="AF24" s="11"/>
+      <c r="P24" s="14"/>
+      <c r="AF24" s="14"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="18"/>
+        <v>39</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="9"/>
+      <c r="L25" s="12"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="11"/>
-      <c r="AF25" s="11"/>
+      <c r="P25" s="14"/>
+      <c r="AF25" s="14"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="9"/>
+        <v>97</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" s="18"/>
+        <v>110</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="15"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="9"/>
+        <v>53</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="12"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="11"/>
-      <c r="AF26" s="11"/>
+      <c r="P26" s="14"/>
+      <c r="AF26" s="14"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="12"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="20"/>
-      <c r="H27" s="18"/>
+        <v>111</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="15"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="9"/>
+        <v>51</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="12"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="11"/>
-      <c r="AF27" s="11"/>
+      <c r="P27" s="14"/>
+      <c r="AF27" s="14"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="12"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="21"/>
-      <c r="H28" s="18"/>
+        <v>112</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="12"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="11"/>
-      <c r="AF28" s="11"/>
+      <c r="P28" s="14"/>
+      <c r="AF28" s="14"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="12"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="15"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="9"/>
+      <c r="L29" s="12"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="11"/>
-      <c r="AF29" s="11"/>
+      <c r="P29" s="14"/>
+      <c r="AF29" s="14"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="12"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="18"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="9"/>
+      <c r="L30" s="12"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="11"/>
-      <c r="AF30" s="11"/>
+      <c r="P30" s="14"/>
+      <c r="AF30" s="14"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="12"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="H31" s="15"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="9"/>
+      <c r="L31" s="12"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="11"/>
-      <c r="AF31" s="11"/>
+      <c r="P31" s="14"/>
+      <c r="AF31" s="14"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2342,196 +2320,200 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="12"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="18"/>
+      <c r="F32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H32" s="15"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="L32" s="12"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="11"/>
-      <c r="AF32" s="11"/>
+      <c r="P32" s="14"/>
+      <c r="AF32" s="14"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="12"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H33" s="18"/>
+        <v>53</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="15"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="9"/>
+      <c r="L33" s="12"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="11"/>
-      <c r="AF33" s="11"/>
+      <c r="P33" s="14"/>
+      <c r="AF33" s="14"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="12"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="18"/>
+        <v>51</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="9"/>
+      <c r="L34" s="12"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="11"/>
-      <c r="AF34" s="11"/>
+      <c r="P34" s="14"/>
+      <c r="AF34" s="14"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="18"/>
+        <v>52</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="15"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="9"/>
+      <c r="L35" s="12"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="11"/>
-      <c r="AF35" s="11"/>
+      <c r="P35" s="14"/>
+      <c r="AF35" s="14"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="14"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="A37" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="A38" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2541,9 +2523,9 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D39" s="12"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2551,9 +2533,9 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="H39" s="20"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2561,9 +2543,9 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L39" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="L39" s="12"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2571,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
@@ -2581,30 +2563,30 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="9"/>
+      <c r="C40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="12"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="H40" s="16"/>
+        <v>115</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="20"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="L40" s="9"/>
+      <c r="K40" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="12"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2618,24 +2600,24 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="9"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="12"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="16"/>
+        <v>116</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="20"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="9"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="12"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2649,22 +2631,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="9"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="12"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="20"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="9"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="12"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2678,24 +2660,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="9"/>
+      <c r="C43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="12"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="16"/>
+      <c r="H43" s="20"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="9"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="12"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2709,22 +2691,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="9"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="12"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="16"/>
+      <c r="H44" s="20"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="9"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="12"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2738,22 +2720,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="9"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="12"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="16"/>
+      <c r="H45" s="20"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="9"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="12"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2765,26 +2747,26 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="12"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="16"/>
+      <c r="H46" s="20"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="9"/>
+        <v>56</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="12"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2796,24 +2778,24 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="12"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="16"/>
+      <c r="H47" s="20"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="9"/>
+        <v>57</v>
+      </c>
+      <c r="K47" s="13"/>
+      <c r="L47" s="12"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2825,24 +2807,24 @@
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="12"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="16"/>
+      <c r="H48" s="20"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="K48" s="13"/>
+      <c r="L48" s="12"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2854,26 +2836,26 @@
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="12"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="16"/>
+      <c r="H49" s="20"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="9"/>
+        <v>59</v>
+      </c>
+      <c r="K49" s="13"/>
+      <c r="L49" s="12"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2885,24 +2867,24 @@
         <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="C50" s="13"/>
+      <c r="D50" s="12"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="16"/>
+      <c r="H50" s="20"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="9"/>
+        <v>60</v>
+      </c>
+      <c r="K50" s="13"/>
+      <c r="L50" s="12"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2914,24 +2896,24 @@
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="C51" s="13"/>
+      <c r="D51" s="12"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="16"/>
+      <c r="H51" s="20"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="9"/>
+        <v>61</v>
+      </c>
+      <c r="K51" s="13"/>
+      <c r="L51" s="12"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2943,28 +2925,28 @@
         <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="12"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="16"/>
+      <c r="H52" s="20"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="L52" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L52" s="12"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2976,24 +2958,24 @@
         <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="C53" s="13"/>
+      <c r="D53" s="12"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="16"/>
+      <c r="H53" s="20"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="K53" s="13"/>
+      <c r="L53" s="12"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -3005,24 +2987,24 @@
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="12"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="16"/>
+      <c r="H54" s="20"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="9"/>
+        <v>64</v>
+      </c>
+      <c r="K54" s="13"/>
+      <c r="L54" s="12"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3034,28 +3016,28 @@
         <v>16</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D55" s="9"/>
+        <v>110</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="12"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="16"/>
+      <c r="H55" s="20"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L55" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="L55" s="12"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3067,24 +3049,24 @@
         <v>17</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="12"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="16"/>
+      <c r="H56" s="20"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K56" s="2"/>
-      <c r="L56" s="9"/>
+      <c r="L56" s="12"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3096,24 +3078,24 @@
         <v>18</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="9"/>
+        <v>112</v>
+      </c>
+      <c r="C57" s="11"/>
+      <c r="D57" s="12"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="16"/>
+      <c r="H57" s="20"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K57" s="2"/>
-      <c r="L57" s="9"/>
+      <c r="L57" s="12"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3125,28 +3107,28 @@
         <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="D58" s="12"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="16"/>
+      <c r="H58" s="20"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L58" s="9"/>
+        <v>69</v>
+      </c>
+      <c r="L58" s="12"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3158,26 +3140,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D59" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="D59" s="12"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="16"/>
+      <c r="H59" s="20"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="9"/>
+      <c r="L59" s="12"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3189,24 +3171,24 @@
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="D60" s="12"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="16"/>
+      <c r="H60" s="20"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="9"/>
+      <c r="L60" s="12"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3219,19 +3201,19 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="12"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="16"/>
+      <c r="H61" s="20"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="9"/>
+      <c r="L61" s="12"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3243,24 +3225,24 @@
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D62" s="9"/>
+        <v>53</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="12"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="16"/>
+      <c r="H62" s="20"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="9"/>
+      <c r="L62" s="12"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3272,22 +3254,22 @@
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="9"/>
+        <v>51</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="12"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="16"/>
+      <c r="H63" s="20"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="9"/>
+      <c r="L63" s="12"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3299,22 +3281,22 @@
         <v>25</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="C64" s="11"/>
+      <c r="D64" s="12"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="16"/>
+      <c r="H64" s="20"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="9"/>
+      <c r="L64" s="12"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3326,24 +3308,24 @@
         <v>26</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D65" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="D65" s="12"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="16"/>
+      <c r="H65" s="20"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="9"/>
+      <c r="L65" s="12"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3356,19 +3338,19 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="12"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="16"/>
+      <c r="H66" s="20"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="9"/>
+      <c r="L66" s="12"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3380,22 +3362,22 @@
         <v>28</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="12"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="16"/>
+      <c r="H67" s="20"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="9"/>
+      <c r="L67" s="12"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3408,19 +3390,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="12"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="16"/>
+      <c r="H68" s="20"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="9"/>
+      <c r="L68" s="12"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3433,19 +3415,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="9"/>
+      <c r="D69" s="12"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="16"/>
+      <c r="H69" s="20"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="9"/>
+      <c r="L69" s="12"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3458,19 +3440,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="12"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="16"/>
+      <c r="H70" s="20"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="9"/>
+      <c r="L70" s="12"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3483,19 +3465,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="12"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="17"/>
+      <c r="H71" s="21"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="9"/>
+      <c r="L71" s="12"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3504,6 +3486,48 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="C43:C45"/>
     <mergeCell ref="C55:C57"/>
     <mergeCell ref="C62:C64"/>
     <mergeCell ref="G40:G41"/>
@@ -3520,48 +3544,6 @@
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="K26:K28"/>
     <mergeCell ref="C52:C54"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC343C7-E2F8-41B8-89C5-34230C50D488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2236CD71-180B-4C71-B8C3-650D700603CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="140">
   <si>
     <t>Freq:</t>
   </si>
@@ -392,12 +392,6 @@
     <t>laser slew</t>
   </si>
   <si>
-    <t>friend x / enemy x</t>
-  </si>
-  <si>
-    <t>friend y / enemy y</t>
-  </si>
-  <si>
     <t>datalink send freq</t>
   </si>
   <si>
@@ -405,6 +399,63 @@
   </si>
   <si>
     <t>debug number</t>
+  </si>
+  <si>
+    <t>radar 1</t>
+  </si>
+  <si>
+    <t>radar 2</t>
+  </si>
+  <si>
+    <t>radar 3</t>
+  </si>
+  <si>
+    <t>radar 4</t>
+  </si>
+  <si>
+    <t>emission target 1</t>
+  </si>
+  <si>
+    <t>emission target 2</t>
+  </si>
+  <si>
+    <t>emission target 3</t>
+  </si>
+  <si>
+    <t>emission target 4</t>
+  </si>
+  <si>
+    <t>emission target 5</t>
+  </si>
+  <si>
+    <t>emission target 6</t>
+  </si>
+  <si>
+    <t>emission target 7</t>
+  </si>
+  <si>
+    <t>emission target 8</t>
+  </si>
+  <si>
+    <t>emission target 9</t>
+  </si>
+  <si>
+    <t>emission target 10</t>
+  </si>
+  <si>
+    <t>enemy x</t>
+  </si>
+  <si>
+    <t>enemy y</t>
+  </si>
+  <si>
+    <t>friend y</t>
+  </si>
+  <si>
+    <t>friend x</t>
+  </si>
+  <si>
+    <t>enemy xy</t>
   </si>
 </sst>
 </file>
@@ -594,6 +645,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -601,12 +658,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -972,8 +1023,8 @@
     <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="12" style="1" customWidth="1"/>
     <col min="22" max="22" width="12.140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" style="1"/>
+    <col min="23" max="23" width="5.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="17.85546875" style="1" customWidth="1"/>
     <col min="25" max="25" width="6.85546875" style="1" customWidth="1"/>
     <col min="26" max="26" width="22.85546875" style="1" customWidth="1"/>
     <col min="27" max="27" width="19.42578125" style="1" customWidth="1"/>
@@ -985,25 +1036,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
       <c r="H1" s="15"/>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
       <c r="P1" s="14"/>
       <c r="Q1" s="14" t="s">
         <v>85</v>
@@ -1015,29 +1066,29 @@
       <c r="AF1" s="14"/>
     </row>
     <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="1" t="s">
         <v>79</v>
@@ -1063,7 +1114,7 @@
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1134,7 @@
       <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="12"/>
+      <c r="L3" s="9"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1109,6 +1160,12 @@
       <c r="U3" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="W3" s="1">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="AF3" s="14"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1118,17 +1175,17 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="9"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="13"/>
+        <v>120</v>
+      </c>
+      <c r="G4" s="10"/>
       <c r="H4" s="15"/>
       <c r="I4" s="2">
         <v>1</v>
@@ -1136,10 +1193,10 @@
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="12"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
@@ -1161,6 +1218,12 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
+      <c r="W4" s="1">
+        <v>2</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="AF4" s="14"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -1170,13 +1233,13 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="10"/>
       <c r="H5" s="15"/>
       <c r="I5" s="2">
         <v>2</v>
@@ -1184,8 +1247,8 @@
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="9"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
@@ -1207,6 +1270,12 @@
       <c r="U5" s="1">
         <v>2</v>
       </c>
+      <c r="W5" s="1">
+        <v>3</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="AF5" s="14"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1216,16 +1285,16 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="12"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="2">
@@ -1234,8 +1303,8 @@
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
@@ -1257,6 +1326,12 @@
       <c r="U6" s="1">
         <v>3</v>
       </c>
+      <c r="W6" s="1">
+        <v>4</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="AF6" s="14"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1266,10 +1341,10 @@
       <c r="B7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
@@ -1282,10 +1357,10 @@
       <c r="J7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="L7" s="9"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
@@ -1307,6 +1382,12 @@
       <c r="U7" s="1">
         <v>4</v>
       </c>
+      <c r="W7" s="1">
+        <v>5</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="AF7" s="14"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1316,8 +1397,8 @@
       <c r="B8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="12"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
@@ -1330,8 +1411,8 @@
       <c r="J8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="12"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -1353,6 +1434,12 @@
       <c r="U8" s="1">
         <v>5</v>
       </c>
+      <c r="W8" s="1">
+        <v>6</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="AF8" s="14"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1362,8 +1449,8 @@
       <c r="B9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
@@ -1376,8 +1463,8 @@
       <c r="J9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="12"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="9"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
@@ -1399,6 +1486,12 @@
       <c r="U9" s="1">
         <v>6</v>
       </c>
+      <c r="W9" s="1">
+        <v>7</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="AF9" s="14"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1406,19 +1499,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="12"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="10" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="15"/>
@@ -1428,10 +1521,10 @@
       <c r="J10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
@@ -1453,6 +1546,12 @@
       <c r="U10" s="1">
         <v>7</v>
       </c>
+      <c r="W10" s="1">
+        <v>8</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="AF10" s="14"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1460,17 +1559,17 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="12"/>
+        <v>137</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="10"/>
       <c r="H11" s="15"/>
       <c r="I11" s="2">
         <v>8</v>
@@ -1478,8 +1577,8 @@
       <c r="J11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="12"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
@@ -1501,6 +1600,12 @@
       <c r="U11" s="1">
         <v>8</v>
       </c>
+      <c r="W11" s="1">
+        <v>9</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="AF11" s="14"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1510,15 +1615,15 @@
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="12"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="10" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="15"/>
@@ -1528,8 +1633,8 @@
       <c r="J12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="12"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
@@ -1551,22 +1656,32 @@
       <c r="U12" s="1">
         <v>9</v>
       </c>
+      <c r="W12" s="1">
+        <v>10</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="AF12" s="14"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="10"/>
       <c r="H13" s="15"/>
       <c r="I13" s="2">
         <v>10</v>
@@ -1574,10 +1689,10 @@
       <c r="J13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="L13" s="9"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
@@ -1599,15 +1714,23 @@
       <c r="U13" s="1">
         <v>10</v>
       </c>
+      <c r="W13" s="1">
+        <v>11</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="AF13" s="14"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="12"/>
+      <c r="B14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
@@ -1624,8 +1747,8 @@
       <c r="J14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="12"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
@@ -1647,6 +1770,12 @@
       <c r="U14" s="1">
         <v>11</v>
       </c>
+      <c r="W14" s="1">
+        <v>12</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="AF14" s="14"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1656,10 +1785,10 @@
       <c r="B15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
@@ -1670,8 +1799,8 @@
       <c r="J15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="13"/>
-      <c r="L15" s="12"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="9"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
@@ -1693,6 +1822,12 @@
       <c r="U15" s="1">
         <v>12</v>
       </c>
+      <c r="W15" s="1">
+        <v>13</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="AF15" s="14"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1702,8 +1837,8 @@
       <c r="B16" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="12"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
@@ -1716,10 +1851,10 @@
       <c r="J16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L16" s="12"/>
+      <c r="L16" s="9"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
@@ -1741,6 +1876,12 @@
       <c r="U16" s="1">
         <v>13</v>
       </c>
+      <c r="W16" s="1">
+        <v>14</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="AF16" s="14"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
@@ -1750,15 +1891,15 @@
       <c r="B17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="12"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="10" t="s">
         <v>48</v>
       </c>
       <c r="H17" s="15"/>
@@ -1768,8 +1909,8 @@
       <c r="J17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="9"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
@@ -1800,17 +1941,17 @@
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="13"/>
+      <c r="G18" s="10"/>
       <c r="H18" s="15"/>
       <c r="I18" s="2">
         <v>15</v>
@@ -1818,8 +1959,8 @@
       <c r="J18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="13"/>
-      <c r="L18" s="12"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="9"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
@@ -1850,15 +1991,15 @@
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="12"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="13"/>
+      <c r="G19" s="10"/>
       <c r="H19" s="15"/>
       <c r="I19" s="2">
         <v>16</v>
@@ -1866,10 +2007,10 @@
       <c r="J19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="L19" s="12"/>
+      <c r="L19" s="9"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
@@ -1900,15 +2041,15 @@
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="10" t="s">
         <v>49</v>
       </c>
       <c r="H20" s="15"/>
@@ -1918,8 +2059,8 @@
       <c r="J20" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="9"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
@@ -1942,17 +2083,17 @@
       <c r="B21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="12"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="13"/>
+      <c r="G21" s="10"/>
       <c r="H21" s="15"/>
       <c r="I21" s="2">
         <v>18</v>
@@ -1960,8 +2101,8 @@
       <c r="J21" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="12"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="9"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
@@ -1977,15 +2118,15 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="12"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="13"/>
+      <c r="G22" s="10"/>
       <c r="H22" s="15"/>
       <c r="I22" s="2">
         <v>19</v>
@@ -1996,7 +2137,7 @@
       <c r="K22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L22" s="12"/>
+      <c r="L22" s="9"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
@@ -2012,15 +2153,15 @@
       <c r="B23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="12"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="10" t="s">
         <v>50</v>
       </c>
       <c r="H23" s="15"/>
@@ -2031,7 +2172,7 @@
         <v>105</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="12"/>
+      <c r="L23" s="9"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
@@ -2047,17 +2188,17 @@
       <c r="B24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="12"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="13"/>
+      <c r="G24" s="10"/>
       <c r="H24" s="15"/>
       <c r="I24" s="2">
         <v>21</v>
@@ -2068,7 +2209,7 @@
       <c r="K24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="L24" s="9"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
@@ -2084,22 +2225,22 @@
       <c r="B25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="13"/>
+      <c r="G25" s="10"/>
       <c r="H25" s="15"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="12"/>
+      <c r="L25" s="9"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
@@ -2115,15 +2256,15 @@
       <c r="B26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="11" t="s">
         <v>113</v>
       </c>
       <c r="H26" s="15"/>
@@ -2133,10 +2274,10 @@
       <c r="J26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="L26" s="12"/>
+      <c r="L26" s="9"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
@@ -2152,17 +2293,17 @@
       <c r="B27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="12"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="10"/>
+      <c r="G27" s="12"/>
       <c r="H27" s="15"/>
       <c r="I27" s="2">
         <v>24</v>
@@ -2170,8 +2311,8 @@
       <c r="J27" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K27" s="13"/>
-      <c r="L27" s="12"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="9"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
@@ -2187,15 +2328,15 @@
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="12"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="13"/>
       <c r="H28" s="15"/>
       <c r="I28" s="2">
         <v>25</v>
@@ -2203,8 +2344,8 @@
       <c r="J28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K28" s="13"/>
-      <c r="L28" s="12"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="9"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
@@ -2220,8 +2361,8 @@
       <c r="B29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="12"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
@@ -2239,7 +2380,7 @@
         <v>74</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="12"/>
+      <c r="L29" s="9"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
@@ -2256,7 +2397,7 @@
         <v>90</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="12"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
@@ -2270,7 +2411,7 @@
         <v>104</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="9"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
@@ -2287,7 +2428,7 @@
         <v>89</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="12"/>
+      <c r="D31" s="9"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
@@ -2305,7 +2446,7 @@
         <v>68</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="12"/>
+      <c r="L31" s="9"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
@@ -2320,15 +2461,15 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="12"/>
+      <c r="D32" s="9"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="2">
@@ -2340,7 +2481,7 @@
       <c r="K32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="L32" s="9"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
@@ -2356,17 +2497,17 @@
       <c r="B33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="12"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H33" s="15"/>
@@ -2377,7 +2518,7 @@
         <v>75</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="12"/>
+      <c r="L33" s="9"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
@@ -2393,15 +2534,15 @@
       <c r="B34" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="9"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G34" s="13"/>
+      <c r="G34" s="10"/>
       <c r="H34" s="15"/>
       <c r="I34" s="2">
         <v>31</v>
@@ -2410,7 +2551,7 @@
         <v>86</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="12"/>
+      <c r="L34" s="9"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
@@ -2426,15 +2567,15 @@
       <c r="B35" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="13"/>
+      <c r="G35" s="10"/>
       <c r="H35" s="15"/>
       <c r="I35" s="2">
         <v>32</v>
@@ -2443,7 +2584,7 @@
         <v>106</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="12"/>
+      <c r="L35" s="9"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
@@ -2470,50 +2611,50 @@
       <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="19"/>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
       <c r="H38" s="20"/>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12" t="s">
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2525,7 +2666,7 @@
       <c r="C39" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="12"/>
+      <c r="D39" s="9"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2545,7 +2686,7 @@
       <c r="K39" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="12"/>
+      <c r="L39" s="9"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2563,17 +2704,17 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="12"/>
+      <c r="D40" s="9"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="11" t="s">
         <v>117</v>
       </c>
       <c r="H40" s="20"/>
@@ -2583,10 +2724,10 @@
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L40" s="12"/>
+      <c r="L40" s="9"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2600,15 +2741,15 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="13"/>
-      <c r="D41" s="12"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G41" s="11"/>
+      <c r="G41" s="13"/>
       <c r="H41" s="20"/>
       <c r="I41" s="2">
         <v>2</v>
@@ -2616,8 +2757,8 @@
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="13"/>
-      <c r="L41" s="12"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="9"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2631,8 +2772,8 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="12"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
@@ -2645,8 +2786,8 @@
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="13"/>
-      <c r="L42" s="12"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="9"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2660,10 +2801,10 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="12"/>
+      <c r="D43" s="9"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
@@ -2676,8 +2817,8 @@
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="13"/>
-      <c r="L43" s="12"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="9"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2691,8 +2832,8 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="12"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
@@ -2705,8 +2846,8 @@
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="13"/>
-      <c r="L44" s="12"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="9"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2720,8 +2861,8 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="13"/>
-      <c r="D45" s="12"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
@@ -2734,8 +2875,8 @@
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="13"/>
-      <c r="L45" s="12"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="9"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2749,10 +2890,10 @@
       <c r="B46" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="12"/>
+      <c r="D46" s="9"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
@@ -2765,8 +2906,8 @@
       <c r="J46" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K46" s="13"/>
-      <c r="L46" s="12"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="9"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2780,8 +2921,8 @@
       <c r="B47" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="12"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="9"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
@@ -2794,8 +2935,8 @@
       <c r="J47" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K47" s="13"/>
-      <c r="L47" s="12"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="9"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2809,8 +2950,8 @@
       <c r="B48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="12"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
@@ -2823,8 +2964,8 @@
       <c r="J48" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K48" s="13"/>
-      <c r="L48" s="12"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="9"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2838,10 +2979,10 @@
       <c r="B49" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="12"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
@@ -2854,8 +2995,8 @@
       <c r="J49" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K49" s="13"/>
-      <c r="L49" s="12"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="9"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -2869,8 +3010,8 @@
       <c r="B50" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="12"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
@@ -2883,8 +3024,8 @@
       <c r="J50" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K50" s="13"/>
-      <c r="L50" s="12"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="9"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -2898,8 +3039,8 @@
       <c r="B51" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="12"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
@@ -2912,8 +3053,8 @@
       <c r="J51" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K51" s="13"/>
-      <c r="L51" s="12"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="9"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -2927,10 +3068,10 @@
       <c r="B52" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D52" s="12"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
@@ -2943,10 +3084,10 @@
       <c r="J52" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K52" s="13" t="s">
+      <c r="K52" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L52" s="12"/>
+      <c r="L52" s="9"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -2960,8 +3101,8 @@
       <c r="B53" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="13"/>
-      <c r="D53" s="12"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="9"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
@@ -2974,8 +3115,8 @@
       <c r="J53" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="13"/>
-      <c r="L53" s="12"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="9"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -2989,8 +3130,8 @@
       <c r="B54" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="12"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
@@ -3003,8 +3144,8 @@
       <c r="J54" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K54" s="13"/>
-      <c r="L54" s="12"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="9"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3018,10 +3159,10 @@
       <c r="B55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="12"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
@@ -3037,7 +3178,7 @@
       <c r="K55" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L55" s="12"/>
+      <c r="L55" s="9"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3051,8 +3192,8 @@
       <c r="B56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
@@ -3066,7 +3207,7 @@
         <v>68</v>
       </c>
       <c r="K56" s="2"/>
-      <c r="L56" s="12"/>
+      <c r="L56" s="9"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3080,8 +3221,8 @@
       <c r="B57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="11"/>
-      <c r="D57" s="12"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
@@ -3095,7 +3236,7 @@
         <v>74</v>
       </c>
       <c r="K57" s="2"/>
-      <c r="L57" s="12"/>
+      <c r="L57" s="9"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3112,7 +3253,7 @@
       <c r="C58" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D58" s="12"/>
+      <c r="D58" s="9"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
@@ -3128,7 +3269,7 @@
       <c r="K58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L58" s="12"/>
+      <c r="L58" s="9"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3145,7 +3286,7 @@
       <c r="C59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="12"/>
+      <c r="D59" s="9"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
@@ -3159,7 +3300,7 @@
         <v>72</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="12"/>
+      <c r="L59" s="9"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3176,7 +3317,7 @@
       <c r="C60" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="12"/>
+      <c r="D60" s="9"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
@@ -3188,7 +3329,7 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="12"/>
+      <c r="L60" s="9"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3201,7 +3342,7 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="4"/>
-      <c r="D61" s="12"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
@@ -3213,7 +3354,7 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="12"/>
+      <c r="L61" s="9"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3227,10 +3368,10 @@
       <c r="B62" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="12"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
@@ -3242,7 +3383,7 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="12"/>
+      <c r="L62" s="9"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3256,8 +3397,8 @@
       <c r="B63" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
@@ -3269,7 +3410,7 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="12"/>
+      <c r="L63" s="9"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3283,8 +3424,8 @@
       <c r="B64" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="11"/>
-      <c r="D64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
@@ -3296,7 +3437,7 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="12"/>
+      <c r="L64" s="9"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3313,7 +3454,7 @@
       <c r="C65" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="12"/>
+      <c r="D65" s="9"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
@@ -3325,7 +3466,7 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="12"/>
+      <c r="L65" s="9"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3338,7 +3479,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="12"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
@@ -3350,7 +3491,7 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="12"/>
+      <c r="L66" s="9"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3365,7 +3506,7 @@
         <v>88</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="12"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
@@ -3377,7 +3518,7 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="12"/>
+      <c r="L67" s="9"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3390,7 +3531,7 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="12"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
@@ -3402,7 +3543,7 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="12"/>
+      <c r="L68" s="9"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3415,7 +3556,7 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="12"/>
+      <c r="D69" s="9"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
@@ -3427,7 +3568,7 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="12"/>
+      <c r="L69" s="9"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3440,7 +3581,7 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="12"/>
+      <c r="D70" s="9"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
@@ -3452,7 +3593,7 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="12"/>
+      <c r="L70" s="9"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3465,7 +3606,7 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="12"/>
+      <c r="D71" s="9"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
@@ -3477,7 +3618,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="12"/>
+      <c r="L71" s="9"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3491,6 +3632,10 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G17:G19"/>
     <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
     <mergeCell ref="Q20:U20"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="C46:C48"/>
@@ -3523,15 +3668,12 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="C55:C57"/>
     <mergeCell ref="C62:C64"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C52:C54"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:L35"/>
@@ -3543,7 +3685,6 @@
     <mergeCell ref="K16:K18"/>
     <mergeCell ref="K19:K21"/>
     <mergeCell ref="K26:K28"/>
-    <mergeCell ref="C52:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2236CD71-180B-4C71-B8C3-650D700603CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BAD0B5-FCB1-4BC3-BB73-B5093A5D7CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="3600" windowWidth="29040" windowHeight="15720" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="38400" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="146">
   <si>
     <t>Freq:</t>
   </si>
@@ -62,9 +62,6 @@
     <t>rz</t>
   </si>
   <si>
-    <t>friend z</t>
-  </si>
-  <si>
     <t>old r x</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>my xyz</t>
   </si>
   <si>
-    <t>friend xyz</t>
-  </si>
-  <si>
     <t>my rot</t>
   </si>
   <si>
@@ -323,15 +317,6 @@
     <t>my rz</t>
   </si>
   <si>
-    <t>friend selected x</t>
-  </si>
-  <si>
-    <t>friend selected y</t>
-  </si>
-  <si>
-    <t>friend selected z</t>
-  </si>
-  <si>
     <t>time since detected scan radar 2</t>
   </si>
   <si>
@@ -365,9 +350,6 @@
     <t>friendly trans index</t>
   </si>
   <si>
-    <t>friendly selected</t>
-  </si>
-  <si>
     <t>friend selected1 x</t>
   </si>
   <si>
@@ -398,9 +380,6 @@
     <t>datalink receive freq</t>
   </si>
   <si>
-    <t>debug number</t>
-  </si>
-  <si>
     <t>radar 1</t>
   </si>
   <si>
@@ -449,13 +428,52 @@
     <t>enemy y</t>
   </si>
   <si>
-    <t>friend y</t>
-  </si>
-  <si>
-    <t>friend x</t>
-  </si>
-  <si>
     <t>enemy xy</t>
+  </si>
+  <si>
+    <t>encrypted mpos</t>
+  </si>
+  <si>
+    <t>encrypted my pos x</t>
+  </si>
+  <si>
+    <t>encrypted my pos y</t>
+  </si>
+  <si>
+    <t>encrypted my pos z</t>
+  </si>
+  <si>
+    <t>encrypted my sel pos x</t>
+  </si>
+  <si>
+    <t>encrypted my sel pos y</t>
+  </si>
+  <si>
+    <t>encrypted my sel pos z</t>
+  </si>
+  <si>
+    <t>encrypted friend x</t>
+  </si>
+  <si>
+    <t>encrypted friend y</t>
+  </si>
+  <si>
+    <t>encrypted friend z</t>
+  </si>
+  <si>
+    <t>encrypted friend xyz</t>
+  </si>
+  <si>
+    <t>encrypted friend selected x</t>
+  </si>
+  <si>
+    <t>encrypted friend selected y</t>
+  </si>
+  <si>
+    <t>encrypted friend selected z</t>
+  </si>
+  <si>
+    <t>encrypted friendly selected</t>
   </si>
 </sst>
 </file>
@@ -619,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -638,12 +656,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1036,73 +1048,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="AF1" s="12"/>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="AF1" s="14"/>
-    </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="14"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="12"/>
       <c r="Q2" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF2" s="14"/>
+      <c r="AF2" s="12"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1112,9 +1124,9 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="D3" s="7"/>
       <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1122,9 +1134,9 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="H3" s="13"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1132,9 +1144,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="L3" s="7"/>
       <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1142,31 +1154,31 @@
         <v>1</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="14"/>
+        <v>23</v>
+      </c>
+      <c r="P3" s="12"/>
       <c r="Q3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="W3" s="1">
         <v>1</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF3" s="14"/>
+        <v>114</v>
+      </c>
+      <c r="AF3" s="12"/>
     </row>
     <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -1175,34 +1187,32 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="9"/>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="15"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="9"/>
+      <c r="K4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="7"/>
       <c r="M4" s="2">
         <v>1</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="14"/>
+      <c r="P4" s="12"/>
       <c r="Q4" s="5" t="b">
         <v>1</v>
       </c>
@@ -1222,9 +1232,9 @@
         <v>2</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF4" s="14"/>
+        <v>115</v>
+      </c>
+      <c r="AF4" s="12"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1233,28 +1243,30 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="7"/>
       <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="15"/>
+      <c r="F5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="9"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="7"/>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="14"/>
+      <c r="P5" s="12"/>
       <c r="Q5" s="5" t="b">
         <v>1</v>
       </c>
@@ -1274,9 +1286,9 @@
         <v>3</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF5" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="AF5" s="12"/>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1285,32 +1297,32 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="2">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="15"/>
+        <v>113</v>
+      </c>
+      <c r="H6" s="13"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="9"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="7"/>
       <c r="M6" s="2">
         <v>3</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="14"/>
+      <c r="P6" s="12"/>
       <c r="Q6" s="5" t="b">
         <v>1</v>
       </c>
@@ -1330,43 +1342,47 @@
         <v>4</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF6" s="14"/>
+        <v>117</v>
+      </c>
+      <c r="AF6" s="12"/>
     </row>
     <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7"/>
       <c r="E7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="15"/>
+      <c r="F7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="13"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="7"/>
       <c r="M7" s="2">
         <v>4</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="14"/>
+      <c r="P7" s="12"/>
       <c r="Q7" s="5" t="b">
         <v>1</v>
       </c>
@@ -1386,39 +1402,41 @@
         <v>5</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF7" s="14"/>
+        <v>118</v>
+      </c>
+      <c r="AF7" s="12"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="2">
         <v>5</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="15"/>
+      <c r="F8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="7"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="14"/>
+      <c r="P8" s="12"/>
       <c r="Q8" s="5" t="b">
         <v>1</v>
       </c>
@@ -1438,39 +1456,41 @@
         <v>6</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF8" s="14"/>
+        <v>119</v>
+      </c>
+      <c r="AF8" s="12"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="15"/>
+      <c r="F9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="7"/>
       <c r="M9" s="2">
         <v>6</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="14"/>
+      <c r="P9" s="12"/>
       <c r="Q9" s="5" t="b">
         <v>1</v>
       </c>
@@ -1490,9 +1510,9 @@
         <v>7</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF9" s="14"/>
+        <v>120</v>
+      </c>
+      <c r="AF9" s="12"/>
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1501,36 +1521,36 @@
       <c r="B10" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9"/>
+      <c r="C10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="2">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="13"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="7"/>
       <c r="M10" s="2">
         <v>7</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="14"/>
+      <c r="P10" s="12"/>
       <c r="Q10" s="5" t="b">
         <v>1</v>
       </c>
@@ -1550,41 +1570,41 @@
         <v>8</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF10" s="14"/>
+        <v>121</v>
+      </c>
+      <c r="AF10" s="12"/>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
+        <v>139</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="2">
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="15"/>
+        <v>42</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="13"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="7"/>
       <c r="M11" s="2">
         <v>8</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="14"/>
+      <c r="P11" s="12"/>
       <c r="Q11" s="5" t="b">
         <v>1</v>
       </c>
@@ -1604,43 +1624,43 @@
         <v>9</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF11" s="14"/>
+        <v>122</v>
+      </c>
+      <c r="AF11" s="12"/>
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="2">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="13"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="7"/>
       <c r="M12" s="2">
         <v>9</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="14"/>
+      <c r="P12" s="12"/>
       <c r="Q12" s="6" t="b">
         <v>0</v>
       </c>
@@ -1660,45 +1680,45 @@
         <v>10</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF12" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="AF12" s="12"/>
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="9"/>
+        <v>128</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="7"/>
       <c r="E13" s="2">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="7"/>
       <c r="M13" s="2">
         <v>10</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="14"/>
+      <c r="P13" s="12"/>
       <c r="Q13" s="6" t="b">
         <v>0</v>
       </c>
@@ -1718,43 +1738,43 @@
         <v>11</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AF13" s="14"/>
+        <v>124</v>
+      </c>
+      <c r="AF13" s="12"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
+        <v>129</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="15"/>
+        <v>67</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="14"/>
+      <c r="P14" s="12"/>
       <c r="Q14" s="6" t="b">
         <v>0</v>
       </c>
@@ -1774,39 +1794,42 @@
         <v>12</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AF14" s="14"/>
+        <v>125</v>
+      </c>
+      <c r="AF14" s="12"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="9"/>
+        <v>96</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="7"/>
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="15"/>
+      <c r="F15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" s="13"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="7"/>
       <c r="M15" s="2">
         <v>12</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="14"/>
+      <c r="P15" s="12"/>
       <c r="Q15" s="6" t="b">
         <v>0</v>
       </c>
@@ -1826,41 +1849,43 @@
         <v>13</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF15" s="14"/>
+        <v>126</v>
+      </c>
+      <c r="AF15" s="12"/>
     </row>
     <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
+        <v>97</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="2">
         <v>13</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L16" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="7"/>
       <c r="M16" s="2">
         <v>13</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="14"/>
+      <c r="P16" s="12"/>
       <c r="Q16" s="6" t="b">
         <v>0</v>
       </c>
@@ -1880,43 +1905,43 @@
         <v>14</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF16" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="AF16" s="12"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="13"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="7"/>
       <c r="M17" s="2">
         <v>14</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
-      <c r="P17" s="14"/>
+      <c r="P17" s="12"/>
       <c r="Q17" s="6" t="b">
         <v>0</v>
       </c>
@@ -1932,41 +1957,41 @@
       <c r="U17" s="1">
         <v>14</v>
       </c>
-      <c r="AF17" s="14"/>
+      <c r="AF17" s="12"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="7"/>
       <c r="E18" s="2">
         <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="7"/>
       <c r="M18" s="2">
         <v>15</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-      <c r="P18" s="14"/>
+      <c r="P18" s="12"/>
       <c r="Q18" s="6" t="b">
         <v>0</v>
       </c>
@@ -1982,41 +2007,41 @@
       <c r="U18" s="1">
         <v>15</v>
       </c>
-      <c r="AF18" s="14"/>
+      <c r="AF18" s="12"/>
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="2">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="15"/>
+        <v>31</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="L19" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" s="7"/>
       <c r="M19" s="2">
         <v>16</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="14"/>
+      <c r="P19" s="12"/>
       <c r="Q19" s="6" t="b">
         <v>0</v>
       </c>
@@ -2032,428 +2057,428 @@
       <c r="U19" s="1">
         <v>16</v>
       </c>
-      <c r="AF19" s="14"/>
+      <c r="AF19" s="12"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="2">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="13"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="9"/>
+        <v>105</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="2">
         <v>17</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="AF20" s="14"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="AF20" s="12"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="C21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7"/>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="13"/>
-      <c r="L21" s="9"/>
+        <v>106</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="7"/>
       <c r="M21" s="2">
         <v>18</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="14"/>
-      <c r="AF21" s="14"/>
+      <c r="P21" s="12"/>
+      <c r="AF21" s="12"/>
     </row>
     <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="2">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="15"/>
+        <v>34</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L22" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="L22" s="7"/>
       <c r="M22" s="2">
         <v>19</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="14"/>
-      <c r="AF22" s="14"/>
+      <c r="P22" s="12"/>
+      <c r="AF22" s="12"/>
     </row>
     <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="2">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="13"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="9"/>
+      <c r="L23" s="7"/>
       <c r="M23" s="2">
         <v>20</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="14"/>
-      <c r="AF23" s="14"/>
+      <c r="P23" s="12"/>
+      <c r="AF23" s="12"/>
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="9"/>
+        <v>142</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="7"/>
       <c r="E24" s="2">
         <v>21</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="13"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L24" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="L24" s="7"/>
       <c r="M24" s="2">
         <v>21</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="14"/>
-      <c r="AF24" s="14"/>
+      <c r="P24" s="12"/>
+      <c r="AF24" s="12"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="9"/>
+        <v>143</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="2">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="13"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="9"/>
+      <c r="L25" s="7"/>
       <c r="M25" s="2">
         <v>22</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
-      <c r="P25" s="14"/>
-      <c r="AF25" s="14"/>
+      <c r="P25" s="12"/>
+      <c r="AF25" s="12"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="9"/>
+        <v>144</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="2">
         <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="15"/>
+        <v>104</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="13"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="L26" s="9"/>
+        <v>51</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="7"/>
       <c r="M26" s="2">
         <v>23</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="14"/>
-      <c r="AF26" s="14"/>
+      <c r="P26" s="12"/>
+      <c r="AF26" s="12"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7"/>
       <c r="E27" s="2">
         <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="15"/>
+        <v>105</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="13"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="7"/>
       <c r="M27" s="2">
         <v>24</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
-      <c r="P27" s="14"/>
-      <c r="AF27" s="14"/>
+      <c r="P27" s="12"/>
+      <c r="AF27" s="12"/>
     </row>
     <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="2">
         <v>25</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15"/>
+        <v>106</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="13"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="7"/>
       <c r="M28" s="2">
         <v>25</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-      <c r="P28" s="14"/>
-      <c r="AF28" s="14"/>
+      <c r="P28" s="12"/>
+      <c r="AF28" s="12"/>
     </row>
     <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="2">
         <v>26</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H29" s="13"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K29" s="2"/>
-      <c r="L29" s="9"/>
+      <c r="L29" s="7"/>
       <c r="M29" s="2">
         <v>26</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="14"/>
-      <c r="AF29" s="14"/>
+      <c r="P29" s="12"/>
+      <c r="AF29" s="12"/>
     </row>
     <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="2">
         <v>27</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="15"/>
+      <c r="H30" s="13"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="9"/>
+      <c r="L30" s="7"/>
       <c r="M30" s="2">
         <v>27</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
-      <c r="P30" s="14"/>
-      <c r="AF30" s="14"/>
+      <c r="P30" s="12"/>
+      <c r="AF30" s="12"/>
     </row>
     <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="2">
         <v>28</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="H31" s="13"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="9"/>
+      <c r="L31" s="7"/>
       <c r="M31" s="2">
         <v>28</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
-      <c r="P31" s="14"/>
-      <c r="AF31" s="14"/>
+      <c r="P31" s="12"/>
+      <c r="AF31" s="12"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2461,200 +2486,200 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="2">
         <v>29</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H32" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="H32" s="13"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L32" s="9"/>
+        <v>68</v>
+      </c>
+      <c r="L32" s="7"/>
       <c r="M32" s="2">
         <v>29</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
-      <c r="P32" s="14"/>
-      <c r="AF32" s="14"/>
+      <c r="P32" s="12"/>
+      <c r="AF32" s="12"/>
     </row>
     <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="7"/>
       <c r="E33" s="2">
         <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="H33" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="13"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="9"/>
+      <c r="L33" s="7"/>
       <c r="M33" s="2">
         <v>30</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="14"/>
-      <c r="AF33" s="14"/>
+      <c r="P33" s="12"/>
+      <c r="AF33" s="12"/>
     </row>
     <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="2">
         <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="15"/>
+        <v>49</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="9"/>
+      <c r="L34" s="7"/>
       <c r="M34" s="2">
         <v>31</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="14"/>
-      <c r="AF34" s="14"/>
+      <c r="P34" s="12"/>
+      <c r="AF34" s="12"/>
     </row>
     <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="9"/>
+        <v>94</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="2">
         <v>32</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="13"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="9"/>
+      <c r="L35" s="7"/>
       <c r="M35" s="2">
         <v>32</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="14"/>
-      <c r="AF35" s="14"/>
+      <c r="P35" s="12"/>
+      <c r="AF35" s="12"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="18"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="A37" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="A38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2664,9 +2689,9 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D39" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="D39" s="7"/>
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2674,9 +2699,9 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="20"/>
+        <v>23</v>
+      </c>
+      <c r="H39" s="18"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2684,9 +2709,9 @@
         <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="L39" s="7"/>
       <c r="M39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2694,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
@@ -2704,30 +2729,30 @@
       <c r="B40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="9"/>
+      <c r="C40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="7"/>
       <c r="E40" s="2">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H40" s="20"/>
+        <v>109</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" s="18"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L40" s="9"/>
+      <c r="K40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L40" s="7"/>
       <c r="M40" s="2">
         <v>1</v>
       </c>
@@ -2741,24 +2766,24 @@
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="9"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="2">
         <v>2</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="20"/>
+        <v>110</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="18"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="9"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="7"/>
       <c r="M41" s="2">
         <v>2</v>
       </c>
@@ -2772,22 +2797,22 @@
       <c r="B42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="9"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="20"/>
+      <c r="H42" s="18"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="9"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="7"/>
       <c r="M42" s="2">
         <v>3</v>
       </c>
@@ -2801,24 +2826,24 @@
       <c r="B43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" s="9"/>
+      <c r="C43" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="7"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="20"/>
+      <c r="H43" s="18"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="9"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="7"/>
       <c r="M43" s="2">
         <v>4</v>
       </c>
@@ -2832,22 +2857,22 @@
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="9"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="7"/>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="20"/>
+      <c r="H44" s="18"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="9"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="7"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
@@ -2861,22 +2886,22 @@
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="9"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="7"/>
       <c r="E45" s="2">
         <v>6</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="20"/>
+      <c r="H45" s="18"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="9"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="7"/>
       <c r="M45" s="2">
         <v>6</v>
       </c>
@@ -2888,26 +2913,26 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="7"/>
       <c r="E46" s="2">
         <v>7</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="20"/>
+      <c r="H46" s="18"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="K46" s="8"/>
+      <c r="L46" s="7"/>
       <c r="M46" s="2">
         <v>7</v>
       </c>
@@ -2919,24 +2944,24 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="7"/>
       <c r="E47" s="2">
         <v>8</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="20"/>
+      <c r="H47" s="18"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="K47" s="8"/>
+      <c r="L47" s="7"/>
       <c r="M47" s="2">
         <v>8</v>
       </c>
@@ -2948,24 +2973,24 @@
         <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="7"/>
       <c r="E48" s="2">
         <v>9</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="20"/>
+      <c r="H48" s="18"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="9"/>
+        <v>56</v>
+      </c>
+      <c r="K48" s="8"/>
+      <c r="L48" s="7"/>
       <c r="M48" s="2">
         <v>9</v>
       </c>
@@ -2977,26 +3002,26 @@
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="7"/>
       <c r="E49" s="2">
         <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="20"/>
+      <c r="H49" s="18"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="9"/>
+        <v>57</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="7"/>
       <c r="M49" s="2">
         <v>10</v>
       </c>
@@ -3008,24 +3033,24 @@
         <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="20"/>
+      <c r="H50" s="18"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="K50" s="8"/>
+      <c r="L50" s="7"/>
       <c r="M50" s="2">
         <v>11</v>
       </c>
@@ -3037,24 +3062,24 @@
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="7"/>
       <c r="E51" s="2">
         <v>12</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="20"/>
+      <c r="H51" s="18"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="9"/>
+        <v>59</v>
+      </c>
+      <c r="K51" s="8"/>
+      <c r="L51" s="7"/>
       <c r="M51" s="2">
         <v>12</v>
       </c>
@@ -3066,28 +3091,28 @@
         <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="7"/>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="20"/>
+      <c r="H52" s="18"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="L52" s="9"/>
+        <v>60</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L52" s="7"/>
       <c r="M52" s="2">
         <v>13</v>
       </c>
@@ -3099,24 +3124,24 @@
         <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="20"/>
+      <c r="H53" s="18"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="9"/>
+        <v>61</v>
+      </c>
+      <c r="K53" s="8"/>
+      <c r="L53" s="7"/>
       <c r="M53" s="2">
         <v>14</v>
       </c>
@@ -3128,24 +3153,24 @@
         <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="7"/>
       <c r="E54" s="2">
         <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="20"/>
+      <c r="H54" s="18"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="7"/>
       <c r="M54" s="2">
         <v>15</v>
       </c>
@@ -3157,28 +3182,28 @@
         <v>16</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D55" s="7"/>
       <c r="E55" s="2">
         <v>16</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="20"/>
+      <c r="H55" s="18"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L55" s="9"/>
+        <v>68</v>
+      </c>
+      <c r="L55" s="7"/>
       <c r="M55" s="2">
         <v>16</v>
       </c>
@@ -3190,24 +3215,24 @@
         <v>17</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="9"/>
+        <v>105</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="2">
         <v>17</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="20"/>
+      <c r="H56" s="18"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K56" s="2"/>
-      <c r="L56" s="9"/>
+      <c r="L56" s="7"/>
       <c r="M56" s="2">
         <v>17</v>
       </c>
@@ -3219,24 +3244,24 @@
         <v>18</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="9"/>
+        <v>106</v>
+      </c>
+      <c r="C57" s="11"/>
+      <c r="D57" s="7"/>
       <c r="E57" s="2">
         <v>18</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="20"/>
+      <c r="H57" s="18"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K57" s="2"/>
-      <c r="L57" s="9"/>
+      <c r="L57" s="7"/>
       <c r="M57" s="2">
         <v>18</v>
       </c>
@@ -3248,28 +3273,28 @@
         <v>19</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D58" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="D58" s="7"/>
       <c r="E58" s="2">
         <v>19</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="20"/>
+      <c r="H58" s="18"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L58" s="9"/>
+        <v>67</v>
+      </c>
+      <c r="L58" s="7"/>
       <c r="M58" s="2">
         <v>19</v>
       </c>
@@ -3281,26 +3306,26 @@
         <v>20</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="9"/>
+        <v>108</v>
+      </c>
+      <c r="D59" s="7"/>
       <c r="E59" s="2">
         <v>20</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="20"/>
+      <c r="H59" s="18"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="9"/>
+      <c r="L59" s="7"/>
       <c r="M59" s="2">
         <v>20</v>
       </c>
@@ -3312,24 +3337,24 @@
         <v>21</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="D60" s="7"/>
       <c r="E60" s="2">
         <v>21</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="20"/>
+      <c r="H60" s="18"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="9"/>
+      <c r="L60" s="7"/>
       <c r="M60" s="2">
         <v>21</v>
       </c>
@@ -3342,19 +3367,19 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="4"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="7"/>
       <c r="E61" s="2">
         <v>22</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="20"/>
+      <c r="H61" s="18"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="9"/>
+      <c r="L61" s="7"/>
       <c r="M61" s="2">
         <v>22</v>
       </c>
@@ -3366,24 +3391,24 @@
         <v>23</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D62" s="9"/>
+        <v>51</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="7"/>
       <c r="E62" s="2">
         <v>23</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="20"/>
+      <c r="H62" s="18"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="9"/>
+      <c r="L62" s="7"/>
       <c r="M62" s="2">
         <v>23</v>
       </c>
@@ -3395,22 +3420,22 @@
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="2">
         <v>24</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="20"/>
+      <c r="H63" s="18"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="9"/>
+      <c r="L63" s="7"/>
       <c r="M63" s="2">
         <v>24</v>
       </c>
@@ -3422,22 +3447,22 @@
         <v>25</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="C64" s="11"/>
+      <c r="D64" s="7"/>
       <c r="E64" s="2">
         <v>25</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="20"/>
+      <c r="H64" s="18"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="9"/>
+      <c r="L64" s="7"/>
       <c r="M64" s="2">
         <v>25</v>
       </c>
@@ -3449,24 +3474,24 @@
         <v>26</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="9"/>
+        <v>68</v>
+      </c>
+      <c r="D65" s="7"/>
       <c r="E65" s="2">
         <v>26</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="20"/>
+      <c r="H65" s="18"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="9"/>
+      <c r="L65" s="7"/>
       <c r="M65" s="2">
         <v>26</v>
       </c>
@@ -3479,19 +3504,19 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="7"/>
       <c r="E66" s="2">
         <v>27</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="20"/>
+      <c r="H66" s="18"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="9"/>
+      <c r="L66" s="7"/>
       <c r="M66" s="2">
         <v>27</v>
       </c>
@@ -3503,22 +3528,22 @@
         <v>28</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="7"/>
       <c r="E67" s="2">
         <v>28</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="20"/>
+      <c r="H67" s="18"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="9"/>
+      <c r="L67" s="7"/>
       <c r="M67" s="2">
         <v>28</v>
       </c>
@@ -3531,19 +3556,19 @@
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="9"/>
+      <c r="D68" s="7"/>
       <c r="E68" s="2">
         <v>29</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="20"/>
+      <c r="H68" s="18"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="9"/>
+      <c r="L68" s="7"/>
       <c r="M68" s="2">
         <v>29</v>
       </c>
@@ -3556,19 +3581,19 @@
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="9"/>
+      <c r="D69" s="7"/>
       <c r="E69" s="2">
         <v>30</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="20"/>
+      <c r="H69" s="18"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="9"/>
+      <c r="L69" s="7"/>
       <c r="M69" s="2">
         <v>30</v>
       </c>
@@ -3581,19 +3606,19 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="7"/>
       <c r="E70" s="2">
         <v>31</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="20"/>
+      <c r="H70" s="18"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="9"/>
+      <c r="L70" s="7"/>
       <c r="M70" s="2">
         <v>31</v>
       </c>
@@ -3606,19 +3631,19 @@
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="7"/>
       <c r="E71" s="2">
         <v>32</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="21"/>
+      <c r="H71" s="19"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="9"/>
+      <c r="L71" s="7"/>
       <c r="M71" s="2">
         <v>32</v>
       </c>
@@ -3629,13 +3654,13 @@
   <mergeCells count="58">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="G17:G19"/>
     <mergeCell ref="G33:G35"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G7:G9"/>
     <mergeCell ref="Q20:U20"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="C46:C48"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BAD0B5-FCB1-4BC3-BB73-B5093A5D7CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0762B1AB-B467-4937-9A9A-B0E70F39FDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="147">
   <si>
     <t>Freq:</t>
   </si>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>encrypted friendly selected</t>
+  </si>
+  <si>
+    <t>01 A/G mode</t>
   </si>
 </sst>
 </file>
@@ -675,9 +678,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -694,6 +694,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1057,7 +1060,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
-      <c r="H1" s="13"/>
+      <c r="H1" s="19"/>
       <c r="I1" s="7" t="s">
         <v>53</v>
       </c>
@@ -1089,7 +1092,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="13"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="7" t="s">
         <v>24</v>
       </c>
@@ -1136,7 +1139,7 @@
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="13"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1199,7 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="19"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
@@ -1252,7 +1255,7 @@
         <v>135</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="13"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
@@ -1308,7 +1311,7 @@
       <c r="G6" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="13"/>
+      <c r="H6" s="19"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
@@ -1366,7 +1369,7 @@
       <c r="G7" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="H7" s="13"/>
+      <c r="H7" s="19"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>133</v>
       </c>
       <c r="G8" s="10"/>
-      <c r="H8" s="13"/>
+      <c r="H8" s="19"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>134</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="13"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
@@ -1534,7 +1537,7 @@
       <c r="G10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="13"/>
+      <c r="H10" s="19"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
@@ -1590,7 +1593,7 @@
         <v>42</v>
       </c>
       <c r="G11" s="8"/>
-      <c r="H11" s="13"/>
+      <c r="H11" s="19"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
@@ -1646,7 +1649,7 @@
       <c r="G12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="13"/>
+      <c r="H12" s="19"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>27</v>
       </c>
       <c r="G13" s="8"/>
-      <c r="H13" s="13"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
@@ -1760,7 +1763,7 @@
       <c r="G14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="13"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
@@ -1815,7 +1818,7 @@
       <c r="F15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H15" s="13"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>137</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="13"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
@@ -1927,7 +1930,7 @@
       <c r="G17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="13"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
@@ -1977,7 +1980,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="8"/>
-      <c r="H18" s="13"/>
+      <c r="H18" s="19"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
@@ -2025,7 +2028,7 @@
         <v>31</v>
       </c>
       <c r="G19" s="8"/>
-      <c r="H19" s="13"/>
+      <c r="H19" s="19"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
@@ -2077,7 +2080,7 @@
       <c r="G20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="13"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
@@ -2119,7 +2122,7 @@
         <v>33</v>
       </c>
       <c r="G21" s="8"/>
-      <c r="H21" s="13"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
@@ -2152,7 +2155,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="8"/>
-      <c r="H22" s="13"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -2189,7 +2192,7 @@
       <c r="G23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="13"/>
+      <c r="H23" s="19"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
@@ -2224,7 +2227,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="8"/>
-      <c r="H24" s="13"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -2259,7 +2262,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="8"/>
-      <c r="H25" s="13"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
@@ -2292,7 +2295,7 @@
       <c r="G26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="13"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
@@ -2329,7 +2332,7 @@
         <v>105</v>
       </c>
       <c r="G27" s="10"/>
-      <c r="H27" s="13"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>106</v>
       </c>
       <c r="G28" s="11"/>
-      <c r="H28" s="13"/>
+      <c r="H28" s="19"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -2397,7 +2400,7 @@
       <c r="G29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="13"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2428,7 +2431,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="13"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2463,7 +2466,7 @@
       <c r="G31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="13"/>
+      <c r="H31" s="19"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2484,7 +2487,9 @@
       <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="7"/>
       <c r="E32" s="2">
@@ -2496,7 +2501,7 @@
       <c r="G32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="13"/>
+      <c r="H32" s="19"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2535,7 +2540,7 @@
       <c r="G33" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="13"/>
+      <c r="H33" s="19"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2568,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="G34" s="8"/>
-      <c r="H34" s="13"/>
+      <c r="H34" s="19"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2601,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="G35" s="8"/>
-      <c r="H35" s="13"/>
+      <c r="H35" s="19"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
@@ -2619,21 +2624,21 @@
       <c r="AF35" s="12"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="16"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="15"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
@@ -2645,7 +2650,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
-      <c r="H37" s="17"/>
+      <c r="H37" s="16"/>
       <c r="I37" s="7" t="s">
         <v>65</v>
       </c>
@@ -2668,7 +2673,7 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="18"/>
+      <c r="H38" s="17"/>
       <c r="I38" s="7" t="s">
         <v>24</v>
       </c>
@@ -2701,7 +2706,7 @@
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="18"/>
+      <c r="H39" s="17"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2742,7 +2747,7 @@
       <c r="G40" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="18"/>
+      <c r="H40" s="17"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
@@ -2775,7 +2780,7 @@
         <v>110</v>
       </c>
       <c r="G41" s="11"/>
-      <c r="H41" s="18"/>
+      <c r="H41" s="17"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
@@ -2804,7 +2809,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="18"/>
+      <c r="H42" s="17"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
@@ -2835,7 +2840,7 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="18"/>
+      <c r="H43" s="17"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
@@ -2864,7 +2869,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="18"/>
+      <c r="H44" s="17"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
@@ -2893,7 +2898,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="18"/>
+      <c r="H45" s="17"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
@@ -2924,7 +2929,7 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="18"/>
+      <c r="H46" s="17"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
@@ -2953,7 +2958,7 @@
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="18"/>
+      <c r="H47" s="17"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
@@ -2982,7 +2987,7 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="18"/>
+      <c r="H48" s="17"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
@@ -3013,7 +3018,7 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="18"/>
+      <c r="H49" s="17"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="18"/>
+      <c r="H50" s="17"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
@@ -3071,7 +3076,7 @@
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="18"/>
+      <c r="H51" s="17"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
@@ -3102,7 +3107,7 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="18"/>
+      <c r="H52" s="17"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
@@ -3133,7 +3138,7 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="18"/>
+      <c r="H53" s="17"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
@@ -3162,7 +3167,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="18"/>
+      <c r="H54" s="17"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="18"/>
+      <c r="H55" s="17"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3224,7 +3229,7 @@
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="18"/>
+      <c r="H56" s="17"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3253,7 +3258,7 @@
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="18"/>
+      <c r="H57" s="17"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3284,7 +3289,7 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="18"/>
+      <c r="H58" s="17"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3317,7 +3322,7 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="18"/>
+      <c r="H59" s="17"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3348,7 +3353,7 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="18"/>
+      <c r="H60" s="17"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="18"/>
+      <c r="H61" s="17"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
@@ -3402,7 +3407,7 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="18"/>
+      <c r="H62" s="17"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
@@ -3429,7 +3434,7 @@
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="18"/>
+      <c r="H63" s="17"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
@@ -3456,7 +3461,7 @@
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="18"/>
+      <c r="H64" s="17"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
@@ -3485,7 +3490,7 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="18"/>
+      <c r="H65" s="17"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
@@ -3510,7 +3515,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="18"/>
+      <c r="H66" s="17"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
@@ -3537,7 +3542,7 @@
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="18"/>
+      <c r="H67" s="17"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
@@ -3562,7 +3567,7 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="18"/>
+      <c r="H68" s="17"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
@@ -3587,7 +3592,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="18"/>
+      <c r="H69" s="17"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
@@ -3612,7 +3617,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="18"/>
+      <c r="H70" s="17"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
@@ -3637,7 +3642,7 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="19"/>
+      <c r="H71" s="18"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
@@ -3652,15 +3657,39 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="AF1:AF35"/>
+    <mergeCell ref="P1:P35"/>
+    <mergeCell ref="H1:H35"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="D2:D35"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="Q20:U20"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="C46:C48"/>
@@ -3677,39 +3706,15 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="D38:D71"/>
     <mergeCell ref="E38:G38"/>
-    <mergeCell ref="AF1:AF35"/>
-    <mergeCell ref="P1:P35"/>
-    <mergeCell ref="H1:H35"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="D2:D35"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G7:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/parts and their channels.xlsx
+++ b/documentation/parts and their channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Squingle\Desktop\!folders\! d-github\EISS\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0762B1AB-B467-4937-9A9A-B0E70F39FDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A7ABB7-53F0-4E55-9C7E-852B11202F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A0965BB0-A002-463F-9819-73939F3991DC}"/>
   </bookViews>
@@ -678,6 +678,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -694,9 +697,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1060,7 +1060,7 @@
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
-      <c r="H1" s="19"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="7" t="s">
         <v>53</v>
       </c>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="19"/>
+      <c r="H2" s="13"/>
       <c r="I2" s="7" t="s">
         <v>24</v>
       </c>
@@ -1139,7 +1139,7 @@
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="19"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="19"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="2">
         <v>1</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>135</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="19"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="2">
         <v>2</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="G6" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="2">
         <v>3</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="G7" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="13"/>
       <c r="I7" s="2">
         <v>4</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>133</v>
       </c>
       <c r="G8" s="10"/>
-      <c r="H8" s="19"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="2">
         <v>5</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>134</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="19"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="2">
         <v>6</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="G10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="2">
         <v>7</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>42</v>
       </c>
       <c r="G11" s="8"/>
-      <c r="H11" s="19"/>
+      <c r="H11" s="13"/>
       <c r="I11" s="2">
         <v>8</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="G12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="13"/>
       <c r="I12" s="2">
         <v>9</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>27</v>
       </c>
       <c r="G13" s="8"/>
-      <c r="H13" s="19"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="2">
         <v>10</v>
       </c>
@@ -1763,7 +1763,7 @@
       <c r="G14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="13"/>
       <c r="I14" s="2">
         <v>11</v>
       </c>
@@ -1818,7 +1818,7 @@
       <c r="F15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="13"/>
       <c r="I15" s="2">
         <v>12</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>137</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="19"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="2">
         <v>13</v>
       </c>
@@ -1930,7 +1930,7 @@
       <c r="G17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="19"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="2">
         <v>14</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="8"/>
-      <c r="H18" s="19"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="2">
         <v>15</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>31</v>
       </c>
       <c r="G19" s="8"/>
-      <c r="H19" s="19"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="2">
         <v>16</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="G20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="19"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="2">
         <v>17</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>33</v>
       </c>
       <c r="G21" s="8"/>
-      <c r="H21" s="19"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="2">
         <v>18</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="8"/>
-      <c r="H22" s="19"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="2">
         <v>19</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="G23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="19"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="2">
         <v>20</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="8"/>
-      <c r="H24" s="19"/>
+      <c r="H24" s="13"/>
       <c r="I24" s="2">
         <v>21</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="8"/>
-      <c r="H25" s="19"/>
+      <c r="H25" s="13"/>
       <c r="I25" s="2">
         <v>22</v>
       </c>
@@ -2295,7 +2295,7 @@
       <c r="G26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="19"/>
+      <c r="H26" s="13"/>
       <c r="I26" s="2">
         <v>23</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>105</v>
       </c>
       <c r="G27" s="10"/>
-      <c r="H27" s="19"/>
+      <c r="H27" s="13"/>
       <c r="I27" s="2">
         <v>24</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>106</v>
       </c>
       <c r="G28" s="11"/>
-      <c r="H28" s="19"/>
+      <c r="H28" s="13"/>
       <c r="I28" s="2">
         <v>25</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="G29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="19"/>
+      <c r="H29" s="13"/>
       <c r="I29" s="2">
         <v>26</v>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="19"/>
+      <c r="H30" s="13"/>
       <c r="I30" s="2">
         <v>27</v>
       </c>
@@ -2466,7 +2466,7 @@
       <c r="G31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="19"/>
+      <c r="H31" s="13"/>
       <c r="I31" s="2">
         <v>28</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="G32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="19"/>
+      <c r="H32" s="13"/>
       <c r="I32" s="2">
         <v>29</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="G33" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="19"/>
+      <c r="H33" s="13"/>
       <c r="I33" s="2">
         <v>30</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="G34" s="8"/>
-      <c r="H34" s="19"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="2">
         <v>31</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="G35" s="8"/>
-      <c r="H35" s="19"/>
+      <c r="H35" s="13"/>
       <c r="I35" s="2">
         <v>32</v>
       </c>
@@ -2624,21 +2624,21 @@
       <c r="AF35" s="12"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
@@ -2650,7 +2650,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
-      <c r="H37" s="16"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="7" t="s">
         <v>65</v>
       </c>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="17"/>
+      <c r="H38" s="18"/>
       <c r="I38" s="7" t="s">
         <v>24</v>
       </c>
@@ -2706,7 +2706,7 @@
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="17"/>
+      <c r="H39" s="18"/>
       <c r="I39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="G40" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="17"/>
+      <c r="H40" s="18"/>
       <c r="I40" s="2">
         <v>1</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>110</v>
       </c>
       <c r="G41" s="11"/>
-      <c r="H41" s="17"/>
+      <c r="H41" s="18"/>
       <c r="I41" s="2">
         <v>2</v>
       </c>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="17"/>
+      <c r="H42" s="18"/>
       <c r="I42" s="2">
         <v>3</v>
       </c>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="17"/>
+      <c r="H43" s="18"/>
       <c r="I43" s="2">
         <v>4</v>
       </c>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="17"/>
+      <c r="H44" s="18"/>
       <c r="I44" s="2">
         <v>5</v>
       </c>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="17"/>
+      <c r="H45" s="18"/>
       <c r="I45" s="2">
         <v>6</v>
       </c>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="17"/>
+      <c r="H46" s="18"/>
       <c r="I46" s="2">
         <v>7</v>
       </c>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="17"/>
+      <c r="H47" s="18"/>
       <c r="I47" s="2">
         <v>8</v>
       </c>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="17"/>
+      <c r="H48" s="18"/>
       <c r="I48" s="2">
         <v>9</v>
       </c>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="17"/>
+      <c r="H49" s="18"/>
       <c r="I49" s="2">
         <v>10</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="17"/>
+      <c r="H50" s="18"/>
       <c r="I50" s="2">
         <v>11</v>
       </c>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="17"/>
+      <c r="H51" s="18"/>
       <c r="I51" s="2">
         <v>12</v>
       </c>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="17"/>
+      <c r="H52" s="18"/>
       <c r="I52" s="2">
         <v>13</v>
       </c>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="17"/>
+      <c r="H53" s="18"/>
       <c r="I53" s="2">
         <v>14</v>
       </c>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="17"/>
+      <c r="H54" s="18"/>
       <c r="I54" s="2">
         <v>15</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="17"/>
+      <c r="H55" s="18"/>
       <c r="I55" s="2">
         <v>16</v>
       </c>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="17"/>
+      <c r="H56" s="18"/>
       <c r="I56" s="2">
         <v>17</v>
       </c>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="17"/>
+      <c r="H57" s="18"/>
       <c r="I57" s="2">
         <v>18</v>
       </c>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="17"/>
+      <c r="H58" s="18"/>
       <c r="I58" s="2">
         <v>19</v>
       </c>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="17"/>
+      <c r="H59" s="18"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="17"/>
+      <c r="H60" s="18"/>
       <c r="I60" s="2">
         <v>21</v>
       </c>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="17"/>
+      <c r="H61" s="18"/>
       <c r="I61" s="2">
         <v>22</v>
       </c>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="17"/>
+      <c r="H62" s="18"/>
       <c r="I62" s="2">
         <v>23</v>
       </c>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="17"/>
+      <c r="H63" s="18"/>
       <c r="I63" s="2">
         <v>24</v>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="17"/>
+      <c r="H64" s="18"/>
       <c r="I64" s="2">
         <v>25</v>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="17"/>
+      <c r="H65" s="18"/>
       <c r="I65" s="2">
         <v>26</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="17"/>
+      <c r="H66" s="18"/>
       <c r="I66" s="2">
         <v>27</v>
       </c>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="17"/>
+      <c r="H67" s="18"/>
       <c r="I67" s="2">
         <v>28</v>
       </c>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="17"/>
+      <c r="H68" s="18"/>
       <c r="I68" s="2">
         <v>29</v>
       </c>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="17"/>
+      <c r="H69" s="18"/>
       <c r="I69" s="2">
         <v>30</v>
       </c>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="17"/>
+      <c r="H70" s="18"/>
       <c r="I70" s="2">
         <v>31</v>
       </c>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="18"/>
+      <c r="H71" s="19"/>
       <c r="I71" s="2">
         <v>32</v>
       </c>
@@ -3657,23 +3657,31 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:L35"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="K40:K51"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="H37:H71"/>
+    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:L71"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="K52:K54"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:D71"/>
+    <mergeCell ref="E38:G38"/>
     <mergeCell ref="AF1:AF35"/>
     <mergeCell ref="P1:P35"/>
     <mergeCell ref="H1:H35"/>
@@ -3690,31 +3698,23 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="K40:K51"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="H37:H71"/>
-    <mergeCell ref="I37:O37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:L71"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:D71"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:L35"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="K26:K28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
